--- a/Data/LIVRABLE.xlsx
+++ b/Data/LIVRABLE.xlsx
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="864" uniqueCount="615">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="864" uniqueCount="614">
   <si>
     <t>Cybersecurity Governance &amp; Protection</t>
   </si>
@@ -1969,9 +1969,6 @@
   </si>
   <si>
     <t>Confirmitee</t>
-  </si>
-  <si>
-    <t>Score final</t>
   </si>
   <si>
     <t>Nb App</t>
@@ -2557,7 +2554,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="195">
+  <cellXfs count="200">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2912,6 +2909,10 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="1" fontId="16" fillId="11" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2949,43 +2950,97 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="10" fillId="8" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="10" fillId="8" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="10" fillId="8" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="10" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3005,58 +3060,7 @@
     <xf numFmtId="0" fontId="10" fillId="11" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="10" fillId="8" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="10" fillId="8" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="10" fillId="8" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="12" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3068,7 +3072,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3080,43 +3090,41 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="16" fillId="11" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4049,7 +4057,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -4193,20 +4201,20 @@
     <row r="3" spans="1:31" ht="28.8">
       <c r="A3" s="50"/>
       <c r="B3" s="5"/>
-      <c r="C3" s="131" t="s">
+      <c r="C3" s="133" t="s">
         <v>133</v>
       </c>
-      <c r="D3" s="133"/>
-      <c r="E3" s="133"/>
-      <c r="F3" s="133"/>
-      <c r="G3" s="133"/>
-      <c r="H3" s="133"/>
-      <c r="I3" s="132"/>
+      <c r="D3" s="135"/>
+      <c r="E3" s="135"/>
+      <c r="F3" s="135"/>
+      <c r="G3" s="135"/>
+      <c r="H3" s="135"/>
+      <c r="I3" s="134"/>
       <c r="J3" s="40"/>
-      <c r="K3" s="131" t="s">
+      <c r="K3" s="133" t="s">
         <v>134</v>
       </c>
-      <c r="L3" s="132"/>
+      <c r="L3" s="134"/>
       <c r="M3" s="40"/>
       <c r="N3" s="38" t="s">
         <v>148</v>
@@ -4245,10 +4253,10 @@
         <v>219</v>
       </c>
       <c r="J4" s="19"/>
-      <c r="K4" s="129" t="s">
+      <c r="K4" s="131" t="s">
         <v>140</v>
       </c>
-      <c r="L4" s="130"/>
+      <c r="L4" s="132"/>
       <c r="M4" s="5"/>
       <c r="N4" s="62" t="s">
         <v>135</v>
@@ -4291,10 +4299,10 @@
         <v>4</v>
       </c>
       <c r="J5" s="20"/>
-      <c r="K5" s="129" t="s">
+      <c r="K5" s="131" t="s">
         <v>141</v>
       </c>
-      <c r="L5" s="130"/>
+      <c r="L5" s="132"/>
       <c r="M5" s="5"/>
       <c r="N5" s="62" t="s">
         <v>136</v>
@@ -4337,10 +4345,10 @@
         <v>3</v>
       </c>
       <c r="J6" s="20"/>
-      <c r="K6" s="129" t="s">
+      <c r="K6" s="131" t="s">
         <v>142</v>
       </c>
-      <c r="L6" s="130"/>
+      <c r="L6" s="132"/>
       <c r="M6" s="5"/>
       <c r="N6" s="62" t="s">
         <v>137</v>
@@ -4383,10 +4391,10 @@
         <v>6</v>
       </c>
       <c r="J7" s="20"/>
-      <c r="K7" s="129" t="s">
+      <c r="K7" s="131" t="s">
         <v>143</v>
       </c>
-      <c r="L7" s="130"/>
+      <c r="L7" s="132"/>
       <c r="M7" s="5"/>
       <c r="N7" s="62" t="s">
         <v>138</v>
@@ -4431,10 +4439,10 @@
         <v>5</v>
       </c>
       <c r="J8" s="20"/>
-      <c r="K8" s="129" t="s">
+      <c r="K8" s="131" t="s">
         <v>144</v>
       </c>
-      <c r="L8" s="130"/>
+      <c r="L8" s="132"/>
       <c r="M8" s="5"/>
       <c r="N8" s="62" t="s">
         <v>139</v>
@@ -4477,10 +4485,10 @@
         <v>0.66666666666666663</v>
       </c>
       <c r="J9" s="20"/>
-      <c r="K9" s="129" t="s">
+      <c r="K9" s="131" t="s">
         <v>145</v>
       </c>
-      <c r="L9" s="130"/>
+      <c r="L9" s="132"/>
       <c r="M9" s="5"/>
       <c r="N9" s="62" t="s">
         <v>219</v>
@@ -4588,15 +4596,15 @@
     <row r="12" spans="1:31">
       <c r="A12" s="50"/>
       <c r="B12" s="5"/>
-      <c r="C12" s="134"/>
-      <c r="D12" s="134"/>
-      <c r="E12" s="134"/>
-      <c r="F12" s="134"/>
-      <c r="G12" s="134"/>
-      <c r="H12" s="134"/>
-      <c r="I12" s="134"/>
-      <c r="J12" s="134"/>
-      <c r="K12" s="134"/>
+      <c r="C12" s="136"/>
+      <c r="D12" s="136"/>
+      <c r="E12" s="136"/>
+      <c r="F12" s="136"/>
+      <c r="G12" s="136"/>
+      <c r="H12" s="136"/>
+      <c r="I12" s="136"/>
+      <c r="J12" s="136"/>
+      <c r="K12" s="136"/>
       <c r="L12" s="5"/>
       <c r="M12" s="22"/>
       <c r="S12" s="50"/>
@@ -4604,37 +4612,37 @@
     <row r="13" spans="1:31" ht="14.55" customHeight="1">
       <c r="A13" s="50"/>
       <c r="B13" s="5"/>
-      <c r="C13" s="135" t="s">
+      <c r="C13" s="137" t="s">
         <v>147</v>
       </c>
-      <c r="D13" s="136"/>
-      <c r="E13" s="136"/>
-      <c r="F13" s="136"/>
-      <c r="G13" s="136"/>
-      <c r="H13" s="136"/>
-      <c r="I13" s="136"/>
-      <c r="J13" s="136"/>
-      <c r="K13" s="136"/>
-      <c r="L13" s="137"/>
+      <c r="D13" s="138"/>
+      <c r="E13" s="138"/>
+      <c r="F13" s="138"/>
+      <c r="G13" s="138"/>
+      <c r="H13" s="138"/>
+      <c r="I13" s="138"/>
+      <c r="J13" s="138"/>
+      <c r="K13" s="138"/>
+      <c r="L13" s="139"/>
       <c r="M13" s="22"/>
       <c r="S13" s="50"/>
     </row>
     <row r="14" spans="1:31" ht="15.6">
       <c r="A14" s="50"/>
       <c r="B14" s="5"/>
-      <c r="C14" s="126" t="s">
+      <c r="C14" s="128" t="s">
         <v>148</v>
       </c>
-      <c r="D14" s="127"/>
-      <c r="E14" s="127"/>
-      <c r="F14" s="127"/>
-      <c r="G14" s="127"/>
-      <c r="H14" s="127"/>
-      <c r="I14" s="128"/>
-      <c r="J14" s="126" t="s">
+      <c r="D14" s="129"/>
+      <c r="E14" s="129"/>
+      <c r="F14" s="129"/>
+      <c r="G14" s="129"/>
+      <c r="H14" s="129"/>
+      <c r="I14" s="130"/>
+      <c r="J14" s="128" t="s">
         <v>149</v>
       </c>
-      <c r="K14" s="128"/>
+      <c r="K14" s="130"/>
       <c r="L14" s="35" t="s">
         <v>217</v>
       </c>
@@ -5182,7 +5190,7 @@
     </row>
     <row r="3" spans="1:22" ht="81" customHeight="1">
       <c r="A3" s="50"/>
-      <c r="B3" s="142"/>
+      <c r="B3" s="141"/>
       <c r="C3" s="145"/>
       <c r="D3" s="4" t="s">
         <v>43</v>
@@ -5219,7 +5227,7 @@
     </row>
     <row r="4" spans="1:22" ht="79.95" customHeight="1" thickBot="1">
       <c r="A4" s="50"/>
-      <c r="B4" s="142"/>
+      <c r="B4" s="141"/>
       <c r="C4" s="4" t="s">
         <v>55</v>
       </c>
@@ -5257,7 +5265,7 @@
     </row>
     <row r="5" spans="1:22" ht="87" thickBot="1">
       <c r="A5" s="50"/>
-      <c r="B5" s="142"/>
+      <c r="B5" s="141"/>
       <c r="C5" s="3" t="s">
         <v>283</v>
       </c>
@@ -5285,15 +5293,15 @@
       <c r="K5" s="50"/>
       <c r="L5" s="50"/>
       <c r="M5" s="92" t="s">
+        <v>611</v>
+      </c>
+      <c r="N5" s="126" t="s">
         <v>612</v>
-      </c>
-      <c r="N5" s="193" t="s">
-        <v>613</v>
       </c>
     </row>
     <row r="6" spans="1:22" ht="91.05" customHeight="1">
       <c r="A6" s="50"/>
-      <c r="B6" s="142"/>
+      <c r="B6" s="141"/>
       <c r="C6" s="146" t="s">
         <v>293</v>
       </c>
@@ -5323,7 +5331,7 @@
     </row>
     <row r="7" spans="1:22" ht="43.5" customHeight="1">
       <c r="A7" s="50"/>
-      <c r="B7" s="142"/>
+      <c r="B7" s="141"/>
       <c r="C7" s="147"/>
       <c r="D7" s="140" t="s">
         <v>287</v>
@@ -5351,23 +5359,23 @@
     </row>
     <row r="8" spans="1:22" ht="43.5" customHeight="1">
       <c r="A8" s="50"/>
-      <c r="B8" s="142"/>
+      <c r="B8" s="141"/>
       <c r="C8" s="147"/>
-      <c r="D8" s="142"/>
+      <c r="D8" s="141"/>
       <c r="E8" s="144"/>
       <c r="F8" s="144"/>
       <c r="G8" s="144"/>
       <c r="H8" s="144"/>
       <c r="I8" s="83"/>
-      <c r="J8" s="141"/>
+      <c r="J8" s="142"/>
       <c r="K8" s="50"/>
       <c r="L8" s="50"/>
     </row>
     <row r="9" spans="1:22" ht="49.95" customHeight="1">
       <c r="A9" s="50"/>
-      <c r="B9" s="142"/>
+      <c r="B9" s="141"/>
       <c r="C9" s="147"/>
-      <c r="D9" s="141"/>
+      <c r="D9" s="142"/>
       <c r="E9" s="24" t="s">
         <v>459</v>
       </c>
@@ -5391,7 +5399,7 @@
     </row>
     <row r="10" spans="1:22" ht="43.5" customHeight="1">
       <c r="A10" s="50"/>
-      <c r="B10" s="142"/>
+      <c r="B10" s="141"/>
       <c r="C10" s="147"/>
       <c r="D10" s="140" t="s">
         <v>288</v>
@@ -5419,9 +5427,9 @@
     </row>
     <row r="11" spans="1:22" ht="43.5" customHeight="1">
       <c r="A11" s="50"/>
-      <c r="B11" s="142"/>
+      <c r="B11" s="141"/>
       <c r="C11" s="147"/>
-      <c r="D11" s="142"/>
+      <c r="D11" s="141"/>
       <c r="E11" s="143" t="s">
         <v>465</v>
       </c>
@@ -5445,21 +5453,21 @@
     </row>
     <row r="12" spans="1:22" ht="43.5" customHeight="1">
       <c r="A12" s="50"/>
-      <c r="B12" s="142"/>
+      <c r="B12" s="141"/>
       <c r="C12" s="147"/>
-      <c r="D12" s="141"/>
+      <c r="D12" s="142"/>
       <c r="E12" s="144"/>
       <c r="F12" s="144"/>
       <c r="G12" s="144"/>
       <c r="H12" s="144"/>
       <c r="I12" s="83"/>
-      <c r="J12" s="141"/>
+      <c r="J12" s="142"/>
       <c r="K12" s="50"/>
       <c r="L12" s="50"/>
     </row>
     <row r="13" spans="1:22" ht="43.2">
       <c r="A13" s="50"/>
-      <c r="B13" s="142"/>
+      <c r="B13" s="141"/>
       <c r="C13" s="147"/>
       <c r="D13" s="140" t="s">
         <v>289</v>
@@ -5487,9 +5495,9 @@
     </row>
     <row r="14" spans="1:22" ht="53.55" customHeight="1">
       <c r="A14" s="50"/>
-      <c r="B14" s="142"/>
+      <c r="B14" s="141"/>
       <c r="C14" s="147"/>
-      <c r="D14" s="142"/>
+      <c r="D14" s="141"/>
       <c r="E14" s="42" t="s">
         <v>469</v>
       </c>
@@ -5513,9 +5521,9 @@
     </row>
     <row r="15" spans="1:22" ht="51" customHeight="1">
       <c r="A15" s="50"/>
-      <c r="B15" s="142"/>
+      <c r="B15" s="141"/>
       <c r="C15" s="147"/>
-      <c r="D15" s="141"/>
+      <c r="D15" s="142"/>
       <c r="E15" s="42" t="s">
         <v>470</v>
       </c>
@@ -5539,7 +5547,7 @@
     </row>
     <row r="16" spans="1:22" ht="47.55" customHeight="1">
       <c r="A16" s="50"/>
-      <c r="B16" s="142"/>
+      <c r="B16" s="141"/>
       <c r="C16" s="147"/>
       <c r="D16" s="140" t="s">
         <v>290</v>
@@ -5567,35 +5575,35 @@
     </row>
     <row r="17" spans="1:12" ht="22.05" hidden="1" customHeight="1">
       <c r="A17" s="50"/>
-      <c r="B17" s="142"/>
+      <c r="B17" s="141"/>
       <c r="C17" s="147"/>
-      <c r="D17" s="142"/>
+      <c r="D17" s="141"/>
       <c r="E17" s="150"/>
       <c r="F17" s="150"/>
       <c r="G17" s="150"/>
       <c r="H17" s="150"/>
       <c r="I17" s="84"/>
-      <c r="J17" s="142"/>
+      <c r="J17" s="141"/>
       <c r="K17" s="50"/>
       <c r="L17" s="50"/>
     </row>
     <row r="18" spans="1:12">
       <c r="A18" s="50"/>
-      <c r="B18" s="142"/>
+      <c r="B18" s="141"/>
       <c r="C18" s="147"/>
-      <c r="D18" s="141"/>
+      <c r="D18" s="142"/>
       <c r="E18" s="144"/>
       <c r="F18" s="144"/>
       <c r="G18" s="144"/>
       <c r="H18" s="144"/>
       <c r="I18" s="83"/>
-      <c r="J18" s="141"/>
+      <c r="J18" s="142"/>
       <c r="K18" s="50"/>
       <c r="L18" s="50"/>
     </row>
     <row r="19" spans="1:12" ht="61.95" customHeight="1">
       <c r="A19" s="50"/>
-      <c r="B19" s="142"/>
+      <c r="B19" s="141"/>
       <c r="C19" s="147"/>
       <c r="D19" s="140" t="s">
         <v>291</v>
@@ -5623,16 +5631,16 @@
     </row>
     <row r="20" spans="1:12">
       <c r="A20" s="50"/>
-      <c r="B20" s="142"/>
+      <c r="B20" s="141"/>
       <c r="C20" s="147"/>
-      <c r="D20" s="142"/>
+      <c r="D20" s="141"/>
       <c r="E20" s="143" t="s">
         <v>481</v>
       </c>
       <c r="F20" s="143" t="s">
         <v>485</v>
       </c>
-      <c r="G20" s="138" t="s">
+      <c r="G20" s="151" t="s">
         <v>489</v>
       </c>
       <c r="H20" s="143" t="s">
@@ -5647,25 +5655,25 @@
     </row>
     <row r="21" spans="1:12" ht="28.95" customHeight="1">
       <c r="A21" s="50"/>
-      <c r="B21" s="142"/>
+      <c r="B21" s="141"/>
       <c r="C21" s="147"/>
-      <c r="D21" s="142"/>
+      <c r="D21" s="141"/>
       <c r="E21" s="144"/>
       <c r="F21" s="144"/>
-      <c r="G21" s="139"/>
+      <c r="G21" s="152"/>
       <c r="H21" s="144"/>
       <c r="I21" s="83" t="s">
         <v>564</v>
       </c>
-      <c r="J21" s="141"/>
+      <c r="J21" s="142"/>
       <c r="K21" s="50"/>
       <c r="L21" s="50"/>
     </row>
     <row r="22" spans="1:12" ht="39.450000000000003" customHeight="1">
       <c r="A22" s="50"/>
-      <c r="B22" s="142"/>
+      <c r="B22" s="141"/>
       <c r="C22" s="147"/>
-      <c r="D22" s="142"/>
+      <c r="D22" s="141"/>
       <c r="E22" s="24" t="s">
         <v>482</v>
       </c>
@@ -5689,7 +5697,7 @@
     </row>
     <row r="23" spans="1:12" ht="42" customHeight="1">
       <c r="A23" s="50"/>
-      <c r="B23" s="142"/>
+      <c r="B23" s="141"/>
       <c r="C23" s="147"/>
       <c r="D23" s="145" t="s">
         <v>292</v>
@@ -5717,7 +5725,7 @@
     </row>
     <row r="24" spans="1:12" ht="28.95" customHeight="1">
       <c r="A24" s="50"/>
-      <c r="B24" s="141"/>
+      <c r="B24" s="142"/>
       <c r="C24" s="148"/>
       <c r="D24" s="145"/>
       <c r="E24" s="144"/>
@@ -5725,7 +5733,7 @@
       <c r="G24" s="144"/>
       <c r="H24" s="144"/>
       <c r="I24" s="83"/>
-      <c r="J24" s="141"/>
+      <c r="J24" s="142"/>
       <c r="K24" s="50"/>
       <c r="L24" s="50"/>
     </row>
@@ -5759,16 +5767,14 @@
     </row>
   </sheetData>
   <mergeCells count="34">
-    <mergeCell ref="D10:D12"/>
-    <mergeCell ref="D13:D15"/>
-    <mergeCell ref="G11:G12"/>
-    <mergeCell ref="F11:F12"/>
-    <mergeCell ref="E11:E12"/>
-    <mergeCell ref="D7:D9"/>
-    <mergeCell ref="G7:G8"/>
-    <mergeCell ref="F7:F8"/>
-    <mergeCell ref="E7:E8"/>
-    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="G20:G21"/>
+    <mergeCell ref="J20:J21"/>
+    <mergeCell ref="J23:J24"/>
+    <mergeCell ref="J16:J18"/>
+    <mergeCell ref="H7:H8"/>
+    <mergeCell ref="J7:J8"/>
+    <mergeCell ref="H11:H12"/>
+    <mergeCell ref="J11:J12"/>
     <mergeCell ref="D19:D22"/>
     <mergeCell ref="D23:D24"/>
     <mergeCell ref="C6:C24"/>
@@ -5785,14 +5791,16 @@
     <mergeCell ref="H16:H18"/>
     <mergeCell ref="E20:E21"/>
     <mergeCell ref="F20:F21"/>
-    <mergeCell ref="G20:G21"/>
-    <mergeCell ref="J20:J21"/>
-    <mergeCell ref="J23:J24"/>
-    <mergeCell ref="J16:J18"/>
-    <mergeCell ref="H7:H8"/>
-    <mergeCell ref="J7:J8"/>
-    <mergeCell ref="H11:H12"/>
-    <mergeCell ref="J11:J12"/>
+    <mergeCell ref="D7:D9"/>
+    <mergeCell ref="G7:G8"/>
+    <mergeCell ref="F7:F8"/>
+    <mergeCell ref="E7:E8"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="D10:D12"/>
+    <mergeCell ref="D13:D15"/>
+    <mergeCell ref="G11:G12"/>
+    <mergeCell ref="F11:F12"/>
+    <mergeCell ref="E11:E12"/>
   </mergeCells>
   <conditionalFormatting sqref="B1:E1">
     <cfRule type="expression" dxfId="48" priority="9">
@@ -5880,21 +5888,21 @@
       <c r="S1" s="59"/>
     </row>
     <row r="2" spans="1:19" ht="21.45" customHeight="1" thickBot="1">
-      <c r="A2" s="164"/>
-      <c r="B2" s="165"/>
-      <c r="C2" s="165"/>
-      <c r="D2" s="165"/>
-      <c r="E2" s="165"/>
-      <c r="F2" s="165"/>
-      <c r="G2" s="165"/>
-      <c r="H2" s="165"/>
+      <c r="A2" s="159"/>
+      <c r="B2" s="160"/>
+      <c r="C2" s="160"/>
+      <c r="D2" s="160"/>
+      <c r="E2" s="160"/>
+      <c r="F2" s="160"/>
+      <c r="G2" s="160"/>
+      <c r="H2" s="160"/>
       <c r="I2" s="53"/>
-      <c r="J2" s="164"/>
-      <c r="K2" s="164"/>
-      <c r="L2" s="167" t="s">
+      <c r="J2" s="159"/>
+      <c r="K2" s="159"/>
+      <c r="L2" s="163" t="s">
         <v>279</v>
       </c>
-      <c r="M2" s="168"/>
+      <c r="M2" s="164"/>
       <c r="N2" s="58" t="s">
         <v>275</v>
       </c>
@@ -5905,7 +5913,7 @@
         <v>274</v>
       </c>
       <c r="Q2" s="58" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="R2" s="58" t="s">
         <v>521</v>
@@ -5913,7 +5921,7 @@
       <c r="S2" s="59"/>
     </row>
     <row r="3" spans="1:19" ht="28.05" customHeight="1">
-      <c r="A3" s="164"/>
+      <c r="A3" s="159"/>
       <c r="B3" s="43" t="s">
         <v>148</v>
       </c>
@@ -5938,37 +5946,37 @@
       <c r="I3" s="56" t="s">
         <v>272</v>
       </c>
-      <c r="J3" s="164"/>
-      <c r="K3" s="164"/>
-      <c r="L3" s="158">
+      <c r="J3" s="159"/>
+      <c r="K3" s="159"/>
+      <c r="L3" s="153">
         <f>COUNTA(I4:I13)</f>
         <v>4</v>
       </c>
-      <c r="M3" s="169"/>
-      <c r="N3" s="172">
+      <c r="M3" s="165"/>
+      <c r="N3" s="168">
         <f>COUNTIF(I4:I12,"Yes")</f>
         <v>2</v>
       </c>
-      <c r="O3" s="151">
+      <c r="O3" s="171">
         <f>COUNTIF(I4:I12,"No")</f>
         <v>1</v>
       </c>
-      <c r="P3" s="154">
+      <c r="P3" s="174">
         <f>COUNTIF(I4:I12,"N/A")</f>
         <v>1</v>
       </c>
-      <c r="Q3" s="158">
+      <c r="Q3" s="153">
         <f>L3-P3</f>
         <v>3</v>
       </c>
-      <c r="R3" s="161">
+      <c r="R3" s="156">
         <f>N3/Q3</f>
         <v>0.66666666666666663</v>
       </c>
       <c r="S3" s="59"/>
     </row>
     <row r="4" spans="1:19" ht="73.95" customHeight="1">
-      <c r="A4" s="164"/>
+      <c r="A4" s="159"/>
       <c r="B4" s="140" t="s">
         <v>101</v>
       </c>
@@ -5987,60 +5995,60 @@
       <c r="G4" s="24" t="s">
         <v>229</v>
       </c>
-      <c r="H4" s="157" t="s">
+      <c r="H4" s="162" t="s">
         <v>262</v>
       </c>
       <c r="I4" s="145" t="s">
         <v>275</v>
       </c>
-      <c r="J4" s="164"/>
-      <c r="K4" s="164"/>
-      <c r="L4" s="159"/>
-      <c r="M4" s="170"/>
-      <c r="N4" s="173"/>
-      <c r="O4" s="152"/>
-      <c r="P4" s="155"/>
-      <c r="Q4" s="159"/>
-      <c r="R4" s="162"/>
+      <c r="J4" s="159"/>
+      <c r="K4" s="159"/>
+      <c r="L4" s="154"/>
+      <c r="M4" s="166"/>
+      <c r="N4" s="169"/>
+      <c r="O4" s="172"/>
+      <c r="P4" s="175"/>
+      <c r="Q4" s="154"/>
+      <c r="R4" s="157"/>
       <c r="S4" s="59"/>
     </row>
     <row r="5" spans="1:19" ht="78" customHeight="1" thickBot="1">
-      <c r="A5" s="164"/>
-      <c r="B5" s="142"/>
-      <c r="C5" s="142"/>
+      <c r="A5" s="159"/>
+      <c r="B5" s="141"/>
+      <c r="C5" s="141"/>
       <c r="D5" s="149"/>
       <c r="E5" s="149"/>
       <c r="F5" s="150"/>
       <c r="G5" s="24" t="s">
         <v>231</v>
       </c>
-      <c r="H5" s="157"/>
+      <c r="H5" s="162"/>
       <c r="I5" s="145"/>
-      <c r="J5" s="164"/>
-      <c r="K5" s="164"/>
-      <c r="L5" s="160"/>
-      <c r="M5" s="171"/>
-      <c r="N5" s="174"/>
-      <c r="O5" s="153"/>
-      <c r="P5" s="156"/>
-      <c r="Q5" s="160"/>
-      <c r="R5" s="163"/>
+      <c r="J5" s="159"/>
+      <c r="K5" s="159"/>
+      <c r="L5" s="155"/>
+      <c r="M5" s="167"/>
+      <c r="N5" s="170"/>
+      <c r="O5" s="173"/>
+      <c r="P5" s="176"/>
+      <c r="Q5" s="155"/>
+      <c r="R5" s="158"/>
       <c r="S5" s="59"/>
     </row>
     <row r="6" spans="1:19" ht="72.599999999999994" thickBot="1">
-      <c r="A6" s="164"/>
-      <c r="B6" s="142"/>
-      <c r="C6" s="142"/>
+      <c r="A6" s="159"/>
+      <c r="B6" s="141"/>
+      <c r="C6" s="141"/>
       <c r="D6" s="149"/>
       <c r="E6" s="149"/>
       <c r="F6" s="144"/>
       <c r="G6" s="24" t="s">
         <v>232</v>
       </c>
-      <c r="H6" s="157"/>
+      <c r="H6" s="162"/>
       <c r="I6" s="145"/>
-      <c r="J6" s="164"/>
-      <c r="K6" s="164"/>
+      <c r="J6" s="159"/>
+      <c r="K6" s="159"/>
       <c r="L6" s="59"/>
       <c r="M6" s="59"/>
       <c r="N6" s="59"/>
@@ -6051,9 +6059,9 @@
       <c r="S6" s="59"/>
     </row>
     <row r="7" spans="1:19" ht="109.05" customHeight="1" thickBot="1">
-      <c r="A7" s="164"/>
-      <c r="B7" s="142"/>
-      <c r="C7" s="142"/>
+      <c r="A7" s="159"/>
+      <c r="B7" s="141"/>
+      <c r="C7" s="141"/>
       <c r="D7" s="24" t="s">
         <v>234</v>
       </c>
@@ -6066,26 +6074,26 @@
       <c r="G7" s="24" t="s">
         <v>236</v>
       </c>
-      <c r="H7" s="157" t="s">
+      <c r="H7" s="162" t="s">
         <v>263</v>
       </c>
       <c r="I7" s="145" t="s">
         <v>274</v>
       </c>
-      <c r="J7" s="164"/>
-      <c r="K7" s="164"/>
+      <c r="J7" s="159"/>
+      <c r="K7" s="159"/>
       <c r="L7" s="92" t="s">
+        <v>611</v>
+      </c>
+      <c r="M7" s="126" t="s">
         <v>612</v>
       </c>
-      <c r="M7" s="193" t="s">
-        <v>613</v>
-      </c>
       <c r="N7" s="114"/>
     </row>
     <row r="8" spans="1:19" ht="102" customHeight="1">
-      <c r="A8" s="164"/>
-      <c r="B8" s="142"/>
-      <c r="C8" s="142"/>
+      <c r="A8" s="159"/>
+      <c r="B8" s="141"/>
+      <c r="C8" s="141"/>
       <c r="D8" s="24" t="s">
         <v>235</v>
       </c>
@@ -6098,16 +6106,16 @@
       <c r="G8" s="24" t="s">
         <v>238</v>
       </c>
-      <c r="H8" s="157"/>
+      <c r="H8" s="162"/>
       <c r="I8" s="145"/>
-      <c r="J8" s="164"/>
-      <c r="K8" s="164"/>
+      <c r="J8" s="159"/>
+      <c r="K8" s="159"/>
       <c r="N8" s="115"/>
     </row>
     <row r="9" spans="1:19" ht="252" customHeight="1">
-      <c r="A9" s="164"/>
-      <c r="B9" s="142"/>
-      <c r="C9" s="142"/>
+      <c r="A9" s="159"/>
+      <c r="B9" s="141"/>
+      <c r="C9" s="141"/>
       <c r="D9" s="24" t="s">
         <v>244</v>
       </c>
@@ -6120,19 +6128,19 @@
       <c r="G9" s="24" t="s">
         <v>246</v>
       </c>
-      <c r="H9" s="157" t="s">
+      <c r="H9" s="162" t="s">
         <v>265</v>
       </c>
       <c r="I9" s="145" t="s">
         <v>273</v>
       </c>
-      <c r="J9" s="164"/>
-      <c r="K9" s="164"/>
+      <c r="J9" s="159"/>
+      <c r="K9" s="159"/>
     </row>
     <row r="10" spans="1:19" ht="139.05000000000001" customHeight="1">
-      <c r="A10" s="164"/>
-      <c r="B10" s="142"/>
-      <c r="C10" s="142"/>
+      <c r="A10" s="159"/>
+      <c r="B10" s="141"/>
+      <c r="C10" s="141"/>
       <c r="D10" s="24" t="s">
         <v>248</v>
       </c>
@@ -6145,15 +6153,15 @@
       <c r="G10" s="24" t="s">
         <v>243</v>
       </c>
-      <c r="H10" s="157"/>
+      <c r="H10" s="162"/>
       <c r="I10" s="145"/>
-      <c r="J10" s="164"/>
-      <c r="K10" s="164"/>
+      <c r="J10" s="159"/>
+      <c r="K10" s="159"/>
     </row>
     <row r="11" spans="1:19" ht="64.95" customHeight="1">
-      <c r="A11" s="164"/>
-      <c r="B11" s="141"/>
-      <c r="C11" s="141"/>
+      <c r="A11" s="159"/>
+      <c r="B11" s="142"/>
+      <c r="C11" s="142"/>
       <c r="D11" s="24" t="s">
         <v>239</v>
       </c>
@@ -6172,37 +6180,43 @@
       <c r="I11" s="4" t="s">
         <v>275</v>
       </c>
-      <c r="J11" s="164"/>
-      <c r="K11" s="164"/>
+      <c r="J11" s="159"/>
+      <c r="K11" s="159"/>
     </row>
     <row r="12" spans="1:19">
-      <c r="A12" s="164"/>
-      <c r="B12" s="166"/>
-      <c r="C12" s="166"/>
-      <c r="D12" s="166"/>
-      <c r="E12" s="166"/>
-      <c r="F12" s="166"/>
-      <c r="G12" s="166"/>
-      <c r="H12" s="166"/>
+      <c r="A12" s="159"/>
+      <c r="B12" s="161"/>
+      <c r="C12" s="161"/>
+      <c r="D12" s="161"/>
+      <c r="E12" s="161"/>
+      <c r="F12" s="161"/>
+      <c r="G12" s="161"/>
+      <c r="H12" s="161"/>
       <c r="I12" s="53"/>
-      <c r="J12" s="164"/>
-      <c r="K12" s="164"/>
+      <c r="J12" s="159"/>
+      <c r="K12" s="159"/>
     </row>
     <row r="13" spans="1:19">
-      <c r="A13" s="164"/>
-      <c r="B13" s="164"/>
-      <c r="C13" s="164"/>
-      <c r="D13" s="164"/>
-      <c r="E13" s="164"/>
-      <c r="F13" s="164"/>
-      <c r="G13" s="164"/>
-      <c r="H13" s="164"/>
+      <c r="A13" s="159"/>
+      <c r="B13" s="159"/>
+      <c r="C13" s="159"/>
+      <c r="D13" s="159"/>
+      <c r="E13" s="159"/>
+      <c r="F13" s="159"/>
+      <c r="G13" s="159"/>
+      <c r="H13" s="159"/>
       <c r="I13" s="53"/>
-      <c r="J13" s="164"/>
-      <c r="K13" s="164"/>
+      <c r="J13" s="159"/>
+      <c r="K13" s="159"/>
     </row>
   </sheetData>
   <mergeCells count="22">
+    <mergeCell ref="I9:I10"/>
+    <mergeCell ref="O3:O5"/>
+    <mergeCell ref="P3:P5"/>
+    <mergeCell ref="F4:F6"/>
+    <mergeCell ref="H4:H6"/>
+    <mergeCell ref="H7:H8"/>
     <mergeCell ref="Q3:Q5"/>
     <mergeCell ref="R3:R5"/>
     <mergeCell ref="B4:B11"/>
@@ -6219,12 +6233,6 @@
     <mergeCell ref="J2:K13"/>
     <mergeCell ref="I4:I6"/>
     <mergeCell ref="I7:I8"/>
-    <mergeCell ref="I9:I10"/>
-    <mergeCell ref="O3:O5"/>
-    <mergeCell ref="P3:P5"/>
-    <mergeCell ref="F4:F6"/>
-    <mergeCell ref="H4:H6"/>
-    <mergeCell ref="H7:H8"/>
   </mergeCells>
   <conditionalFormatting sqref="H3:I3">
     <cfRule type="expression" dxfId="41" priority="5">
@@ -6318,10 +6326,10 @@
       <c r="L1" s="96" t="s">
         <v>590</v>
       </c>
-      <c r="M1" s="175" t="s">
+      <c r="M1" s="178" t="s">
         <v>588</v>
       </c>
-      <c r="N1" s="176"/>
+      <c r="N1" s="179"/>
       <c r="O1" s="95" t="s">
         <v>589</v>
       </c>
@@ -6381,10 +6389,10 @@
         <v>32</v>
       </c>
       <c r="T2" s="92" t="s">
-        <v>612</v>
-      </c>
-      <c r="U2" s="193" t="s">
-        <v>614</v>
+        <v>611</v>
+      </c>
+      <c r="U2" s="126" t="s">
+        <v>613</v>
       </c>
       <c r="V2" s="91"/>
       <c r="W2" s="91"/>
@@ -6697,7 +6705,7 @@
     <row r="10" spans="1:32" ht="82.8">
       <c r="A10" s="145"/>
       <c r="B10" s="145"/>
-      <c r="C10" s="178"/>
+      <c r="C10" s="177"/>
       <c r="D10" s="31" t="s">
         <v>13</v>
       </c>
@@ -6735,7 +6743,7 @@
     <row r="11" spans="1:32" ht="72">
       <c r="A11" s="145"/>
       <c r="B11" s="145"/>
-      <c r="C11" s="178"/>
+      <c r="C11" s="177"/>
       <c r="D11" s="31" t="s">
         <v>15</v>
       </c>
@@ -6889,7 +6897,7 @@
     <row r="15" spans="1:32" ht="82.8">
       <c r="A15" s="145"/>
       <c r="B15" s="145"/>
-      <c r="C15" s="178" t="s">
+      <c r="C15" s="177" t="s">
         <v>19</v>
       </c>
       <c r="D15" s="31" t="s">
@@ -6929,7 +6937,7 @@
     <row r="16" spans="1:32" ht="72">
       <c r="A16" s="145"/>
       <c r="B16" s="145"/>
-      <c r="C16" s="178"/>
+      <c r="C16" s="177"/>
       <c r="D16" s="30" t="s">
         <v>52</v>
       </c>
@@ -7660,7 +7668,7 @@
       <c r="A36" s="145"/>
       <c r="B36" s="145"/>
       <c r="C36" s="145"/>
-      <c r="D36" s="177" t="s">
+      <c r="D36" s="180" t="s">
         <v>247</v>
       </c>
       <c r="E36" s="145" t="s">
@@ -7681,7 +7689,7 @@
       <c r="A37" s="145"/>
       <c r="B37" s="145"/>
       <c r="C37" s="145"/>
-      <c r="D37" s="177"/>
+      <c r="D37" s="180"/>
       <c r="E37" s="145"/>
       <c r="F37" s="145"/>
       <c r="G37" s="145"/>
@@ -7694,6 +7702,17 @@
     </row>
   </sheetData>
   <mergeCells count="24">
+    <mergeCell ref="G31:G33"/>
+    <mergeCell ref="B32:B33"/>
+    <mergeCell ref="M1:N1"/>
+    <mergeCell ref="B34:B37"/>
+    <mergeCell ref="C35:C37"/>
+    <mergeCell ref="I36:I37"/>
+    <mergeCell ref="D36:D37"/>
+    <mergeCell ref="E36:E37"/>
+    <mergeCell ref="F36:F37"/>
+    <mergeCell ref="G36:G37"/>
+    <mergeCell ref="H36:H37"/>
     <mergeCell ref="A2:A37"/>
     <mergeCell ref="B2:B5"/>
     <mergeCell ref="B6:B7"/>
@@ -7707,17 +7726,6 @@
     <mergeCell ref="C27:C28"/>
     <mergeCell ref="B29:B31"/>
     <mergeCell ref="C29:C30"/>
-    <mergeCell ref="G31:G33"/>
-    <mergeCell ref="B32:B33"/>
-    <mergeCell ref="M1:N1"/>
-    <mergeCell ref="B34:B37"/>
-    <mergeCell ref="C35:C37"/>
-    <mergeCell ref="I36:I37"/>
-    <mergeCell ref="D36:D37"/>
-    <mergeCell ref="E36:E37"/>
-    <mergeCell ref="F36:F37"/>
-    <mergeCell ref="G36:G37"/>
-    <mergeCell ref="H36:H37"/>
   </mergeCells>
   <conditionalFormatting sqref="A1:D1">
     <cfRule type="expression" dxfId="35" priority="7">
@@ -7806,12 +7814,12 @@
       <c r="H2" s="50"/>
       <c r="I2" s="50"/>
       <c r="K2" s="50"/>
-      <c r="L2" s="167" t="s">
+      <c r="L2" s="163" t="s">
         <v>279</v>
       </c>
-      <c r="M2" s="168"/>
+      <c r="M2" s="164"/>
       <c r="N2" s="117" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="O2" s="58" t="s">
         <v>275</v>
@@ -7854,28 +7862,28 @@
         <v>272</v>
       </c>
       <c r="K3" s="50"/>
-      <c r="L3" s="158">
+      <c r="L3" s="153">
         <f>COUNTA(H4:H25)</f>
         <v>21</v>
       </c>
-      <c r="M3" s="169"/>
-      <c r="N3" s="182">
+      <c r="M3" s="165"/>
+      <c r="N3" s="181">
         <f>L3-Q3</f>
         <v>20</v>
       </c>
-      <c r="O3" s="172">
+      <c r="O3" s="168">
         <f>COUNTIF(J4:J21,"Yes")</f>
         <v>16</v>
       </c>
-      <c r="P3" s="151">
+      <c r="P3" s="171">
         <f>COUNTIF(J4:J21,"No")</f>
         <v>0</v>
       </c>
-      <c r="Q3" s="154">
+      <c r="Q3" s="174">
         <f>COUNTIF(J4:J21,"N/A")</f>
         <v>1</v>
       </c>
-      <c r="R3" s="161">
+      <c r="R3" s="156">
         <f>O3/N3</f>
         <v>0.8</v>
       </c>
@@ -7891,7 +7899,7 @@
       <c r="D4" s="145" t="s">
         <v>87</v>
       </c>
-      <c r="E4" s="179" t="s">
+      <c r="E4" s="184" t="s">
         <v>278</v>
       </c>
       <c r="F4" s="12" t="s">
@@ -7910,20 +7918,20 @@
         <v>274</v>
       </c>
       <c r="K4" s="50"/>
-      <c r="L4" s="159"/>
-      <c r="M4" s="170"/>
-      <c r="N4" s="183"/>
-      <c r="O4" s="173"/>
-      <c r="P4" s="152"/>
-      <c r="Q4" s="155"/>
-      <c r="R4" s="162"/>
+      <c r="L4" s="154"/>
+      <c r="M4" s="166"/>
+      <c r="N4" s="182"/>
+      <c r="O4" s="169"/>
+      <c r="P4" s="172"/>
+      <c r="Q4" s="175"/>
+      <c r="R4" s="157"/>
     </row>
     <row r="5" spans="1:18" ht="81" customHeight="1" thickBot="1">
       <c r="A5" s="50"/>
       <c r="B5" s="147"/>
-      <c r="C5" s="142"/>
+      <c r="C5" s="141"/>
       <c r="D5" s="145"/>
-      <c r="E5" s="179"/>
+      <c r="E5" s="184"/>
       <c r="F5" s="12" t="s">
         <v>90</v>
       </c>
@@ -7936,18 +7944,18 @@
       </c>
       <c r="J5" s="145"/>
       <c r="K5" s="50"/>
-      <c r="L5" s="160"/>
-      <c r="M5" s="171"/>
-      <c r="N5" s="184"/>
-      <c r="O5" s="174"/>
-      <c r="P5" s="153"/>
-      <c r="Q5" s="156"/>
-      <c r="R5" s="163"/>
+      <c r="L5" s="155"/>
+      <c r="M5" s="167"/>
+      <c r="N5" s="183"/>
+      <c r="O5" s="170"/>
+      <c r="P5" s="173"/>
+      <c r="Q5" s="176"/>
+      <c r="R5" s="158"/>
     </row>
     <row r="6" spans="1:18" ht="111" customHeight="1" thickBot="1">
       <c r="A6" s="50"/>
       <c r="B6" s="147"/>
-      <c r="C6" s="141"/>
+      <c r="C6" s="142"/>
       <c r="D6" s="2" t="s">
         <v>384</v>
       </c>
@@ -7986,13 +7994,13 @@
       <c r="D7" s="145" t="s">
         <v>216</v>
       </c>
-      <c r="E7" s="179" t="s">
+      <c r="E7" s="184" t="s">
         <v>546</v>
       </c>
-      <c r="F7" s="180" t="s">
+      <c r="F7" s="185" t="s">
         <v>547</v>
       </c>
-      <c r="G7" s="181" t="s">
+      <c r="G7" s="186" t="s">
         <v>197</v>
       </c>
       <c r="H7" s="24" t="s">
@@ -8006,10 +8014,10 @@
       </c>
       <c r="K7" s="50"/>
       <c r="L7" s="92" t="s">
+        <v>611</v>
+      </c>
+      <c r="M7" s="126" t="s">
         <v>612</v>
-      </c>
-      <c r="M7" s="193" t="s">
-        <v>613</v>
       </c>
       <c r="N7" s="50"/>
       <c r="O7" s="114"/>
@@ -8019,9 +8027,9 @@
       <c r="B8" s="147"/>
       <c r="C8" s="145"/>
       <c r="D8" s="145"/>
-      <c r="E8" s="179"/>
-      <c r="F8" s="180"/>
-      <c r="G8" s="181"/>
+      <c r="E8" s="184"/>
+      <c r="F8" s="185"/>
+      <c r="G8" s="186"/>
       <c r="H8" s="24" t="s">
         <v>320</v>
       </c>
@@ -8073,7 +8081,7 @@
     <row r="10" spans="1:18" ht="58.05" customHeight="1">
       <c r="A10" s="50"/>
       <c r="B10" s="147"/>
-      <c r="C10" s="178" t="s">
+      <c r="C10" s="177" t="s">
         <v>307</v>
       </c>
       <c r="D10" s="140" t="s">
@@ -8106,8 +8114,8 @@
     <row r="11" spans="1:18" ht="43.2">
       <c r="A11" s="50"/>
       <c r="B11" s="147"/>
-      <c r="C11" s="178"/>
-      <c r="D11" s="141"/>
+      <c r="C11" s="177"/>
+      <c r="D11" s="142"/>
       <c r="E11" s="2" t="s">
         <v>392</v>
       </c>
@@ -8138,7 +8146,7 @@
       <c r="C12" s="146" t="s">
         <v>308</v>
       </c>
-      <c r="D12" s="178" t="s">
+      <c r="D12" s="177" t="s">
         <v>440</v>
       </c>
       <c r="E12" s="2" t="s">
@@ -8168,7 +8176,7 @@
       <c r="A13" s="50"/>
       <c r="B13" s="147"/>
       <c r="C13" s="147"/>
-      <c r="D13" s="178"/>
+      <c r="D13" s="177"/>
       <c r="E13" s="2" t="s">
         <v>401</v>
       </c>
@@ -8297,7 +8305,7 @@
     </row>
     <row r="18" spans="2:10" ht="57.6">
       <c r="B18" s="147"/>
-      <c r="C18" s="141"/>
+      <c r="C18" s="142"/>
       <c r="D18" s="148"/>
       <c r="E18" s="72" t="s">
         <v>413</v>
@@ -8320,7 +8328,7 @@
     </row>
     <row r="19" spans="2:10" ht="42" customHeight="1">
       <c r="B19" s="147"/>
-      <c r="C19" s="178" t="s">
+      <c r="C19" s="177" t="s">
         <v>323</v>
       </c>
       <c r="D19" s="3" t="s">
@@ -8347,7 +8355,7 @@
     </row>
     <row r="20" spans="2:10" ht="39" customHeight="1">
       <c r="B20" s="147"/>
-      <c r="C20" s="178"/>
+      <c r="C20" s="177"/>
       <c r="D20" s="3" t="s">
         <v>445</v>
       </c>
@@ -8449,7 +8457,7 @@
     </row>
     <row r="24" spans="2:10" ht="43.2">
       <c r="B24" s="147"/>
-      <c r="C24" s="178" t="s">
+      <c r="C24" s="177" t="s">
         <v>333</v>
       </c>
       <c r="D24" s="3" t="s">
@@ -8476,7 +8484,7 @@
     </row>
     <row r="25" spans="2:10" ht="43.2">
       <c r="B25" s="148"/>
-      <c r="C25" s="178"/>
+      <c r="C25" s="177"/>
       <c r="D25" s="3" t="s">
         <v>447</v>
       </c>
@@ -8504,20 +8512,6 @@
     </row>
   </sheetData>
   <mergeCells count="30">
-    <mergeCell ref="R3:R5"/>
-    <mergeCell ref="N3:N5"/>
-    <mergeCell ref="L2:M2"/>
-    <mergeCell ref="O3:O5"/>
-    <mergeCell ref="P3:P5"/>
-    <mergeCell ref="Q3:Q5"/>
-    <mergeCell ref="J4:J5"/>
-    <mergeCell ref="L3:M5"/>
-    <mergeCell ref="E4:E5"/>
-    <mergeCell ref="H4:H5"/>
-    <mergeCell ref="D7:D8"/>
-    <mergeCell ref="E7:E8"/>
-    <mergeCell ref="F7:F8"/>
-    <mergeCell ref="G7:G8"/>
     <mergeCell ref="B4:B25"/>
     <mergeCell ref="D10:D11"/>
     <mergeCell ref="D12:D13"/>
@@ -8534,6 +8528,20 @@
     <mergeCell ref="C17:C18"/>
     <mergeCell ref="C19:C20"/>
     <mergeCell ref="C7:C8"/>
+    <mergeCell ref="J4:J5"/>
+    <mergeCell ref="L3:M5"/>
+    <mergeCell ref="E4:E5"/>
+    <mergeCell ref="H4:H5"/>
+    <mergeCell ref="D7:D8"/>
+    <mergeCell ref="E7:E8"/>
+    <mergeCell ref="F7:F8"/>
+    <mergeCell ref="G7:G8"/>
+    <mergeCell ref="R3:R5"/>
+    <mergeCell ref="N3:N5"/>
+    <mergeCell ref="L2:M2"/>
+    <mergeCell ref="O3:O5"/>
+    <mergeCell ref="P3:P5"/>
+    <mergeCell ref="Q3:Q5"/>
   </mergeCells>
   <conditionalFormatting sqref="B3:E3">
     <cfRule type="expression" dxfId="28" priority="11">
@@ -8613,12 +8621,12 @@
       <c r="I2" s="50"/>
       <c r="J2" s="50"/>
       <c r="K2" s="50"/>
-      <c r="L2" s="167" t="s">
+      <c r="L2" s="163" t="s">
         <v>279</v>
       </c>
-      <c r="M2" s="168"/>
+      <c r="M2" s="164"/>
       <c r="N2" s="117" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="O2" s="58" t="s">
         <v>275</v>
@@ -8663,28 +8671,28 @@
         <v>272</v>
       </c>
       <c r="K3" s="50"/>
-      <c r="L3" s="158">
+      <c r="L3" s="153">
         <f>COUNTA(H4:H25)</f>
         <v>11</v>
       </c>
-      <c r="M3" s="169"/>
-      <c r="N3" s="182">
+      <c r="M3" s="165"/>
+      <c r="N3" s="181">
         <f>L3-Q3</f>
         <v>8</v>
       </c>
-      <c r="O3" s="172">
+      <c r="O3" s="168">
         <f>COUNTIF(J4:J25,"Yes")</f>
         <v>4</v>
       </c>
-      <c r="P3" s="151">
+      <c r="P3" s="171">
         <f>COUNTIF(J4:J25,"No")</f>
         <v>4</v>
       </c>
-      <c r="Q3" s="154">
+      <c r="Q3" s="174">
         <f>COUNTIF(J4:J25,"N/A")</f>
         <v>3</v>
       </c>
-      <c r="R3" s="161">
+      <c r="R3" s="156">
         <f>O3/N3</f>
         <v>0.5</v>
       </c>
@@ -8697,7 +8705,7 @@
       <c r="C4" s="145" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="188" t="s">
+      <c r="D4" s="190" t="s">
         <v>343</v>
       </c>
       <c r="E4" s="8" t="s">
@@ -8709,35 +8717,35 @@
       <c r="G4" s="30" t="s">
         <v>152</v>
       </c>
-      <c r="H4" s="188" t="s">
+      <c r="H4" s="190" t="s">
         <v>346</v>
       </c>
-      <c r="I4" s="189" t="s">
+      <c r="I4" s="187" t="s">
         <v>525</v>
       </c>
       <c r="J4" s="145" t="s">
         <v>274</v>
       </c>
       <c r="K4" s="50"/>
-      <c r="L4" s="159"/>
-      <c r="M4" s="170"/>
-      <c r="N4" s="183"/>
-      <c r="O4" s="173"/>
-      <c r="P4" s="152"/>
-      <c r="Q4" s="155"/>
-      <c r="R4" s="162"/>
+      <c r="L4" s="154"/>
+      <c r="M4" s="166"/>
+      <c r="N4" s="182"/>
+      <c r="O4" s="169"/>
+      <c r="P4" s="172"/>
+      <c r="Q4" s="175"/>
+      <c r="R4" s="157"/>
       <c r="S4" s="92" t="s">
-        <v>612</v>
-      </c>
-      <c r="T4" s="193" t="s">
-        <v>614</v>
+        <v>611</v>
+      </c>
+      <c r="T4" s="126" t="s">
+        <v>613</v>
       </c>
     </row>
     <row r="5" spans="1:20" ht="169.05" customHeight="1" thickBot="1">
       <c r="A5" s="50"/>
       <c r="B5" s="145"/>
       <c r="C5" s="145"/>
-      <c r="D5" s="188"/>
+      <c r="D5" s="190"/>
       <c r="E5" s="8" t="s">
         <v>347</v>
       </c>
@@ -8747,23 +8755,23 @@
       <c r="G5" s="30" t="s">
         <v>154</v>
       </c>
-      <c r="H5" s="188"/>
-      <c r="I5" s="190"/>
+      <c r="H5" s="190"/>
+      <c r="I5" s="188"/>
       <c r="J5" s="145"/>
       <c r="K5" s="50"/>
-      <c r="L5" s="160"/>
-      <c r="M5" s="171"/>
-      <c r="N5" s="184"/>
-      <c r="O5" s="174"/>
-      <c r="P5" s="153"/>
-      <c r="Q5" s="156"/>
-      <c r="R5" s="163"/>
+      <c r="L5" s="155"/>
+      <c r="M5" s="167"/>
+      <c r="N5" s="183"/>
+      <c r="O5" s="170"/>
+      <c r="P5" s="173"/>
+      <c r="Q5" s="176"/>
+      <c r="R5" s="158"/>
     </row>
     <row r="6" spans="1:20" ht="141" customHeight="1">
       <c r="A6" s="50"/>
       <c r="B6" s="145"/>
       <c r="C6" s="145"/>
-      <c r="D6" s="188"/>
+      <c r="D6" s="190"/>
       <c r="E6" s="8" t="s">
         <v>349</v>
       </c>
@@ -8773,10 +8781,10 @@
       <c r="G6" s="30" t="s">
         <v>153</v>
       </c>
-      <c r="H6" s="188" t="s">
+      <c r="H6" s="190" t="s">
         <v>351</v>
       </c>
-      <c r="I6" s="189" t="s">
+      <c r="I6" s="187" t="s">
         <v>526</v>
       </c>
       <c r="J6" s="145" t="s">
@@ -8792,7 +8800,7 @@
       <c r="A7" s="50"/>
       <c r="B7" s="145"/>
       <c r="C7" s="145"/>
-      <c r="D7" s="188"/>
+      <c r="D7" s="190"/>
       <c r="E7" s="27" t="s">
         <v>352</v>
       </c>
@@ -8802,8 +8810,8 @@
       <c r="G7" s="30" t="s">
         <v>155</v>
       </c>
-      <c r="H7" s="188"/>
-      <c r="I7" s="190"/>
+      <c r="H7" s="190"/>
+      <c r="I7" s="188"/>
       <c r="J7" s="145"/>
       <c r="K7" s="50"/>
       <c r="L7" s="50"/>
@@ -8854,7 +8862,7 @@
         <v>157</v>
       </c>
       <c r="H9" s="149"/>
-      <c r="I9" s="141"/>
+      <c r="I9" s="142"/>
       <c r="J9" s="145"/>
       <c r="K9" s="50"/>
     </row>
@@ -8876,10 +8884,10 @@
       <c r="G10" s="30" t="s">
         <v>160</v>
       </c>
-      <c r="H10" s="188" t="s">
+      <c r="H10" s="190" t="s">
         <v>528</v>
       </c>
-      <c r="I10" s="189" t="s">
+      <c r="I10" s="187" t="s">
         <v>529</v>
       </c>
       <c r="J10" s="145" t="s">
@@ -8901,8 +8909,8 @@
       <c r="G11" s="30" t="s">
         <v>163</v>
       </c>
-      <c r="H11" s="188"/>
-      <c r="I11" s="190"/>
+      <c r="H11" s="190"/>
+      <c r="I11" s="188"/>
       <c r="J11" s="145"/>
       <c r="K11" s="50"/>
     </row>
@@ -8922,10 +8930,10 @@
       <c r="G12" s="30" t="s">
         <v>162</v>
       </c>
-      <c r="H12" s="188" t="s">
+      <c r="H12" s="190" t="s">
         <v>342</v>
       </c>
-      <c r="I12" s="189" t="s">
+      <c r="I12" s="187" t="s">
         <v>530</v>
       </c>
       <c r="J12" s="145" t="s">
@@ -8947,8 +8955,8 @@
       <c r="G13" s="30" t="s">
         <v>164</v>
       </c>
-      <c r="H13" s="188"/>
-      <c r="I13" s="191"/>
+      <c r="H13" s="190"/>
+      <c r="I13" s="192"/>
       <c r="J13" s="145"/>
       <c r="K13" s="50"/>
     </row>
@@ -8968,8 +8976,8 @@
       <c r="G14" s="30" t="s">
         <v>170</v>
       </c>
-      <c r="H14" s="188"/>
-      <c r="I14" s="190"/>
+      <c r="H14" s="190"/>
+      <c r="I14" s="188"/>
       <c r="J14" s="145"/>
       <c r="K14" s="50"/>
     </row>
@@ -8980,13 +8988,13 @@
       <c r="D15" s="145" t="s">
         <v>17</v>
       </c>
-      <c r="E15" s="185" t="s">
+      <c r="E15" s="193" t="s">
         <v>369</v>
       </c>
-      <c r="F15" s="186" t="s">
+      <c r="F15" s="191" t="s">
         <v>370</v>
       </c>
-      <c r="G15" s="187" t="s">
+      <c r="G15" s="194" t="s">
         <v>169</v>
       </c>
       <c r="H15" s="24" t="s">
@@ -9005,9 +9013,9 @@
       <c r="B16" s="145"/>
       <c r="C16" s="145"/>
       <c r="D16" s="145"/>
-      <c r="E16" s="185"/>
-      <c r="F16" s="186"/>
-      <c r="G16" s="187"/>
+      <c r="E16" s="193"/>
+      <c r="F16" s="191"/>
+      <c r="G16" s="194"/>
       <c r="H16" s="70" t="s">
         <v>532</v>
       </c>
@@ -9035,10 +9043,10 @@
       <c r="G17" s="30" t="s">
         <v>175</v>
       </c>
-      <c r="H17" s="188" t="s">
+      <c r="H17" s="190" t="s">
         <v>371</v>
       </c>
-      <c r="I17" s="189" t="s">
+      <c r="I17" s="187" t="s">
         <v>534</v>
       </c>
       <c r="J17" s="145" t="s">
@@ -9062,8 +9070,8 @@
       <c r="G18" s="30" t="s">
         <v>171</v>
       </c>
-      <c r="H18" s="188"/>
-      <c r="I18" s="190"/>
+      <c r="H18" s="190"/>
+      <c r="I18" s="188"/>
       <c r="J18" s="145"/>
       <c r="K18" s="50"/>
     </row>
@@ -9083,10 +9091,10 @@
       <c r="G19" s="30" t="s">
         <v>168</v>
       </c>
-      <c r="H19" s="192" t="s">
+      <c r="H19" s="189" t="s">
         <v>376</v>
       </c>
-      <c r="I19" s="189" t="s">
+      <c r="I19" s="187" t="s">
         <v>535</v>
       </c>
       <c r="J19" s="145" t="s">
@@ -9110,8 +9118,8 @@
       <c r="G20" s="30" t="s">
         <v>176</v>
       </c>
-      <c r="H20" s="192"/>
-      <c r="I20" s="191"/>
+      <c r="H20" s="189"/>
+      <c r="I20" s="192"/>
       <c r="J20" s="145"/>
       <c r="K20" s="51"/>
       <c r="L20" s="45"/>
@@ -9133,8 +9141,8 @@
       <c r="G21" s="30" t="s">
         <v>174</v>
       </c>
-      <c r="H21" s="192"/>
-      <c r="I21" s="190"/>
+      <c r="H21" s="189"/>
+      <c r="I21" s="188"/>
       <c r="J21" s="145"/>
       <c r="K21" s="50"/>
     </row>
@@ -9147,19 +9155,19 @@
       <c r="D22" s="145" t="s">
         <v>32</v>
       </c>
-      <c r="E22" s="185" t="s">
+      <c r="E22" s="193" t="s">
         <v>33</v>
       </c>
-      <c r="F22" s="186" t="s">
+      <c r="F22" s="191" t="s">
         <v>34</v>
       </c>
       <c r="G22" s="30" t="s">
         <v>177</v>
       </c>
-      <c r="H22" s="188" t="s">
+      <c r="H22" s="190" t="s">
         <v>341</v>
       </c>
-      <c r="I22" s="189" t="s">
+      <c r="I22" s="187" t="s">
         <v>536</v>
       </c>
       <c r="J22" s="145" t="s">
@@ -9172,13 +9180,13 @@
       <c r="B23" s="145"/>
       <c r="C23" s="145"/>
       <c r="D23" s="145"/>
-      <c r="E23" s="185"/>
-      <c r="F23" s="186"/>
+      <c r="E23" s="193"/>
+      <c r="F23" s="191"/>
       <c r="G23" s="30" t="s">
         <v>158</v>
       </c>
-      <c r="H23" s="188"/>
-      <c r="I23" s="191"/>
+      <c r="H23" s="190"/>
+      <c r="I23" s="192"/>
       <c r="J23" s="145"/>
       <c r="K23" s="50"/>
     </row>
@@ -9198,8 +9206,8 @@
       <c r="G24" s="30" t="s">
         <v>166</v>
       </c>
-      <c r="H24" s="188"/>
-      <c r="I24" s="190"/>
+      <c r="H24" s="190"/>
+      <c r="I24" s="188"/>
       <c r="J24" s="145"/>
       <c r="K24" s="50"/>
     </row>
@@ -9245,37 +9253,6 @@
     </row>
   </sheetData>
   <mergeCells count="47">
-    <mergeCell ref="O3:O5"/>
-    <mergeCell ref="N3:N5"/>
-    <mergeCell ref="R3:R5"/>
-    <mergeCell ref="I8:I9"/>
-    <mergeCell ref="I10:I11"/>
-    <mergeCell ref="C4:C9"/>
-    <mergeCell ref="H19:H21"/>
-    <mergeCell ref="H22:H24"/>
-    <mergeCell ref="D19:D21"/>
-    <mergeCell ref="F22:F23"/>
-    <mergeCell ref="C10:C21"/>
-    <mergeCell ref="D4:D7"/>
-    <mergeCell ref="D8:D9"/>
-    <mergeCell ref="J19:J21"/>
-    <mergeCell ref="J22:J24"/>
-    <mergeCell ref="D10:D11"/>
-    <mergeCell ref="H10:H11"/>
-    <mergeCell ref="D12:D13"/>
-    <mergeCell ref="H12:H14"/>
-    <mergeCell ref="I12:I14"/>
-    <mergeCell ref="I22:I24"/>
-    <mergeCell ref="I19:I21"/>
-    <mergeCell ref="I17:I18"/>
-    <mergeCell ref="L2:M2"/>
-    <mergeCell ref="L3:M5"/>
-    <mergeCell ref="H6:H7"/>
-    <mergeCell ref="H4:H5"/>
-    <mergeCell ref="J4:J5"/>
-    <mergeCell ref="J6:J7"/>
-    <mergeCell ref="I4:I5"/>
-    <mergeCell ref="I6:I7"/>
     <mergeCell ref="B4:B25"/>
     <mergeCell ref="C22:C25"/>
     <mergeCell ref="P3:P5"/>
@@ -9292,6 +9269,37 @@
     <mergeCell ref="J10:J11"/>
     <mergeCell ref="J12:J14"/>
     <mergeCell ref="J17:J18"/>
+    <mergeCell ref="L2:M2"/>
+    <mergeCell ref="L3:M5"/>
+    <mergeCell ref="H6:H7"/>
+    <mergeCell ref="H4:H5"/>
+    <mergeCell ref="J4:J5"/>
+    <mergeCell ref="J6:J7"/>
+    <mergeCell ref="I4:I5"/>
+    <mergeCell ref="I6:I7"/>
+    <mergeCell ref="J19:J21"/>
+    <mergeCell ref="J22:J24"/>
+    <mergeCell ref="D10:D11"/>
+    <mergeCell ref="H10:H11"/>
+    <mergeCell ref="D12:D13"/>
+    <mergeCell ref="H12:H14"/>
+    <mergeCell ref="I12:I14"/>
+    <mergeCell ref="I22:I24"/>
+    <mergeCell ref="I19:I21"/>
+    <mergeCell ref="I17:I18"/>
+    <mergeCell ref="C4:C9"/>
+    <mergeCell ref="H19:H21"/>
+    <mergeCell ref="H22:H24"/>
+    <mergeCell ref="D19:D21"/>
+    <mergeCell ref="F22:F23"/>
+    <mergeCell ref="C10:C21"/>
+    <mergeCell ref="D4:D7"/>
+    <mergeCell ref="D8:D9"/>
+    <mergeCell ref="O3:O5"/>
+    <mergeCell ref="N3:N5"/>
+    <mergeCell ref="R3:R5"/>
+    <mergeCell ref="I8:I9"/>
+    <mergeCell ref="I10:I11"/>
   </mergeCells>
   <conditionalFormatting sqref="B3:D3 E3:E4">
     <cfRule type="expression" dxfId="21" priority="11">
@@ -9404,12 +9412,12 @@
       <c r="K2" s="50"/>
       <c r="L2" s="50"/>
       <c r="M2" s="50"/>
-      <c r="N2" s="167" t="s">
+      <c r="N2" s="163" t="s">
         <v>279</v>
       </c>
-      <c r="O2" s="168"/>
+      <c r="O2" s="164"/>
       <c r="P2" s="117" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="Q2" s="58" t="s">
         <v>275</v>
@@ -9456,28 +9464,28 @@
       <c r="K3" s="6"/>
       <c r="L3" s="50"/>
       <c r="M3" s="50"/>
-      <c r="N3" s="158">
+      <c r="N3" s="153">
         <f>COUNTA(H4:H13)</f>
         <v>4</v>
       </c>
-      <c r="O3" s="169"/>
-      <c r="P3" s="182">
+      <c r="O3" s="165"/>
+      <c r="P3" s="181">
         <f>N3-S3</f>
         <v>3</v>
       </c>
-      <c r="Q3" s="172">
+      <c r="Q3" s="168">
         <f>COUNTIF(J4:J10,"Yes")</f>
         <v>2</v>
       </c>
-      <c r="R3" s="151">
+      <c r="R3" s="171">
         <f>COUNTIF(J4:J10,"No")</f>
         <v>0</v>
       </c>
-      <c r="S3" s="154">
+      <c r="S3" s="174">
         <f>COUNTIF(J4:J10,"N/A")</f>
         <v>1</v>
       </c>
-      <c r="T3" s="172">
+      <c r="T3" s="168">
         <f>Q3/P3</f>
         <v>0.66666666666666663</v>
       </c>
@@ -9514,13 +9522,13 @@
       <c r="K4" s="50"/>
       <c r="L4" s="50"/>
       <c r="M4" s="50"/>
-      <c r="N4" s="159"/>
-      <c r="O4" s="170"/>
-      <c r="P4" s="183"/>
-      <c r="Q4" s="173"/>
-      <c r="R4" s="152"/>
-      <c r="S4" s="155"/>
-      <c r="T4" s="173"/>
+      <c r="N4" s="154"/>
+      <c r="O4" s="166"/>
+      <c r="P4" s="182"/>
+      <c r="Q4" s="169"/>
+      <c r="R4" s="172"/>
+      <c r="S4" s="175"/>
+      <c r="T4" s="169"/>
     </row>
     <row r="5" spans="1:20" ht="82.95" customHeight="1" thickBot="1">
       <c r="A5" s="50"/>
@@ -9544,13 +9552,13 @@
       <c r="K5" s="50"/>
       <c r="L5" s="50"/>
       <c r="M5" s="50"/>
-      <c r="N5" s="160"/>
-      <c r="O5" s="171"/>
-      <c r="P5" s="184"/>
-      <c r="Q5" s="174"/>
-      <c r="R5" s="153"/>
-      <c r="S5" s="156"/>
-      <c r="T5" s="174"/>
+      <c r="N5" s="155"/>
+      <c r="O5" s="167"/>
+      <c r="P5" s="183"/>
+      <c r="Q5" s="170"/>
+      <c r="R5" s="173"/>
+      <c r="S5" s="176"/>
+      <c r="T5" s="170"/>
     </row>
     <row r="6" spans="1:20" ht="88.5" customHeight="1" thickBot="1">
       <c r="A6" s="50"/>
@@ -9581,10 +9589,10 @@
       <c r="L6" s="50"/>
       <c r="M6" s="50"/>
       <c r="N6" s="92" t="s">
+        <v>611</v>
+      </c>
+      <c r="O6" s="126" t="s">
         <v>612</v>
-      </c>
-      <c r="O6" s="193" t="s">
-        <v>613</v>
       </c>
       <c r="P6" s="57"/>
     </row>
@@ -9663,7 +9671,7 @@
       <c r="I9" s="24" t="s">
         <v>541</v>
       </c>
-      <c r="J9" s="142"/>
+      <c r="J9" s="141"/>
       <c r="K9" s="50"/>
       <c r="L9" s="50"/>
       <c r="M9" s="50"/>
@@ -9674,20 +9682,20 @@
       <c r="B10" s="145"/>
       <c r="C10" s="145"/>
       <c r="D10" s="145"/>
-      <c r="E10" s="180" t="s">
+      <c r="E10" s="185" t="s">
         <v>113</v>
       </c>
-      <c r="F10" s="180" t="s">
+      <c r="F10" s="185" t="s">
         <v>227</v>
       </c>
-      <c r="G10" s="181" t="s">
+      <c r="G10" s="186" t="s">
         <v>206</v>
       </c>
       <c r="H10" s="149"/>
       <c r="I10" s="24" t="s">
         <v>542</v>
       </c>
-      <c r="J10" s="141"/>
+      <c r="J10" s="142"/>
       <c r="K10" s="50"/>
       <c r="L10" s="50"/>
       <c r="M10" s="50"/>
@@ -9698,9 +9706,9 @@
       <c r="B11" s="145"/>
       <c r="C11" s="145"/>
       <c r="D11" s="145"/>
-      <c r="E11" s="180"/>
-      <c r="F11" s="180"/>
-      <c r="G11" s="181"/>
+      <c r="E11" s="185"/>
+      <c r="F11" s="185"/>
+      <c r="G11" s="186"/>
       <c r="H11" s="2" t="s">
         <v>280</v>
       </c>
@@ -9722,6 +9730,18 @@
     </row>
   </sheetData>
   <mergeCells count="21">
+    <mergeCell ref="G10:G11"/>
+    <mergeCell ref="F10:F11"/>
+    <mergeCell ref="P3:P5"/>
+    <mergeCell ref="N2:O2"/>
+    <mergeCell ref="N3:O5"/>
+    <mergeCell ref="J4:J5"/>
+    <mergeCell ref="B4:B11"/>
+    <mergeCell ref="D6:D7"/>
+    <mergeCell ref="E10:E11"/>
+    <mergeCell ref="D8:D11"/>
+    <mergeCell ref="C4:C11"/>
+    <mergeCell ref="D4:D5"/>
     <mergeCell ref="T3:T5"/>
     <mergeCell ref="H8:H10"/>
     <mergeCell ref="H4:H5"/>
@@ -9731,18 +9751,6 @@
     <mergeCell ref="J8:J10"/>
     <mergeCell ref="Q3:Q5"/>
     <mergeCell ref="R3:R5"/>
-    <mergeCell ref="B4:B11"/>
-    <mergeCell ref="D6:D7"/>
-    <mergeCell ref="E10:E11"/>
-    <mergeCell ref="D8:D11"/>
-    <mergeCell ref="C4:C11"/>
-    <mergeCell ref="D4:D5"/>
-    <mergeCell ref="G10:G11"/>
-    <mergeCell ref="F10:F11"/>
-    <mergeCell ref="P3:P5"/>
-    <mergeCell ref="N2:O2"/>
-    <mergeCell ref="N3:O5"/>
-    <mergeCell ref="J4:J5"/>
   </mergeCells>
   <conditionalFormatting sqref="B3:E3">
     <cfRule type="expression" dxfId="6" priority="9">
@@ -9802,10 +9810,10 @@
         <v>148</v>
       </c>
       <c r="B1" s="120" t="s">
+        <v>608</v>
+      </c>
+      <c r="C1" s="120" t="s">
         <v>609</v>
-      </c>
-      <c r="C1" s="120" t="s">
-        <v>610</v>
       </c>
       <c r="D1" s="120" t="s">
         <v>275</v>
@@ -9817,13 +9825,13 @@
         <v>274</v>
       </c>
       <c r="G1" s="120" t="s">
+        <v>610</v>
+      </c>
+      <c r="H1" s="120" t="s">
+        <v>602</v>
+      </c>
+      <c r="I1" s="120" t="s">
         <v>611</v>
-      </c>
-      <c r="H1" s="120" t="s">
-        <v>603</v>
-      </c>
-      <c r="I1" s="120" t="s">
-        <v>612</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="14.55" customHeight="1">
@@ -9858,7 +9866,7 @@
         <f>PONDERATION!$L$20</f>
         <v>6</v>
       </c>
-      <c r="I2" s="194" t="str">
+      <c r="I2" s="127" t="str">
         <f>'Questionnaire Domain Forensics'!$O$6</f>
         <v>Oumayma</v>
       </c>
@@ -9895,7 +9903,7 @@
         <f>PONDERATION!$L$19</f>
         <v>23</v>
       </c>
-      <c r="I3" s="194" t="str">
+      <c r="I3" s="127" t="str">
         <f>'Question Continuité d’activité'!$T$4</f>
         <v>Dhia</v>
       </c>
@@ -9932,7 +9940,7 @@
         <f>PONDERATION!$L$18</f>
         <v>20</v>
       </c>
-      <c r="I4" s="194" t="str">
+      <c r="I4" s="127" t="str">
         <f>'Questionnaire Gestion de crise'!$M$7</f>
         <v>Oumayma</v>
       </c>
@@ -9969,7 +9977,7 @@
         <f>PONDERATION!$L$17</f>
         <v>18.5</v>
       </c>
-      <c r="I5" s="194" t="str">
+      <c r="I5" s="127" t="str">
         <f>'Questionnaire Gestion Incidents'!$N$5</f>
         <v>Oumayma</v>
       </c>
@@ -10006,55 +10014,79 @@
         <f>PONDERATION!$L$21</f>
         <v>6</v>
       </c>
-      <c r="I6" s="194" t="str">
+      <c r="I6" s="127" t="str">
         <f>'Questionnaire Confirmitee'!$M$7</f>
         <v>Oumayma</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="14.55" customHeight="1">
-      <c r="A7" s="120" t="s">
+      <c r="A7" s="195" t="s">
         <v>594</v>
       </c>
-      <c r="B7" s="123">
+      <c r="B7" s="196">
         <f>'Questionnaire Gouvernance '!$Q$2</f>
         <v>35</v>
       </c>
-      <c r="C7" s="123">
+      <c r="C7" s="196">
         <f>'Questionnaire Gouvernance '!$S$2</f>
         <v>32</v>
       </c>
-      <c r="D7" s="123">
+      <c r="D7" s="196">
         <f>'Questionnaire Gouvernance '!$O$2</f>
         <v>20</v>
       </c>
-      <c r="E7" s="123">
+      <c r="E7" s="196">
         <f>'Questionnaire Gouvernance '!$O$3</f>
         <v>12</v>
       </c>
-      <c r="F7" s="123">
+      <c r="F7" s="196">
         <f>'Questionnaire Gouvernance '!$O$4</f>
         <v>3</v>
       </c>
-      <c r="G7" s="122">
+      <c r="G7" s="197">
         <f>'Questionnaire Gouvernance '!$L$2</f>
         <v>0.625</v>
       </c>
-      <c r="H7" s="125">
+      <c r="H7" s="198">
         <f>PONDERATION!$L$16</f>
         <v>26.5</v>
       </c>
-      <c r="I7" s="194" t="str">
+      <c r="I7" s="127" t="str">
         <f>'Questionnaire Gouvernance '!$U$2</f>
         <v>Dhia</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="15" customHeight="1">
-      <c r="F8" s="120" t="s">
-        <v>600</v>
+      <c r="A8" s="199" t="s">
+        <v>272</v>
+      </c>
+      <c r="B8" s="18">
+        <f>SUM(B2:B7)</f>
+        <v>92</v>
+      </c>
+      <c r="C8" s="18">
+        <f>SUM(C2:C7)</f>
+        <v>82</v>
+      </c>
+      <c r="D8" s="18">
+        <f t="shared" ref="D8:F8" si="0">SUM(D2:D7)</f>
+        <v>58</v>
+      </c>
+      <c r="E8" s="18">
+        <f t="shared" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="F8" s="18">
+        <f t="shared" si="0"/>
+        <v>10</v>
       </c>
       <c r="G8" s="18">
         <f>G2*H2+G3*H3+G4*H4+G5*H5+G6*H6+G7*H7</f>
         <v>68.25</v>
+      </c>
+      <c r="H8" s="18">
+        <f>SUM(H2:H7)</f>
+        <v>100</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -10067,19 +10099,19 @@
     </row>
     <row r="11" spans="1:9" ht="21">
       <c r="A11" s="113" t="s">
+        <v>603</v>
+      </c>
+      <c r="B11" s="113" t="s">
+        <v>607</v>
+      </c>
+      <c r="C11" s="113" t="s">
         <v>604</v>
       </c>
-      <c r="B11" s="113" t="s">
-        <v>608</v>
-      </c>
-      <c r="C11" s="113" t="s">
+      <c r="D11" s="113" t="s">
         <v>605</v>
       </c>
-      <c r="D11" s="113" t="s">
+      <c r="E11" s="113" t="s">
         <v>606</v>
-      </c>
-      <c r="E11" s="113" t="s">
-        <v>607</v>
       </c>
       <c r="F11" s="119"/>
     </row>

--- a/Data/LIVRABLE.xlsx
+++ b/Data/LIVRABLE.xlsx
@@ -2554,7 +2554,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="200">
+  <cellXfs count="201">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -3125,6 +3125,7 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -10080,7 +10081,7 @@
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="G8" s="18">
+      <c r="G8" s="200">
         <f>G2*H2+G3*H3+G4*H4+G5*H5+G6*H6+G7*H7</f>
         <v>68.25</v>
       </c>

--- a/Data/LIVRABLE.xlsx
+++ b/Data/LIVRABLE.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="6" rupBuild="4505"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="19416" windowHeight="10296" tabRatio="876" firstSheet="2" activeTab="7"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="19416" windowHeight="10296" tabRatio="876" firstSheet="2" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="PONDERATION" sheetId="10" r:id="rId1"/>
@@ -2218,7 +2218,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="25">
+  <borders count="26">
     <border>
       <left/>
       <right/>
@@ -2550,11 +2550,24 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="201">
+  <cellXfs count="204">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2770,9 +2783,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="9" fontId="6" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection hidden="1"/>
@@ -2913,205 +2923,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="10" fillId="8" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="10" fillId="8" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="10" fillId="8" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="11" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="11" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="11" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
@@ -3126,11 +2938,323 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="10" fillId="8" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="10" fillId="8" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="10" fillId="8" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="16" fillId="11" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="12" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="49">
+  <dxfs count="53">
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <color theme="2" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i/>
+        <u val="double"/>
+        <color theme="2" tint="-0.499984740745262"/>
+      </font>
+      <border>
+        <left style="thin">
+          <color theme="1"/>
+        </left>
+        <right style="thin">
+          <color theme="1"/>
+        </right>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+        <bottom style="thin">
+          <color theme="1"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <color theme="2" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i/>
+        <u val="double"/>
+        <color theme="2" tint="-0.499984740745262"/>
+      </font>
+      <border>
+        <left style="thin">
+          <color theme="1"/>
+        </left>
+        <right style="thin">
+          <color theme="1"/>
+        </right>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+        <bottom style="thin">
+          <color theme="1"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF006100"/>
@@ -3221,57 +3345,6 @@
         <b/>
         <i val="0"/>
       </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <color theme="2" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i/>
-        <u val="double"/>
-        <color theme="2" tint="-0.499984740745262"/>
-      </font>
-      <border>
-        <left style="thin">
-          <color theme="1"/>
-        </left>
-        <right style="thin">
-          <color theme="1"/>
-        </right>
-        <top style="thin">
-          <color theme="1"/>
-        </top>
-        <bottom style="thin">
-          <color theme="1"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
     </dxf>
     <dxf>
       <font>
@@ -4058,7 +4131,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -4082,8 +4155,8 @@
     <col min="15" max="15" width="13.44140625" customWidth="1"/>
     <col min="16" max="16" width="14.77734375" customWidth="1"/>
     <col min="18" max="18" width="6.77734375" customWidth="1"/>
-    <col min="20" max="20" width="11.44140625" style="97"/>
-    <col min="21" max="21" width="11.44140625" style="94"/>
+    <col min="20" max="20" width="11.44140625" style="96"/>
+    <col min="21" max="21" width="11.44140625" style="93"/>
     <col min="28" max="28" width="11.44140625" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4107,40 +4180,40 @@
       <c r="Q1" s="50"/>
       <c r="R1" s="50"/>
       <c r="S1" s="50"/>
-      <c r="T1" s="99" t="s">
+      <c r="T1" s="98" t="s">
         <v>592</v>
       </c>
-      <c r="U1" s="99" t="s">
+      <c r="U1" s="98" t="s">
         <v>593</v>
       </c>
-      <c r="V1" s="99" t="s">
+      <c r="V1" s="98" t="s">
         <v>592</v>
       </c>
-      <c r="W1" s="99" t="s">
+      <c r="W1" s="98" t="s">
         <v>593</v>
       </c>
-      <c r="X1" s="99" t="s">
+      <c r="X1" s="98" t="s">
         <v>592</v>
       </c>
-      <c r="Y1" s="99" t="s">
+      <c r="Y1" s="98" t="s">
         <v>593</v>
       </c>
-      <c r="Z1" s="99" t="s">
+      <c r="Z1" s="98" t="s">
         <v>592</v>
       </c>
-      <c r="AA1" s="99" t="s">
+      <c r="AA1" s="98" t="s">
         <v>593</v>
       </c>
-      <c r="AB1" s="99" t="s">
+      <c r="AB1" s="98" t="s">
         <v>592</v>
       </c>
-      <c r="AC1" s="99" t="s">
+      <c r="AC1" s="98" t="s">
         <v>593</v>
       </c>
-      <c r="AD1" s="99" t="s">
+      <c r="AD1" s="98" t="s">
         <v>592</v>
       </c>
-      <c r="AE1" s="99" t="s">
+      <c r="AE1" s="98" t="s">
         <v>593</v>
       </c>
     </row>
@@ -4162,60 +4235,60 @@
       <c r="P2" s="5"/>
       <c r="Q2" s="5"/>
       <c r="R2" s="5"/>
-      <c r="T2" s="99" t="s">
+      <c r="T2" s="98" t="s">
         <v>135</v>
       </c>
-      <c r="U2" s="81">
+      <c r="U2" s="80">
         <v>23</v>
       </c>
-      <c r="V2" s="99" t="s">
+      <c r="V2" s="98" t="s">
         <v>136</v>
       </c>
-      <c r="W2" s="81">
+      <c r="W2" s="80">
         <v>12</v>
       </c>
-      <c r="X2" s="99" t="s">
+      <c r="X2" s="98" t="s">
         <v>137</v>
       </c>
-      <c r="Y2" s="81">
+      <c r="Y2" s="80">
         <v>35</v>
       </c>
-      <c r="Z2" s="99" t="s">
+      <c r="Z2" s="98" t="s">
         <v>138</v>
       </c>
-      <c r="AA2" s="81">
+      <c r="AA2" s="80">
         <v>23</v>
       </c>
-      <c r="AB2" s="99" t="s">
+      <c r="AB2" s="98" t="s">
         <v>139</v>
       </c>
-      <c r="AC2" s="81">
+      <c r="AC2" s="80">
         <v>3</v>
       </c>
-      <c r="AD2" s="99" t="s">
+      <c r="AD2" s="98" t="s">
         <v>219</v>
       </c>
-      <c r="AE2" s="81">
+      <c r="AE2" s="80">
         <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:31" ht="28.8">
       <c r="A3" s="50"/>
       <c r="B3" s="5"/>
-      <c r="C3" s="133" t="s">
+      <c r="C3" s="139" t="s">
         <v>133</v>
       </c>
-      <c r="D3" s="135"/>
-      <c r="E3" s="135"/>
-      <c r="F3" s="135"/>
-      <c r="G3" s="135"/>
-      <c r="H3" s="135"/>
-      <c r="I3" s="134"/>
+      <c r="D3" s="141"/>
+      <c r="E3" s="141"/>
+      <c r="F3" s="141"/>
+      <c r="G3" s="141"/>
+      <c r="H3" s="141"/>
+      <c r="I3" s="140"/>
       <c r="J3" s="40"/>
-      <c r="K3" s="133" t="s">
+      <c r="K3" s="139" t="s">
         <v>134</v>
       </c>
-      <c r="L3" s="134"/>
+      <c r="L3" s="140"/>
       <c r="M3" s="40"/>
       <c r="N3" s="38" t="s">
         <v>148</v>
@@ -4254,10 +4327,10 @@
         <v>219</v>
       </c>
       <c r="J4" s="19"/>
-      <c r="K4" s="131" t="s">
+      <c r="K4" s="137" t="s">
         <v>140</v>
       </c>
-      <c r="L4" s="132"/>
+      <c r="L4" s="138"/>
       <c r="M4" s="5"/>
       <c r="N4" s="62" t="s">
         <v>135</v>
@@ -4300,10 +4373,10 @@
         <v>4</v>
       </c>
       <c r="J5" s="20"/>
-      <c r="K5" s="131" t="s">
+      <c r="K5" s="137" t="s">
         <v>141</v>
       </c>
-      <c r="L5" s="132"/>
+      <c r="L5" s="138"/>
       <c r="M5" s="5"/>
       <c r="N5" s="62" t="s">
         <v>136</v>
@@ -4346,10 +4419,10 @@
         <v>3</v>
       </c>
       <c r="J6" s="20"/>
-      <c r="K6" s="131" t="s">
+      <c r="K6" s="137" t="s">
         <v>142</v>
       </c>
-      <c r="L6" s="132"/>
+      <c r="L6" s="138"/>
       <c r="M6" s="5"/>
       <c r="N6" s="62" t="s">
         <v>137</v>
@@ -4392,10 +4465,10 @@
         <v>6</v>
       </c>
       <c r="J7" s="20"/>
-      <c r="K7" s="131" t="s">
+      <c r="K7" s="137" t="s">
         <v>143</v>
       </c>
-      <c r="L7" s="132"/>
+      <c r="L7" s="138"/>
       <c r="M7" s="5"/>
       <c r="N7" s="62" t="s">
         <v>138</v>
@@ -4412,8 +4485,8 @@
       </c>
       <c r="R7" s="5"/>
       <c r="S7" s="50"/>
-      <c r="T7" s="100"/>
-      <c r="U7" s="101"/>
+      <c r="T7" s="99"/>
+      <c r="U7" s="100"/>
     </row>
     <row r="8" spans="1:31">
       <c r="A8" s="50"/>
@@ -4440,10 +4513,10 @@
         <v>5</v>
       </c>
       <c r="J8" s="20"/>
-      <c r="K8" s="131" t="s">
+      <c r="K8" s="137" t="s">
         <v>144</v>
       </c>
-      <c r="L8" s="132"/>
+      <c r="L8" s="138"/>
       <c r="M8" s="5"/>
       <c r="N8" s="62" t="s">
         <v>139</v>
@@ -4486,10 +4559,10 @@
         <v>0.66666666666666663</v>
       </c>
       <c r="J9" s="20"/>
-      <c r="K9" s="131" t="s">
+      <c r="K9" s="137" t="s">
         <v>145</v>
       </c>
-      <c r="L9" s="132"/>
+      <c r="L9" s="138"/>
       <c r="M9" s="5"/>
       <c r="N9" s="62" t="s">
         <v>219</v>
@@ -4597,15 +4670,15 @@
     <row r="12" spans="1:31">
       <c r="A12" s="50"/>
       <c r="B12" s="5"/>
-      <c r="C12" s="136"/>
-      <c r="D12" s="136"/>
-      <c r="E12" s="136"/>
-      <c r="F12" s="136"/>
-      <c r="G12" s="136"/>
-      <c r="H12" s="136"/>
-      <c r="I12" s="136"/>
-      <c r="J12" s="136"/>
-      <c r="K12" s="136"/>
+      <c r="C12" s="142"/>
+      <c r="D12" s="142"/>
+      <c r="E12" s="142"/>
+      <c r="F12" s="142"/>
+      <c r="G12" s="142"/>
+      <c r="H12" s="142"/>
+      <c r="I12" s="142"/>
+      <c r="J12" s="142"/>
+      <c r="K12" s="142"/>
       <c r="L12" s="5"/>
       <c r="M12" s="22"/>
       <c r="S12" s="50"/>
@@ -4613,37 +4686,37 @@
     <row r="13" spans="1:31" ht="14.55" customHeight="1">
       <c r="A13" s="50"/>
       <c r="B13" s="5"/>
-      <c r="C13" s="137" t="s">
+      <c r="C13" s="143" t="s">
         <v>147</v>
       </c>
-      <c r="D13" s="138"/>
-      <c r="E13" s="138"/>
-      <c r="F13" s="138"/>
-      <c r="G13" s="138"/>
-      <c r="H13" s="138"/>
-      <c r="I13" s="138"/>
-      <c r="J13" s="138"/>
-      <c r="K13" s="138"/>
-      <c r="L13" s="139"/>
+      <c r="D13" s="144"/>
+      <c r="E13" s="144"/>
+      <c r="F13" s="144"/>
+      <c r="G13" s="144"/>
+      <c r="H13" s="144"/>
+      <c r="I13" s="144"/>
+      <c r="J13" s="144"/>
+      <c r="K13" s="144"/>
+      <c r="L13" s="145"/>
       <c r="M13" s="22"/>
       <c r="S13" s="50"/>
     </row>
     <row r="14" spans="1:31" ht="15.6">
       <c r="A14" s="50"/>
       <c r="B14" s="5"/>
-      <c r="C14" s="128" t="s">
+      <c r="C14" s="134" t="s">
         <v>148</v>
       </c>
-      <c r="D14" s="129"/>
-      <c r="E14" s="129"/>
-      <c r="F14" s="129"/>
-      <c r="G14" s="129"/>
-      <c r="H14" s="129"/>
-      <c r="I14" s="130"/>
-      <c r="J14" s="128" t="s">
+      <c r="D14" s="135"/>
+      <c r="E14" s="135"/>
+      <c r="F14" s="135"/>
+      <c r="G14" s="135"/>
+      <c r="H14" s="135"/>
+      <c r="I14" s="136"/>
+      <c r="J14" s="134" t="s">
         <v>149</v>
       </c>
-      <c r="K14" s="130"/>
+      <c r="K14" s="136"/>
       <c r="L14" s="35" t="s">
         <v>217</v>
       </c>
@@ -5086,7 +5159,7 @@
     <col min="8" max="9" width="48.77734375" customWidth="1"/>
     <col min="10" max="10" width="18.21875" customWidth="1"/>
     <col min="12" max="12" width="33" customWidth="1"/>
-    <col min="13" max="13" width="19.5546875" style="97" customWidth="1"/>
+    <col min="13" max="13" width="19.5546875" style="96" customWidth="1"/>
     <col min="14" max="14" width="41.88671875" customWidth="1"/>
     <col min="15" max="15" width="21.5546875" customWidth="1"/>
     <col min="16" max="17" width="27.77734375" customWidth="1"/>
@@ -5123,22 +5196,22 @@
         <v>272</v>
       </c>
       <c r="K1" s="50"/>
-      <c r="L1" s="96" t="s">
+      <c r="L1" s="95" t="s">
         <v>590</v>
       </c>
-      <c r="M1" s="95" t="s">
+      <c r="M1" s="94" t="s">
         <v>588</v>
       </c>
-      <c r="N1" s="95" t="s">
+      <c r="N1" s="94" t="s">
         <v>589</v>
       </c>
     </row>
     <row r="2" spans="1:22" ht="97.5" customHeight="1" thickBot="1">
       <c r="A2" s="50"/>
-      <c r="B2" s="140" t="s">
+      <c r="B2" s="148" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="145" t="s">
+      <c r="C2" s="153" t="s">
         <v>38</v>
       </c>
       <c r="D2" s="4" t="s">
@@ -5163,36 +5236,36 @@
         <v>274</v>
       </c>
       <c r="K2" s="50"/>
-      <c r="L2" s="103">
+      <c r="L2" s="102">
         <f>N2/R2</f>
         <v>0.875</v>
       </c>
-      <c r="M2" s="96" t="s">
+      <c r="M2" s="95" t="s">
         <v>275</v>
       </c>
-      <c r="N2" s="106">
+      <c r="N2" s="105">
         <f>COUNTIF(J2:J24,"Yes")</f>
         <v>14</v>
       </c>
-      <c r="O2" s="102" t="s">
+      <c r="O2" s="101" t="s">
         <v>279</v>
       </c>
-      <c r="P2" s="104">
+      <c r="P2" s="103">
         <f>COUNTA(H2:H24)</f>
         <v>17</v>
       </c>
-      <c r="Q2" s="95" t="s">
+      <c r="Q2" s="94" t="s">
         <v>591</v>
       </c>
-      <c r="R2" s="105">
+      <c r="R2" s="104">
         <f>P2-N4</f>
         <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:22" ht="81" customHeight="1">
       <c r="A3" s="50"/>
-      <c r="B3" s="141"/>
-      <c r="C3" s="145"/>
+      <c r="B3" s="150"/>
+      <c r="C3" s="153"/>
       <c r="D3" s="4" t="s">
         <v>43</v>
       </c>
@@ -5216,10 +5289,10 @@
       </c>
       <c r="K3" s="50"/>
       <c r="L3" s="50"/>
-      <c r="M3" s="109" t="s">
+      <c r="M3" s="108" t="s">
         <v>273</v>
       </c>
-      <c r="N3" s="107">
+      <c r="N3" s="106">
         <f>COUNTIF(J2:J24,"No")</f>
         <v>2</v>
       </c>
@@ -5228,7 +5301,7 @@
     </row>
     <row r="4" spans="1:22" ht="79.95" customHeight="1" thickBot="1">
       <c r="A4" s="50"/>
-      <c r="B4" s="141"/>
+      <c r="B4" s="150"/>
       <c r="C4" s="4" t="s">
         <v>55</v>
       </c>
@@ -5255,18 +5328,18 @@
       </c>
       <c r="K4" s="50"/>
       <c r="L4" s="50"/>
-      <c r="M4" s="110" t="s">
+      <c r="M4" s="109" t="s">
         <v>274</v>
       </c>
-      <c r="N4" s="108">
+      <c r="N4" s="107">
         <f>COUNTIF(J2:J24,"N/A")</f>
         <v>1</v>
       </c>
-      <c r="V4" s="79"/>
+      <c r="V4" s="78"/>
     </row>
     <row r="5" spans="1:22" ht="87" thickBot="1">
       <c r="A5" s="50"/>
-      <c r="B5" s="141"/>
+      <c r="B5" s="150"/>
       <c r="C5" s="3" t="s">
         <v>283</v>
       </c>
@@ -5293,17 +5366,17 @@
       </c>
       <c r="K5" s="50"/>
       <c r="L5" s="50"/>
-      <c r="M5" s="92" t="s">
+      <c r="M5" s="91" t="s">
         <v>611</v>
       </c>
-      <c r="N5" s="126" t="s">
+      <c r="N5" s="125" t="s">
         <v>612</v>
       </c>
     </row>
     <row r="6" spans="1:22" ht="91.05" customHeight="1">
       <c r="A6" s="50"/>
-      <c r="B6" s="141"/>
-      <c r="C6" s="146" t="s">
+      <c r="B6" s="150"/>
+      <c r="C6" s="154" t="s">
         <v>293</v>
       </c>
       <c r="D6" s="4" t="s">
@@ -5332,27 +5405,27 @@
     </row>
     <row r="7" spans="1:22" ht="43.5" customHeight="1">
       <c r="A7" s="50"/>
-      <c r="B7" s="141"/>
-      <c r="C7" s="147"/>
-      <c r="D7" s="140" t="s">
+      <c r="B7" s="150"/>
+      <c r="C7" s="155"/>
+      <c r="D7" s="148" t="s">
         <v>287</v>
       </c>
-      <c r="E7" s="143" t="s">
+      <c r="E7" s="151" t="s">
         <v>456</v>
       </c>
-      <c r="F7" s="143" t="s">
+      <c r="F7" s="151" t="s">
         <v>457</v>
       </c>
-      <c r="G7" s="143" t="s">
+      <c r="G7" s="151" t="s">
         <v>458</v>
       </c>
-      <c r="H7" s="143" t="s">
+      <c r="H7" s="151" t="s">
         <v>302</v>
       </c>
-      <c r="I7" s="82" t="s">
+      <c r="I7" s="81" t="s">
         <v>555</v>
       </c>
-      <c r="J7" s="140" t="s">
+      <c r="J7" s="148" t="s">
         <v>273</v>
       </c>
       <c r="K7" s="50"/>
@@ -5360,23 +5433,23 @@
     </row>
     <row r="8" spans="1:22" ht="43.5" customHeight="1">
       <c r="A8" s="50"/>
-      <c r="B8" s="141"/>
-      <c r="C8" s="147"/>
-      <c r="D8" s="141"/>
-      <c r="E8" s="144"/>
-      <c r="F8" s="144"/>
-      <c r="G8" s="144"/>
-      <c r="H8" s="144"/>
-      <c r="I8" s="83"/>
-      <c r="J8" s="142"/>
+      <c r="B8" s="150"/>
+      <c r="C8" s="155"/>
+      <c r="D8" s="150"/>
+      <c r="E8" s="152"/>
+      <c r="F8" s="152"/>
+      <c r="G8" s="152"/>
+      <c r="H8" s="152"/>
+      <c r="I8" s="82"/>
+      <c r="J8" s="149"/>
       <c r="K8" s="50"/>
       <c r="L8" s="50"/>
     </row>
     <row r="9" spans="1:22" ht="49.95" customHeight="1">
       <c r="A9" s="50"/>
-      <c r="B9" s="141"/>
-      <c r="C9" s="147"/>
-      <c r="D9" s="142"/>
+      <c r="B9" s="150"/>
+      <c r="C9" s="155"/>
+      <c r="D9" s="149"/>
       <c r="E9" s="24" t="s">
         <v>459</v>
       </c>
@@ -5400,9 +5473,9 @@
     </row>
     <row r="10" spans="1:22" ht="43.5" customHeight="1">
       <c r="A10" s="50"/>
-      <c r="B10" s="141"/>
-      <c r="C10" s="147"/>
-      <c r="D10" s="140" t="s">
+      <c r="B10" s="150"/>
+      <c r="C10" s="155"/>
+      <c r="D10" s="148" t="s">
         <v>288</v>
       </c>
       <c r="E10" s="24" t="s">
@@ -5428,25 +5501,25 @@
     </row>
     <row r="11" spans="1:22" ht="43.5" customHeight="1">
       <c r="A11" s="50"/>
-      <c r="B11" s="141"/>
-      <c r="C11" s="147"/>
-      <c r="D11" s="141"/>
-      <c r="E11" s="143" t="s">
+      <c r="B11" s="150"/>
+      <c r="C11" s="155"/>
+      <c r="D11" s="150"/>
+      <c r="E11" s="151" t="s">
         <v>465</v>
       </c>
-      <c r="F11" s="143" t="s">
+      <c r="F11" s="151" t="s">
         <v>466</v>
       </c>
-      <c r="G11" s="143" t="s">
+      <c r="G11" s="151" t="s">
         <v>467</v>
       </c>
-      <c r="H11" s="143" t="s">
+      <c r="H11" s="151" t="s">
         <v>295</v>
       </c>
-      <c r="I11" s="82" t="s">
+      <c r="I11" s="81" t="s">
         <v>558</v>
       </c>
-      <c r="J11" s="140" t="s">
+      <c r="J11" s="148" t="s">
         <v>275</v>
       </c>
       <c r="K11" s="50"/>
@@ -5454,23 +5527,23 @@
     </row>
     <row r="12" spans="1:22" ht="43.5" customHeight="1">
       <c r="A12" s="50"/>
-      <c r="B12" s="141"/>
-      <c r="C12" s="147"/>
-      <c r="D12" s="142"/>
-      <c r="E12" s="144"/>
-      <c r="F12" s="144"/>
-      <c r="G12" s="144"/>
-      <c r="H12" s="144"/>
-      <c r="I12" s="83"/>
-      <c r="J12" s="142"/>
+      <c r="B12" s="150"/>
+      <c r="C12" s="155"/>
+      <c r="D12" s="149"/>
+      <c r="E12" s="152"/>
+      <c r="F12" s="152"/>
+      <c r="G12" s="152"/>
+      <c r="H12" s="152"/>
+      <c r="I12" s="82"/>
+      <c r="J12" s="149"/>
       <c r="K12" s="50"/>
       <c r="L12" s="50"/>
     </row>
     <row r="13" spans="1:22" ht="43.2">
       <c r="A13" s="50"/>
-      <c r="B13" s="141"/>
-      <c r="C13" s="147"/>
-      <c r="D13" s="140" t="s">
+      <c r="B13" s="150"/>
+      <c r="C13" s="155"/>
+      <c r="D13" s="148" t="s">
         <v>289</v>
       </c>
       <c r="E13" s="42" t="s">
@@ -5496,9 +5569,9 @@
     </row>
     <row r="14" spans="1:22" ht="53.55" customHeight="1">
       <c r="A14" s="50"/>
-      <c r="B14" s="141"/>
-      <c r="C14" s="147"/>
-      <c r="D14" s="141"/>
+      <c r="B14" s="150"/>
+      <c r="C14" s="155"/>
+      <c r="D14" s="150"/>
       <c r="E14" s="42" t="s">
         <v>469</v>
       </c>
@@ -5522,9 +5595,9 @@
     </row>
     <row r="15" spans="1:22" ht="51" customHeight="1">
       <c r="A15" s="50"/>
-      <c r="B15" s="141"/>
-      <c r="C15" s="147"/>
-      <c r="D15" s="142"/>
+      <c r="B15" s="150"/>
+      <c r="C15" s="155"/>
+      <c r="D15" s="149"/>
       <c r="E15" s="42" t="s">
         <v>470</v>
       </c>
@@ -5548,27 +5621,27 @@
     </row>
     <row r="16" spans="1:22" ht="47.55" customHeight="1">
       <c r="A16" s="50"/>
-      <c r="B16" s="141"/>
-      <c r="C16" s="147"/>
-      <c r="D16" s="140" t="s">
+      <c r="B16" s="150"/>
+      <c r="C16" s="155"/>
+      <c r="D16" s="148" t="s">
         <v>290</v>
       </c>
-      <c r="E16" s="143" t="s">
+      <c r="E16" s="151" t="s">
         <v>477</v>
       </c>
-      <c r="F16" s="143" t="s">
+      <c r="F16" s="151" t="s">
         <v>478</v>
       </c>
-      <c r="G16" s="143" t="s">
+      <c r="G16" s="151" t="s">
         <v>479</v>
       </c>
-      <c r="H16" s="143" t="s">
+      <c r="H16" s="151" t="s">
         <v>301</v>
       </c>
-      <c r="I16" s="82" t="s">
+      <c r="I16" s="81" t="s">
         <v>562</v>
       </c>
-      <c r="J16" s="140" t="s">
+      <c r="J16" s="148" t="s">
         <v>275</v>
       </c>
       <c r="K16" s="50"/>
@@ -5576,37 +5649,37 @@
     </row>
     <row r="17" spans="1:12" ht="22.05" hidden="1" customHeight="1">
       <c r="A17" s="50"/>
-      <c r="B17" s="141"/>
-      <c r="C17" s="147"/>
-      <c r="D17" s="141"/>
-      <c r="E17" s="150"/>
-      <c r="F17" s="150"/>
-      <c r="G17" s="150"/>
-      <c r="H17" s="150"/>
-      <c r="I17" s="84"/>
-      <c r="J17" s="141"/>
+      <c r="B17" s="150"/>
+      <c r="C17" s="155"/>
+      <c r="D17" s="150"/>
+      <c r="E17" s="158"/>
+      <c r="F17" s="158"/>
+      <c r="G17" s="158"/>
+      <c r="H17" s="158"/>
+      <c r="I17" s="83"/>
+      <c r="J17" s="150"/>
       <c r="K17" s="50"/>
       <c r="L17" s="50"/>
     </row>
     <row r="18" spans="1:12">
       <c r="A18" s="50"/>
-      <c r="B18" s="141"/>
-      <c r="C18" s="147"/>
-      <c r="D18" s="142"/>
-      <c r="E18" s="144"/>
-      <c r="F18" s="144"/>
-      <c r="G18" s="144"/>
-      <c r="H18" s="144"/>
-      <c r="I18" s="83"/>
-      <c r="J18" s="142"/>
+      <c r="B18" s="150"/>
+      <c r="C18" s="155"/>
+      <c r="D18" s="149"/>
+      <c r="E18" s="152"/>
+      <c r="F18" s="152"/>
+      <c r="G18" s="152"/>
+      <c r="H18" s="152"/>
+      <c r="I18" s="82"/>
+      <c r="J18" s="149"/>
       <c r="K18" s="50"/>
       <c r="L18" s="50"/>
     </row>
     <row r="19" spans="1:12" ht="61.95" customHeight="1">
       <c r="A19" s="50"/>
-      <c r="B19" s="141"/>
-      <c r="C19" s="147"/>
-      <c r="D19" s="140" t="s">
+      <c r="B19" s="150"/>
+      <c r="C19" s="155"/>
+      <c r="D19" s="148" t="s">
         <v>291</v>
       </c>
       <c r="E19" s="24" t="s">
@@ -5632,23 +5705,23 @@
     </row>
     <row r="20" spans="1:12">
       <c r="A20" s="50"/>
-      <c r="B20" s="141"/>
-      <c r="C20" s="147"/>
-      <c r="D20" s="141"/>
-      <c r="E20" s="143" t="s">
+      <c r="B20" s="150"/>
+      <c r="C20" s="155"/>
+      <c r="D20" s="150"/>
+      <c r="E20" s="151" t="s">
         <v>481</v>
       </c>
-      <c r="F20" s="143" t="s">
+      <c r="F20" s="151" t="s">
         <v>485</v>
       </c>
-      <c r="G20" s="151" t="s">
+      <c r="G20" s="146" t="s">
         <v>489</v>
       </c>
-      <c r="H20" s="143" t="s">
+      <c r="H20" s="151" t="s">
         <v>300</v>
       </c>
-      <c r="I20" s="82"/>
-      <c r="J20" s="140" t="s">
+      <c r="I20" s="81"/>
+      <c r="J20" s="148" t="s">
         <v>275</v>
       </c>
       <c r="K20" s="50"/>
@@ -5656,25 +5729,25 @@
     </row>
     <row r="21" spans="1:12" ht="28.95" customHeight="1">
       <c r="A21" s="50"/>
-      <c r="B21" s="141"/>
-      <c r="C21" s="147"/>
-      <c r="D21" s="141"/>
-      <c r="E21" s="144"/>
-      <c r="F21" s="144"/>
-      <c r="G21" s="152"/>
-      <c r="H21" s="144"/>
-      <c r="I21" s="83" t="s">
+      <c r="B21" s="150"/>
+      <c r="C21" s="155"/>
+      <c r="D21" s="150"/>
+      <c r="E21" s="152"/>
+      <c r="F21" s="152"/>
+      <c r="G21" s="147"/>
+      <c r="H21" s="152"/>
+      <c r="I21" s="82" t="s">
         <v>564</v>
       </c>
-      <c r="J21" s="142"/>
+      <c r="J21" s="149"/>
       <c r="K21" s="50"/>
       <c r="L21" s="50"/>
     </row>
     <row r="22" spans="1:12" ht="39.450000000000003" customHeight="1">
       <c r="A22" s="50"/>
-      <c r="B22" s="141"/>
-      <c r="C22" s="147"/>
-      <c r="D22" s="141"/>
+      <c r="B22" s="150"/>
+      <c r="C22" s="155"/>
+      <c r="D22" s="150"/>
       <c r="E22" s="24" t="s">
         <v>482</v>
       </c>
@@ -5698,27 +5771,27 @@
     </row>
     <row r="23" spans="1:12" ht="42" customHeight="1">
       <c r="A23" s="50"/>
-      <c r="B23" s="141"/>
-      <c r="C23" s="147"/>
-      <c r="D23" s="145" t="s">
+      <c r="B23" s="150"/>
+      <c r="C23" s="155"/>
+      <c r="D23" s="153" t="s">
         <v>292</v>
       </c>
-      <c r="E23" s="143" t="s">
+      <c r="E23" s="151" t="s">
         <v>483</v>
       </c>
-      <c r="F23" s="149" t="s">
+      <c r="F23" s="157" t="s">
         <v>487</v>
       </c>
-      <c r="G23" s="143" t="s">
+      <c r="G23" s="151" t="s">
         <v>491</v>
       </c>
-      <c r="H23" s="143" t="s">
+      <c r="H23" s="151" t="s">
         <v>299</v>
       </c>
-      <c r="I23" s="82" t="s">
+      <c r="I23" s="81" t="s">
         <v>566</v>
       </c>
-      <c r="J23" s="140" t="s">
+      <c r="J23" s="148" t="s">
         <v>275</v>
       </c>
       <c r="K23" s="50"/>
@@ -5726,15 +5799,15 @@
     </row>
     <row r="24" spans="1:12" ht="28.95" customHeight="1">
       <c r="A24" s="50"/>
-      <c r="B24" s="142"/>
-      <c r="C24" s="148"/>
-      <c r="D24" s="145"/>
-      <c r="E24" s="144"/>
-      <c r="F24" s="149"/>
-      <c r="G24" s="144"/>
-      <c r="H24" s="144"/>
-      <c r="I24" s="83"/>
-      <c r="J24" s="142"/>
+      <c r="B24" s="149"/>
+      <c r="C24" s="156"/>
+      <c r="D24" s="153"/>
+      <c r="E24" s="152"/>
+      <c r="F24" s="157"/>
+      <c r="G24" s="152"/>
+      <c r="H24" s="152"/>
+      <c r="I24" s="82"/>
+      <c r="J24" s="149"/>
       <c r="K24" s="50"/>
       <c r="L24" s="50"/>
     </row>
@@ -5768,14 +5841,16 @@
     </row>
   </sheetData>
   <mergeCells count="34">
-    <mergeCell ref="G20:G21"/>
-    <mergeCell ref="J20:J21"/>
-    <mergeCell ref="J23:J24"/>
-    <mergeCell ref="J16:J18"/>
-    <mergeCell ref="H7:H8"/>
-    <mergeCell ref="J7:J8"/>
-    <mergeCell ref="H11:H12"/>
-    <mergeCell ref="J11:J12"/>
+    <mergeCell ref="D10:D12"/>
+    <mergeCell ref="D13:D15"/>
+    <mergeCell ref="G11:G12"/>
+    <mergeCell ref="F11:F12"/>
+    <mergeCell ref="E11:E12"/>
+    <mergeCell ref="D7:D9"/>
+    <mergeCell ref="G7:G8"/>
+    <mergeCell ref="F7:F8"/>
+    <mergeCell ref="E7:E8"/>
+    <mergeCell ref="C2:C3"/>
     <mergeCell ref="D19:D22"/>
     <mergeCell ref="D23:D24"/>
     <mergeCell ref="C6:C24"/>
@@ -5792,41 +5867,39 @@
     <mergeCell ref="H16:H18"/>
     <mergeCell ref="E20:E21"/>
     <mergeCell ref="F20:F21"/>
-    <mergeCell ref="D7:D9"/>
-    <mergeCell ref="G7:G8"/>
-    <mergeCell ref="F7:F8"/>
-    <mergeCell ref="E7:E8"/>
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="D10:D12"/>
-    <mergeCell ref="D13:D15"/>
-    <mergeCell ref="G11:G12"/>
-    <mergeCell ref="F11:F12"/>
-    <mergeCell ref="E11:E12"/>
+    <mergeCell ref="G20:G21"/>
+    <mergeCell ref="J20:J21"/>
+    <mergeCell ref="J23:J24"/>
+    <mergeCell ref="J16:J18"/>
+    <mergeCell ref="H7:H8"/>
+    <mergeCell ref="J7:J8"/>
+    <mergeCell ref="H11:H12"/>
+    <mergeCell ref="J11:J12"/>
   </mergeCells>
   <conditionalFormatting sqref="B1:E1">
-    <cfRule type="expression" dxfId="48" priority="9">
+    <cfRule type="expression" dxfId="52" priority="9">
       <formula>$A1="header"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1:J1">
-    <cfRule type="expression" dxfId="47" priority="5">
+    <cfRule type="expression" dxfId="51" priority="5">
       <formula>$A1="header"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="46" priority="6">
+    <cfRule type="expression" dxfId="50" priority="6">
       <formula>$A1="blank"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J7 J9:J11 J13:J16 J19:J20 J22:J23">
-    <cfRule type="cellIs" dxfId="45" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="49" priority="1" operator="equal">
       <formula>"N/A"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="44" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="48" priority="2" operator="equal">
       <formula>"N/A"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="43" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="47" priority="3" operator="equal">
       <formula>"No"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="42" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="46" priority="4" operator="equal">
       <formula>"Yes"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5889,21 +5962,21 @@
       <c r="S1" s="59"/>
     </row>
     <row r="2" spans="1:19" ht="21.45" customHeight="1" thickBot="1">
-      <c r="A2" s="159"/>
-      <c r="B2" s="160"/>
-      <c r="C2" s="160"/>
-      <c r="D2" s="160"/>
-      <c r="E2" s="160"/>
-      <c r="F2" s="160"/>
-      <c r="G2" s="160"/>
-      <c r="H2" s="160"/>
+      <c r="A2" s="172"/>
+      <c r="B2" s="173"/>
+      <c r="C2" s="173"/>
+      <c r="D2" s="173"/>
+      <c r="E2" s="173"/>
+      <c r="F2" s="173"/>
+      <c r="G2" s="173"/>
+      <c r="H2" s="173"/>
       <c r="I2" s="53"/>
-      <c r="J2" s="159"/>
-      <c r="K2" s="159"/>
-      <c r="L2" s="163" t="s">
+      <c r="J2" s="172"/>
+      <c r="K2" s="172"/>
+      <c r="L2" s="175" t="s">
         <v>279</v>
       </c>
-      <c r="M2" s="164"/>
+      <c r="M2" s="176"/>
       <c r="N2" s="58" t="s">
         <v>275</v>
       </c>
@@ -5922,7 +5995,7 @@
       <c r="S2" s="59"/>
     </row>
     <row r="3" spans="1:19" ht="28.05" customHeight="1">
-      <c r="A3" s="159"/>
+      <c r="A3" s="172"/>
       <c r="B3" s="43" t="s">
         <v>148</v>
       </c>
@@ -5941,115 +6014,115 @@
       <c r="G3" s="43" t="s">
         <v>259</v>
       </c>
-      <c r="H3" s="116" t="s">
+      <c r="H3" s="115" t="s">
         <v>260</v>
       </c>
       <c r="I3" s="56" t="s">
         <v>272</v>
       </c>
-      <c r="J3" s="159"/>
-      <c r="K3" s="159"/>
-      <c r="L3" s="153">
+      <c r="J3" s="172"/>
+      <c r="K3" s="172"/>
+      <c r="L3" s="166">
         <f>COUNTA(I4:I13)</f>
         <v>4</v>
       </c>
-      <c r="M3" s="165"/>
-      <c r="N3" s="168">
+      <c r="M3" s="177"/>
+      <c r="N3" s="180">
         <f>COUNTIF(I4:I12,"Yes")</f>
         <v>2</v>
       </c>
-      <c r="O3" s="171">
+      <c r="O3" s="159">
         <f>COUNTIF(I4:I12,"No")</f>
         <v>1</v>
       </c>
-      <c r="P3" s="174">
+      <c r="P3" s="162">
         <f>COUNTIF(I4:I12,"N/A")</f>
         <v>1</v>
       </c>
-      <c r="Q3" s="153">
+      <c r="Q3" s="166">
         <f>L3-P3</f>
         <v>3</v>
       </c>
-      <c r="R3" s="156">
+      <c r="R3" s="169">
         <f>N3/Q3</f>
         <v>0.66666666666666663</v>
       </c>
       <c r="S3" s="59"/>
     </row>
     <row r="4" spans="1:19" ht="73.95" customHeight="1">
-      <c r="A4" s="159"/>
-      <c r="B4" s="140" t="s">
+      <c r="A4" s="172"/>
+      <c r="B4" s="148" t="s">
         <v>101</v>
       </c>
-      <c r="C4" s="140" t="s">
+      <c r="C4" s="148" t="s">
         <v>0</v>
       </c>
-      <c r="D4" s="149" t="s">
+      <c r="D4" s="157" t="s">
         <v>228</v>
       </c>
-      <c r="E4" s="149" t="s">
+      <c r="E4" s="157" t="s">
         <v>230</v>
       </c>
-      <c r="F4" s="143" t="s">
+      <c r="F4" s="151" t="s">
         <v>249</v>
       </c>
       <c r="G4" s="24" t="s">
         <v>229</v>
       </c>
-      <c r="H4" s="162" t="s">
+      <c r="H4" s="165" t="s">
         <v>262</v>
       </c>
-      <c r="I4" s="145" t="s">
+      <c r="I4" s="153" t="s">
         <v>275</v>
       </c>
-      <c r="J4" s="159"/>
-      <c r="K4" s="159"/>
-      <c r="L4" s="154"/>
-      <c r="M4" s="166"/>
-      <c r="N4" s="169"/>
-      <c r="O4" s="172"/>
-      <c r="P4" s="175"/>
-      <c r="Q4" s="154"/>
-      <c r="R4" s="157"/>
+      <c r="J4" s="172"/>
+      <c r="K4" s="172"/>
+      <c r="L4" s="167"/>
+      <c r="M4" s="178"/>
+      <c r="N4" s="181"/>
+      <c r="O4" s="160"/>
+      <c r="P4" s="163"/>
+      <c r="Q4" s="167"/>
+      <c r="R4" s="170"/>
       <c r="S4" s="59"/>
     </row>
     <row r="5" spans="1:19" ht="78" customHeight="1" thickBot="1">
-      <c r="A5" s="159"/>
-      <c r="B5" s="141"/>
-      <c r="C5" s="141"/>
-      <c r="D5" s="149"/>
-      <c r="E5" s="149"/>
-      <c r="F5" s="150"/>
+      <c r="A5" s="172"/>
+      <c r="B5" s="150"/>
+      <c r="C5" s="150"/>
+      <c r="D5" s="157"/>
+      <c r="E5" s="157"/>
+      <c r="F5" s="158"/>
       <c r="G5" s="24" t="s">
         <v>231</v>
       </c>
-      <c r="H5" s="162"/>
-      <c r="I5" s="145"/>
-      <c r="J5" s="159"/>
-      <c r="K5" s="159"/>
-      <c r="L5" s="155"/>
-      <c r="M5" s="167"/>
-      <c r="N5" s="170"/>
-      <c r="O5" s="173"/>
-      <c r="P5" s="176"/>
-      <c r="Q5" s="155"/>
-      <c r="R5" s="158"/>
+      <c r="H5" s="165"/>
+      <c r="I5" s="153"/>
+      <c r="J5" s="172"/>
+      <c r="K5" s="172"/>
+      <c r="L5" s="168"/>
+      <c r="M5" s="179"/>
+      <c r="N5" s="182"/>
+      <c r="O5" s="161"/>
+      <c r="P5" s="164"/>
+      <c r="Q5" s="168"/>
+      <c r="R5" s="171"/>
       <c r="S5" s="59"/>
     </row>
     <row r="6" spans="1:19" ht="72.599999999999994" thickBot="1">
-      <c r="A6" s="159"/>
-      <c r="B6" s="141"/>
-      <c r="C6" s="141"/>
-      <c r="D6" s="149"/>
-      <c r="E6" s="149"/>
-      <c r="F6" s="144"/>
+      <c r="A6" s="172"/>
+      <c r="B6" s="150"/>
+      <c r="C6" s="150"/>
+      <c r="D6" s="157"/>
+      <c r="E6" s="157"/>
+      <c r="F6" s="152"/>
       <c r="G6" s="24" t="s">
         <v>232</v>
       </c>
-      <c r="H6" s="162"/>
-      <c r="I6" s="145"/>
-      <c r="J6" s="159"/>
-      <c r="K6" s="159"/>
+      <c r="H6" s="165"/>
+      <c r="I6" s="153"/>
+      <c r="J6" s="172"/>
+      <c r="K6" s="172"/>
       <c r="L6" s="59"/>
       <c r="M6" s="59"/>
       <c r="N6" s="59"/>
@@ -6060,9 +6133,9 @@
       <c r="S6" s="59"/>
     </row>
     <row r="7" spans="1:19" ht="109.05" customHeight="1" thickBot="1">
-      <c r="A7" s="159"/>
-      <c r="B7" s="141"/>
-      <c r="C7" s="141"/>
+      <c r="A7" s="172"/>
+      <c r="B7" s="150"/>
+      <c r="C7" s="150"/>
       <c r="D7" s="24" t="s">
         <v>234</v>
       </c>
@@ -6075,26 +6148,26 @@
       <c r="G7" s="24" t="s">
         <v>236</v>
       </c>
-      <c r="H7" s="162" t="s">
+      <c r="H7" s="165" t="s">
         <v>263</v>
       </c>
-      <c r="I7" s="145" t="s">
+      <c r="I7" s="153" t="s">
         <v>274</v>
       </c>
-      <c r="J7" s="159"/>
-      <c r="K7" s="159"/>
-      <c r="L7" s="92" t="s">
+      <c r="J7" s="172"/>
+      <c r="K7" s="172"/>
+      <c r="L7" s="91" t="s">
         <v>611</v>
       </c>
-      <c r="M7" s="126" t="s">
+      <c r="M7" s="125" t="s">
         <v>612</v>
       </c>
-      <c r="N7" s="114"/>
+      <c r="N7" s="113"/>
     </row>
     <row r="8" spans="1:19" ht="102" customHeight="1">
-      <c r="A8" s="159"/>
-      <c r="B8" s="141"/>
-      <c r="C8" s="141"/>
+      <c r="A8" s="172"/>
+      <c r="B8" s="150"/>
+      <c r="C8" s="150"/>
       <c r="D8" s="24" t="s">
         <v>235</v>
       </c>
@@ -6107,16 +6180,16 @@
       <c r="G8" s="24" t="s">
         <v>238</v>
       </c>
-      <c r="H8" s="162"/>
-      <c r="I8" s="145"/>
-      <c r="J8" s="159"/>
-      <c r="K8" s="159"/>
-      <c r="N8" s="115"/>
+      <c r="H8" s="165"/>
+      <c r="I8" s="153"/>
+      <c r="J8" s="172"/>
+      <c r="K8" s="172"/>
+      <c r="N8" s="114"/>
     </row>
     <row r="9" spans="1:19" ht="252" customHeight="1">
-      <c r="A9" s="159"/>
-      <c r="B9" s="141"/>
-      <c r="C9" s="141"/>
+      <c r="A9" s="172"/>
+      <c r="B9" s="150"/>
+      <c r="C9" s="150"/>
       <c r="D9" s="24" t="s">
         <v>244</v>
       </c>
@@ -6129,19 +6202,19 @@
       <c r="G9" s="24" t="s">
         <v>246</v>
       </c>
-      <c r="H9" s="162" t="s">
+      <c r="H9" s="165" t="s">
         <v>265</v>
       </c>
-      <c r="I9" s="145" t="s">
+      <c r="I9" s="153" t="s">
         <v>273</v>
       </c>
-      <c r="J9" s="159"/>
-      <c r="K9" s="159"/>
+      <c r="J9" s="172"/>
+      <c r="K9" s="172"/>
     </row>
     <row r="10" spans="1:19" ht="139.05000000000001" customHeight="1">
-      <c r="A10" s="159"/>
-      <c r="B10" s="141"/>
-      <c r="C10" s="141"/>
+      <c r="A10" s="172"/>
+      <c r="B10" s="150"/>
+      <c r="C10" s="150"/>
       <c r="D10" s="24" t="s">
         <v>248</v>
       </c>
@@ -6154,15 +6227,15 @@
       <c r="G10" s="24" t="s">
         <v>243</v>
       </c>
-      <c r="H10" s="162"/>
-      <c r="I10" s="145"/>
-      <c r="J10" s="159"/>
-      <c r="K10" s="159"/>
+      <c r="H10" s="165"/>
+      <c r="I10" s="153"/>
+      <c r="J10" s="172"/>
+      <c r="K10" s="172"/>
     </row>
     <row r="11" spans="1:19" ht="64.95" customHeight="1">
-      <c r="A11" s="159"/>
-      <c r="B11" s="142"/>
-      <c r="C11" s="142"/>
+      <c r="A11" s="172"/>
+      <c r="B11" s="149"/>
+      <c r="C11" s="149"/>
       <c r="D11" s="24" t="s">
         <v>239</v>
       </c>
@@ -6181,43 +6254,37 @@
       <c r="I11" s="4" t="s">
         <v>275</v>
       </c>
-      <c r="J11" s="159"/>
-      <c r="K11" s="159"/>
+      <c r="J11" s="172"/>
+      <c r="K11" s="172"/>
     </row>
     <row r="12" spans="1:19">
-      <c r="A12" s="159"/>
-      <c r="B12" s="161"/>
-      <c r="C12" s="161"/>
-      <c r="D12" s="161"/>
-      <c r="E12" s="161"/>
-      <c r="F12" s="161"/>
-      <c r="G12" s="161"/>
-      <c r="H12" s="161"/>
+      <c r="A12" s="172"/>
+      <c r="B12" s="174"/>
+      <c r="C12" s="174"/>
+      <c r="D12" s="174"/>
+      <c r="E12" s="174"/>
+      <c r="F12" s="174"/>
+      <c r="G12" s="174"/>
+      <c r="H12" s="174"/>
       <c r="I12" s="53"/>
-      <c r="J12" s="159"/>
-      <c r="K12" s="159"/>
+      <c r="J12" s="172"/>
+      <c r="K12" s="172"/>
     </row>
     <row r="13" spans="1:19">
-      <c r="A13" s="159"/>
-      <c r="B13" s="159"/>
-      <c r="C13" s="159"/>
-      <c r="D13" s="159"/>
-      <c r="E13" s="159"/>
-      <c r="F13" s="159"/>
-      <c r="G13" s="159"/>
-      <c r="H13" s="159"/>
+      <c r="A13" s="172"/>
+      <c r="B13" s="172"/>
+      <c r="C13" s="172"/>
+      <c r="D13" s="172"/>
+      <c r="E13" s="172"/>
+      <c r="F13" s="172"/>
+      <c r="G13" s="172"/>
+      <c r="H13" s="172"/>
       <c r="I13" s="53"/>
-      <c r="J13" s="159"/>
-      <c r="K13" s="159"/>
+      <c r="J13" s="172"/>
+      <c r="K13" s="172"/>
     </row>
   </sheetData>
   <mergeCells count="22">
-    <mergeCell ref="I9:I10"/>
-    <mergeCell ref="O3:O5"/>
-    <mergeCell ref="P3:P5"/>
-    <mergeCell ref="F4:F6"/>
-    <mergeCell ref="H4:H6"/>
-    <mergeCell ref="H7:H8"/>
     <mergeCell ref="Q3:Q5"/>
     <mergeCell ref="R3:R5"/>
     <mergeCell ref="B4:B11"/>
@@ -6234,26 +6301,32 @@
     <mergeCell ref="J2:K13"/>
     <mergeCell ref="I4:I6"/>
     <mergeCell ref="I7:I8"/>
+    <mergeCell ref="I9:I10"/>
+    <mergeCell ref="O3:O5"/>
+    <mergeCell ref="P3:P5"/>
+    <mergeCell ref="F4:F6"/>
+    <mergeCell ref="H4:H6"/>
+    <mergeCell ref="H7:H8"/>
   </mergeCells>
   <conditionalFormatting sqref="H3:I3">
-    <cfRule type="expression" dxfId="41" priority="5">
+    <cfRule type="expression" dxfId="45" priority="5">
       <formula>$A3="header"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="40" priority="6">
+    <cfRule type="expression" dxfId="44" priority="6">
       <formula>$A3="blank"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I4 I7 I9 I11">
-    <cfRule type="cellIs" dxfId="39" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="43" priority="1" operator="equal">
       <formula>"N/A"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="38" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="42" priority="2" operator="equal">
       <formula>"N/A"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="37" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="41" priority="3" operator="equal">
       <formula>"No"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="36" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="40" priority="4" operator="equal">
       <formula>"Yes"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6288,9 +6361,9 @@
     <col min="12" max="12" width="37.6640625" customWidth="1"/>
     <col min="13" max="13" width="24" customWidth="1"/>
     <col min="14" max="14" width="10.88671875" hidden="1" customWidth="1"/>
-    <col min="15" max="15" width="25.33203125" style="91" customWidth="1"/>
-    <col min="16" max="16" width="24.21875" style="91" customWidth="1"/>
-    <col min="17" max="17" width="26.5546875" style="91" customWidth="1"/>
+    <col min="15" max="15" width="25.33203125" style="90" customWidth="1"/>
+    <col min="16" max="16" width="24.21875" style="90" customWidth="1"/>
+    <col min="17" max="17" width="26.5546875" style="90" customWidth="1"/>
     <col min="18" max="18" width="30.44140625" customWidth="1"/>
     <col min="19" max="19" width="26.21875" customWidth="1"/>
     <col min="20" max="20" width="45.77734375" customWidth="1"/>
@@ -6319,27 +6392,27 @@
       <c r="G1" s="6" t="s">
         <v>260</v>
       </c>
-      <c r="H1" s="78"/>
+      <c r="H1" s="77"/>
       <c r="I1" s="55" t="s">
         <v>272</v>
       </c>
       <c r="J1" s="50"/>
-      <c r="L1" s="96" t="s">
+      <c r="L1" s="95" t="s">
         <v>590</v>
       </c>
-      <c r="M1" s="178" t="s">
+      <c r="M1" s="183" t="s">
         <v>588</v>
       </c>
-      <c r="N1" s="179"/>
-      <c r="O1" s="95" t="s">
+      <c r="N1" s="184"/>
+      <c r="O1" s="94" t="s">
         <v>589</v>
       </c>
     </row>
     <row r="2" spans="1:32" ht="128.4" thickBot="1">
-      <c r="A2" s="145" t="s">
+      <c r="A2" s="153" t="s">
         <v>64</v>
       </c>
-      <c r="B2" s="149" t="s">
+      <c r="B2" s="157" t="s">
         <v>65</v>
       </c>
       <c r="C2" s="24" t="s">
@@ -6358,58 +6431,58 @@
         <v>520</v>
       </c>
       <c r="H2" s="24"/>
-      <c r="I2" s="4" t="s">
-        <v>273</v>
+      <c r="I2" s="127" t="s">
+        <v>275</v>
       </c>
       <c r="J2" s="50"/>
-      <c r="K2" s="91"/>
-      <c r="L2" s="98">
+      <c r="K2" s="90"/>
+      <c r="L2" s="97">
         <f>O2/S2</f>
-        <v>0.625</v>
-      </c>
-      <c r="M2" s="96" t="s">
+        <v>0.97142857142857142</v>
+      </c>
+      <c r="M2" s="95" t="s">
         <v>275</v>
       </c>
-      <c r="N2" s="97"/>
-      <c r="O2" s="88">
+      <c r="N2" s="96"/>
+      <c r="O2" s="87">
         <f>COUNTIF(I2:I37,"Yes")</f>
-        <v>20</v>
-      </c>
-      <c r="P2" s="95" t="s">
+        <v>34</v>
+      </c>
+      <c r="P2" s="94" t="s">
         <v>279</v>
       </c>
-      <c r="Q2" s="87">
+      <c r="Q2" s="86">
         <f>COUNTA(I2:I200)</f>
         <v>35</v>
       </c>
-      <c r="R2" s="95" t="s">
+      <c r="R2" s="94" t="s">
         <v>591</v>
       </c>
-      <c r="S2" s="87">
+      <c r="S2" s="86">
         <f>Q2-O4</f>
-        <v>32</v>
-      </c>
-      <c r="T2" s="92" t="s">
+        <v>35</v>
+      </c>
+      <c r="T2" s="91" t="s">
         <v>611</v>
       </c>
-      <c r="U2" s="126" t="s">
+      <c r="U2" s="125" t="s">
         <v>613</v>
       </c>
-      <c r="V2" s="91"/>
-      <c r="W2" s="91"/>
-      <c r="X2" s="91"/>
-      <c r="Y2" s="91"/>
-      <c r="Z2" s="91"/>
-      <c r="AA2" s="91"/>
-      <c r="AB2" s="91"/>
-      <c r="AC2" s="91"/>
-      <c r="AD2" s="91"/>
-      <c r="AE2" s="91"/>
-      <c r="AF2" s="91"/>
+      <c r="V2" s="90"/>
+      <c r="W2" s="90"/>
+      <c r="X2" s="90"/>
+      <c r="Y2" s="90"/>
+      <c r="Z2" s="90"/>
+      <c r="AA2" s="90"/>
+      <c r="AB2" s="90"/>
+      <c r="AC2" s="90"/>
+      <c r="AD2" s="90"/>
+      <c r="AE2" s="90"/>
+      <c r="AF2" s="90"/>
     </row>
     <row r="3" spans="1:32" ht="115.95" customHeight="1" thickBot="1">
-      <c r="A3" s="145"/>
-      <c r="B3" s="149"/>
+      <c r="A3" s="153"/>
+      <c r="B3" s="157"/>
       <c r="C3" s="24" t="s">
         <v>69</v>
       </c>
@@ -6426,36 +6499,36 @@
         <v>519</v>
       </c>
       <c r="H3" s="24"/>
-      <c r="I3" s="4" t="s">
+      <c r="I3" s="127" t="s">
         <v>275</v>
       </c>
       <c r="J3" s="50"/>
-      <c r="K3" s="91"/>
-      <c r="L3" s="91"/>
-      <c r="M3" s="96" t="s">
+      <c r="K3" s="90"/>
+      <c r="L3" s="90"/>
+      <c r="M3" s="95" t="s">
         <v>273</v>
       </c>
-      <c r="N3" s="97"/>
-      <c r="O3" s="89">
+      <c r="N3" s="96"/>
+      <c r="O3" s="88">
         <f>COUNTIF(I2:I37,"No")</f>
-        <v>12</v>
-      </c>
-      <c r="R3" s="91"/>
-      <c r="S3" s="91"/>
-      <c r="T3" s="91"/>
-      <c r="U3" s="91"/>
-      <c r="V3" s="91"/>
-      <c r="W3" s="91"/>
-      <c r="X3" s="91"/>
-      <c r="Y3" s="91"/>
-      <c r="Z3" s="91"/>
-      <c r="AA3" s="91"/>
-      <c r="AB3" s="91"/>
-      <c r="AC3" s="91"/>
+        <v>1</v>
+      </c>
+      <c r="R3" s="90"/>
+      <c r="S3" s="90"/>
+      <c r="T3" s="90"/>
+      <c r="U3" s="90"/>
+      <c r="V3" s="90"/>
+      <c r="W3" s="90"/>
+      <c r="X3" s="90"/>
+      <c r="Y3" s="90"/>
+      <c r="Z3" s="90"/>
+      <c r="AA3" s="90"/>
+      <c r="AB3" s="90"/>
+      <c r="AC3" s="90"/>
     </row>
     <row r="4" spans="1:32" ht="87" customHeight="1" thickBot="1">
-      <c r="A4" s="145"/>
-      <c r="B4" s="149"/>
+      <c r="A4" s="153"/>
+      <c r="B4" s="157"/>
       <c r="C4" s="24" t="s">
         <v>72</v>
       </c>
@@ -6472,38 +6545,38 @@
         <v>495</v>
       </c>
       <c r="H4" s="24"/>
-      <c r="I4" s="4" t="s">
-        <v>273</v>
+      <c r="I4" s="127" t="s">
+        <v>275</v>
       </c>
       <c r="J4" s="50"/>
-      <c r="K4" s="91"/>
-      <c r="L4" s="91"/>
+      <c r="K4" s="90"/>
+      <c r="L4" s="90"/>
       <c r="M4" s="58" t="s">
         <v>274</v>
       </c>
-      <c r="N4" s="91"/>
-      <c r="O4" s="90">
+      <c r="N4" s="90"/>
+      <c r="O4" s="89">
         <f>COUNTIF(I2:I37,"N/A")</f>
-        <v>3</v>
-      </c>
-      <c r="P4" s="93"/>
-      <c r="Q4" s="93"/>
-      <c r="R4" s="91"/>
-      <c r="S4" s="91"/>
-      <c r="T4" s="91"/>
-      <c r="U4" s="91"/>
-      <c r="V4" s="91"/>
-      <c r="W4" s="91"/>
-      <c r="X4" s="91"/>
-      <c r="Y4" s="91"/>
-      <c r="Z4" s="91"/>
-      <c r="AA4" s="91"/>
-      <c r="AB4" s="91"/>
-      <c r="AC4" s="91"/>
+        <v>0</v>
+      </c>
+      <c r="P4" s="92"/>
+      <c r="Q4" s="92"/>
+      <c r="R4" s="90"/>
+      <c r="S4" s="90"/>
+      <c r="T4" s="90"/>
+      <c r="U4" s="90"/>
+      <c r="V4" s="90"/>
+      <c r="W4" s="90"/>
+      <c r="X4" s="90"/>
+      <c r="Y4" s="90"/>
+      <c r="Z4" s="90"/>
+      <c r="AA4" s="90"/>
+      <c r="AB4" s="90"/>
+      <c r="AC4" s="90"/>
     </row>
     <row r="5" spans="1:32" ht="126.45" customHeight="1">
-      <c r="A5" s="145"/>
-      <c r="B5" s="149"/>
+      <c r="A5" s="153"/>
+      <c r="B5" s="157"/>
       <c r="C5" s="68" t="s">
         <v>75</v>
       </c>
@@ -6520,32 +6593,32 @@
         <v>493</v>
       </c>
       <c r="H5" s="68"/>
-      <c r="I5" s="77" t="s">
-        <v>274</v>
+      <c r="I5" s="127" t="s">
+        <v>275</v>
       </c>
       <c r="J5" s="50"/>
-      <c r="K5" s="91"/>
-      <c r="L5" s="91"/>
-      <c r="M5" s="91"/>
-      <c r="N5" s="91"/>
-      <c r="P5" s="93"/>
-      <c r="Q5" s="93"/>
-      <c r="R5" s="91"/>
-      <c r="S5" s="91"/>
-      <c r="T5" s="91"/>
-      <c r="U5" s="91"/>
-      <c r="V5" s="91"/>
-      <c r="W5" s="91"/>
-      <c r="X5" s="91"/>
-      <c r="Y5" s="91"/>
-      <c r="Z5" s="91"/>
-      <c r="AA5" s="91"/>
-      <c r="AB5" s="91"/>
-      <c r="AC5" s="91"/>
+      <c r="K5" s="90"/>
+      <c r="L5" s="90"/>
+      <c r="M5" s="90"/>
+      <c r="N5" s="90"/>
+      <c r="P5" s="92"/>
+      <c r="Q5" s="92"/>
+      <c r="R5" s="90"/>
+      <c r="S5" s="90"/>
+      <c r="T5" s="90"/>
+      <c r="U5" s="90"/>
+      <c r="V5" s="90"/>
+      <c r="W5" s="90"/>
+      <c r="X5" s="90"/>
+      <c r="Y5" s="90"/>
+      <c r="Z5" s="90"/>
+      <c r="AA5" s="90"/>
+      <c r="AB5" s="90"/>
+      <c r="AC5" s="90"/>
     </row>
     <row r="6" spans="1:32" ht="86.4">
-      <c r="A6" s="145"/>
-      <c r="B6" s="149"/>
+      <c r="A6" s="153"/>
+      <c r="B6" s="157"/>
       <c r="C6" s="24" t="s">
         <v>78</v>
       </c>
@@ -6562,30 +6635,30 @@
         <v>492</v>
       </c>
       <c r="H6" s="24"/>
-      <c r="I6" s="4" t="s">
+      <c r="I6" s="127" t="s">
         <v>275</v>
       </c>
       <c r="J6" s="50"/>
-      <c r="K6" s="91"/>
-      <c r="L6" s="91"/>
-      <c r="M6" s="91"/>
-      <c r="N6" s="91"/>
-      <c r="R6" s="91"/>
-      <c r="S6" s="91"/>
-      <c r="T6" s="91"/>
-      <c r="U6" s="91"/>
-      <c r="V6" s="91"/>
-      <c r="W6" s="91"/>
-      <c r="X6" s="91"/>
-      <c r="Y6" s="91"/>
-      <c r="Z6" s="91"/>
-      <c r="AA6" s="91"/>
-      <c r="AB6" s="91"/>
-      <c r="AC6" s="91"/>
+      <c r="K6" s="90"/>
+      <c r="L6" s="90"/>
+      <c r="M6" s="90"/>
+      <c r="N6" s="90"/>
+      <c r="R6" s="90"/>
+      <c r="S6" s="90"/>
+      <c r="T6" s="90"/>
+      <c r="U6" s="90"/>
+      <c r="V6" s="90"/>
+      <c r="W6" s="90"/>
+      <c r="X6" s="90"/>
+      <c r="Y6" s="90"/>
+      <c r="Z6" s="90"/>
+      <c r="AA6" s="90"/>
+      <c r="AB6" s="90"/>
+      <c r="AC6" s="90"/>
     </row>
     <row r="7" spans="1:32" ht="86.4">
-      <c r="A7" s="145"/>
-      <c r="B7" s="149"/>
+      <c r="A7" s="153"/>
+      <c r="B7" s="157"/>
       <c r="C7" s="24" t="s">
         <v>81</v>
       </c>
@@ -6602,33 +6675,33 @@
         <v>494</v>
       </c>
       <c r="H7" s="24"/>
-      <c r="I7" s="4" t="s">
+      <c r="I7" s="127" t="s">
         <v>275</v>
       </c>
       <c r="J7" s="50"/>
-      <c r="K7" s="91"/>
-      <c r="L7" s="91"/>
-      <c r="M7" s="91"/>
-      <c r="N7" s="91"/>
-      <c r="R7" s="91"/>
-      <c r="S7" s="91"/>
-      <c r="T7" s="91"/>
-      <c r="U7" s="91"/>
-      <c r="V7" s="91"/>
-      <c r="W7" s="91"/>
-      <c r="X7" s="91"/>
-      <c r="Y7" s="91"/>
-      <c r="Z7" s="91"/>
-      <c r="AA7" s="91"/>
-      <c r="AB7" s="91"/>
-      <c r="AC7" s="91"/>
+      <c r="K7" s="90"/>
+      <c r="L7" s="90"/>
+      <c r="M7" s="90"/>
+      <c r="N7" s="90"/>
+      <c r="R7" s="90"/>
+      <c r="S7" s="90"/>
+      <c r="T7" s="90"/>
+      <c r="U7" s="90"/>
+      <c r="V7" s="90"/>
+      <c r="W7" s="90"/>
+      <c r="X7" s="90"/>
+      <c r="Y7" s="90"/>
+      <c r="Z7" s="90"/>
+      <c r="AA7" s="90"/>
+      <c r="AB7" s="90"/>
+      <c r="AC7" s="90"/>
     </row>
     <row r="8" spans="1:32" ht="96.6">
-      <c r="A8" s="145"/>
-      <c r="B8" s="145" t="s">
+      <c r="A8" s="153"/>
+      <c r="B8" s="153" t="s">
         <v>6</v>
       </c>
-      <c r="C8" s="145" t="s">
+      <c r="C8" s="153" t="s">
         <v>7</v>
       </c>
       <c r="D8" s="27" t="s">
@@ -6644,31 +6717,31 @@
         <v>496</v>
       </c>
       <c r="H8" s="24"/>
-      <c r="I8" s="4" t="s">
+      <c r="I8" s="127" t="s">
         <v>275</v>
       </c>
       <c r="J8" s="50"/>
-      <c r="K8" s="91"/>
-      <c r="L8" s="91"/>
-      <c r="M8" s="91"/>
-      <c r="N8" s="91"/>
-      <c r="R8" s="91"/>
-      <c r="S8" s="91"/>
-      <c r="T8" s="91"/>
-      <c r="U8" s="91"/>
-      <c r="V8" s="91"/>
-      <c r="W8" s="91"/>
-      <c r="X8" s="91"/>
-      <c r="Y8" s="91"/>
-      <c r="Z8" s="91"/>
-      <c r="AA8" s="91"/>
-      <c r="AB8" s="91"/>
-      <c r="AC8" s="91"/>
+      <c r="K8" s="90"/>
+      <c r="L8" s="90"/>
+      <c r="M8" s="90"/>
+      <c r="N8" s="90"/>
+      <c r="R8" s="90"/>
+      <c r="S8" s="90"/>
+      <c r="T8" s="90"/>
+      <c r="U8" s="90"/>
+      <c r="V8" s="90"/>
+      <c r="W8" s="90"/>
+      <c r="X8" s="90"/>
+      <c r="Y8" s="90"/>
+      <c r="Z8" s="90"/>
+      <c r="AA8" s="90"/>
+      <c r="AB8" s="90"/>
+      <c r="AC8" s="90"/>
     </row>
     <row r="9" spans="1:32" ht="69">
-      <c r="A9" s="145"/>
-      <c r="B9" s="145"/>
-      <c r="C9" s="145"/>
+      <c r="A9" s="153"/>
+      <c r="B9" s="153"/>
+      <c r="C9" s="153"/>
       <c r="D9" s="31" t="s">
         <v>10</v>
       </c>
@@ -6682,31 +6755,31 @@
         <v>497</v>
       </c>
       <c r="H9" s="24"/>
-      <c r="I9" s="124" t="s">
-        <v>273</v>
+      <c r="I9" s="127" t="s">
+        <v>275</v>
       </c>
       <c r="J9" s="50"/>
-      <c r="K9" s="91"/>
-      <c r="L9" s="91"/>
-      <c r="M9" s="91"/>
-      <c r="N9" s="91"/>
-      <c r="R9" s="91"/>
-      <c r="S9" s="91"/>
-      <c r="T9" s="91"/>
-      <c r="U9" s="91"/>
-      <c r="V9" s="91"/>
-      <c r="W9" s="91"/>
-      <c r="X9" s="91"/>
-      <c r="Y9" s="91"/>
-      <c r="Z9" s="91"/>
-      <c r="AA9" s="91"/>
-      <c r="AB9" s="91"/>
-      <c r="AC9" s="91"/>
+      <c r="K9" s="90"/>
+      <c r="L9" s="90"/>
+      <c r="M9" s="90"/>
+      <c r="N9" s="90"/>
+      <c r="R9" s="90"/>
+      <c r="S9" s="90"/>
+      <c r="T9" s="90"/>
+      <c r="U9" s="90"/>
+      <c r="V9" s="90"/>
+      <c r="W9" s="90"/>
+      <c r="X9" s="90"/>
+      <c r="Y9" s="90"/>
+      <c r="Z9" s="90"/>
+      <c r="AA9" s="90"/>
+      <c r="AB9" s="90"/>
+      <c r="AC9" s="90"/>
     </row>
     <row r="10" spans="1:32" ht="82.8">
-      <c r="A10" s="145"/>
-      <c r="B10" s="145"/>
-      <c r="C10" s="177"/>
+      <c r="A10" s="153"/>
+      <c r="B10" s="153"/>
+      <c r="C10" s="186"/>
       <c r="D10" s="31" t="s">
         <v>13</v>
       </c>
@@ -6720,31 +6793,31 @@
         <v>498</v>
       </c>
       <c r="H10" s="24"/>
-      <c r="I10" s="4" t="s">
+      <c r="I10" s="127" t="s">
         <v>275</v>
       </c>
       <c r="J10" s="50"/>
-      <c r="K10" s="91"/>
-      <c r="L10" s="91"/>
-      <c r="M10" s="91"/>
-      <c r="N10" s="91"/>
-      <c r="R10" s="91"/>
-      <c r="S10" s="91"/>
-      <c r="T10" s="91"/>
-      <c r="U10" s="91"/>
-      <c r="V10" s="91"/>
-      <c r="W10" s="91"/>
-      <c r="X10" s="91"/>
-      <c r="Y10" s="91"/>
-      <c r="Z10" s="91"/>
-      <c r="AA10" s="91"/>
-      <c r="AB10" s="91"/>
-      <c r="AC10" s="91"/>
+      <c r="K10" s="90"/>
+      <c r="L10" s="90"/>
+      <c r="M10" s="90"/>
+      <c r="N10" s="90"/>
+      <c r="R10" s="90"/>
+      <c r="S10" s="90"/>
+      <c r="T10" s="90"/>
+      <c r="U10" s="90"/>
+      <c r="V10" s="90"/>
+      <c r="W10" s="90"/>
+      <c r="X10" s="90"/>
+      <c r="Y10" s="90"/>
+      <c r="Z10" s="90"/>
+      <c r="AA10" s="90"/>
+      <c r="AB10" s="90"/>
+      <c r="AC10" s="90"/>
     </row>
     <row r="11" spans="1:32" ht="72">
-      <c r="A11" s="145"/>
-      <c r="B11" s="145"/>
-      <c r="C11" s="177"/>
+      <c r="A11" s="153"/>
+      <c r="B11" s="153"/>
+      <c r="C11" s="186"/>
       <c r="D11" s="31" t="s">
         <v>15</v>
       </c>
@@ -6758,30 +6831,30 @@
         <v>499</v>
       </c>
       <c r="H11" s="24"/>
-      <c r="I11" s="4" t="s">
+      <c r="I11" s="127" t="s">
         <v>275</v>
       </c>
       <c r="J11" s="50"/>
-      <c r="K11" s="91"/>
-      <c r="L11" s="91"/>
-      <c r="M11" s="91"/>
-      <c r="N11" s="91"/>
-      <c r="R11" s="91"/>
-      <c r="S11" s="91"/>
-      <c r="T11" s="91"/>
-      <c r="U11" s="91"/>
-      <c r="V11" s="91"/>
-      <c r="W11" s="91"/>
-      <c r="X11" s="91"/>
-      <c r="Y11" s="91"/>
-      <c r="Z11" s="91"/>
-      <c r="AA11" s="91"/>
-      <c r="AB11" s="91"/>
-      <c r="AC11" s="91"/>
+      <c r="K11" s="90"/>
+      <c r="L11" s="90"/>
+      <c r="M11" s="90"/>
+      <c r="N11" s="90"/>
+      <c r="R11" s="90"/>
+      <c r="S11" s="90"/>
+      <c r="T11" s="90"/>
+      <c r="U11" s="90"/>
+      <c r="V11" s="90"/>
+      <c r="W11" s="90"/>
+      <c r="X11" s="90"/>
+      <c r="Y11" s="90"/>
+      <c r="Z11" s="90"/>
+      <c r="AA11" s="90"/>
+      <c r="AB11" s="90"/>
+      <c r="AC11" s="90"/>
     </row>
     <row r="12" spans="1:32" ht="72">
-      <c r="A12" s="145"/>
-      <c r="B12" s="145"/>
+      <c r="A12" s="153"/>
+      <c r="B12" s="153"/>
       <c r="C12" s="3"/>
       <c r="D12" s="31" t="s">
         <v>20</v>
@@ -6796,30 +6869,30 @@
         <v>500</v>
       </c>
       <c r="H12" s="24"/>
-      <c r="I12" s="4" t="s">
-        <v>273</v>
+      <c r="I12" s="127" t="s">
+        <v>275</v>
       </c>
       <c r="J12" s="50"/>
-      <c r="K12" s="91"/>
-      <c r="L12" s="91"/>
-      <c r="M12" s="91"/>
-      <c r="N12" s="91"/>
-      <c r="R12" s="91"/>
-      <c r="S12" s="91"/>
-      <c r="T12" s="91"/>
-      <c r="U12" s="91"/>
-      <c r="V12" s="91"/>
-      <c r="W12" s="91"/>
-      <c r="X12" s="91"/>
-      <c r="Y12" s="91"/>
-      <c r="Z12" s="91"/>
-      <c r="AA12" s="91"/>
-      <c r="AB12" s="91"/>
-      <c r="AC12" s="91"/>
+      <c r="K12" s="90"/>
+      <c r="L12" s="90"/>
+      <c r="M12" s="90"/>
+      <c r="N12" s="90"/>
+      <c r="R12" s="90"/>
+      <c r="S12" s="90"/>
+      <c r="T12" s="90"/>
+      <c r="U12" s="90"/>
+      <c r="V12" s="90"/>
+      <c r="W12" s="90"/>
+      <c r="X12" s="90"/>
+      <c r="Y12" s="90"/>
+      <c r="Z12" s="90"/>
+      <c r="AA12" s="90"/>
+      <c r="AB12" s="90"/>
+      <c r="AC12" s="90"/>
     </row>
     <row r="13" spans="1:32" ht="69">
-      <c r="A13" s="145"/>
-      <c r="B13" s="145"/>
+      <c r="A13" s="153"/>
+      <c r="B13" s="153"/>
       <c r="C13" s="3"/>
       <c r="D13" s="31" t="s">
         <v>22</v>
@@ -6834,30 +6907,30 @@
         <v>501</v>
       </c>
       <c r="H13" s="24"/>
-      <c r="I13" s="124" t="s">
-        <v>273</v>
+      <c r="I13" s="127" t="s">
+        <v>275</v>
       </c>
       <c r="J13" s="50"/>
-      <c r="K13" s="91"/>
-      <c r="L13" s="91"/>
-      <c r="M13" s="91"/>
-      <c r="N13" s="91"/>
-      <c r="R13" s="91"/>
-      <c r="S13" s="91"/>
-      <c r="T13" s="91"/>
-      <c r="U13" s="91"/>
-      <c r="V13" s="91"/>
-      <c r="W13" s="91"/>
-      <c r="X13" s="91"/>
-      <c r="Y13" s="91"/>
-      <c r="Z13" s="91"/>
-      <c r="AA13" s="91"/>
-      <c r="AB13" s="91"/>
-      <c r="AC13" s="91"/>
+      <c r="K13" s="90"/>
+      <c r="L13" s="90"/>
+      <c r="M13" s="90"/>
+      <c r="N13" s="90"/>
+      <c r="R13" s="90"/>
+      <c r="S13" s="90"/>
+      <c r="T13" s="90"/>
+      <c r="U13" s="90"/>
+      <c r="V13" s="90"/>
+      <c r="W13" s="90"/>
+      <c r="X13" s="90"/>
+      <c r="Y13" s="90"/>
+      <c r="Z13" s="90"/>
+      <c r="AA13" s="90"/>
+      <c r="AB13" s="90"/>
+      <c r="AC13" s="90"/>
     </row>
     <row r="14" spans="1:32" ht="86.4">
-      <c r="A14" s="145"/>
-      <c r="B14" s="145"/>
+      <c r="A14" s="153"/>
+      <c r="B14" s="153"/>
       <c r="C14" s="4" t="s">
         <v>18</v>
       </c>
@@ -6874,31 +6947,31 @@
         <v>502</v>
       </c>
       <c r="H14" s="24"/>
-      <c r="I14" s="4" t="s">
-        <v>273</v>
+      <c r="I14" s="127" t="s">
+        <v>275</v>
       </c>
       <c r="J14" s="50"/>
-      <c r="K14" s="91"/>
-      <c r="L14" s="91"/>
-      <c r="M14" s="91"/>
-      <c r="N14" s="91"/>
-      <c r="R14" s="91"/>
-      <c r="S14" s="91"/>
-      <c r="T14" s="91"/>
-      <c r="U14" s="91"/>
-      <c r="V14" s="91"/>
-      <c r="W14" s="91"/>
-      <c r="X14" s="91"/>
-      <c r="Y14" s="91"/>
-      <c r="Z14" s="91"/>
-      <c r="AA14" s="91"/>
-      <c r="AB14" s="91"/>
-      <c r="AC14" s="91"/>
+      <c r="K14" s="90"/>
+      <c r="L14" s="90"/>
+      <c r="M14" s="90"/>
+      <c r="N14" s="90"/>
+      <c r="R14" s="90"/>
+      <c r="S14" s="90"/>
+      <c r="T14" s="90"/>
+      <c r="U14" s="90"/>
+      <c r="V14" s="90"/>
+      <c r="W14" s="90"/>
+      <c r="X14" s="90"/>
+      <c r="Y14" s="90"/>
+      <c r="Z14" s="90"/>
+      <c r="AA14" s="90"/>
+      <c r="AB14" s="90"/>
+      <c r="AC14" s="90"/>
     </row>
     <row r="15" spans="1:32" ht="82.8">
-      <c r="A15" s="145"/>
-      <c r="B15" s="145"/>
-      <c r="C15" s="177" t="s">
+      <c r="A15" s="153"/>
+      <c r="B15" s="153"/>
+      <c r="C15" s="186" t="s">
         <v>19</v>
       </c>
       <c r="D15" s="31" t="s">
@@ -6914,31 +6987,31 @@
         <v>503</v>
       </c>
       <c r="H15" s="24"/>
-      <c r="I15" s="4" t="s">
+      <c r="I15" s="127" t="s">
         <v>275</v>
       </c>
       <c r="J15" s="50"/>
-      <c r="K15" s="91"/>
-      <c r="L15" s="91"/>
-      <c r="M15" s="91"/>
-      <c r="N15" s="91"/>
-      <c r="R15" s="91"/>
-      <c r="S15" s="91"/>
-      <c r="T15" s="91"/>
-      <c r="U15" s="91"/>
-      <c r="V15" s="91"/>
-      <c r="W15" s="91"/>
-      <c r="X15" s="91"/>
-      <c r="Y15" s="91"/>
-      <c r="Z15" s="91"/>
-      <c r="AA15" s="91"/>
-      <c r="AB15" s="91"/>
-      <c r="AC15" s="91"/>
+      <c r="K15" s="90"/>
+      <c r="L15" s="90"/>
+      <c r="M15" s="90"/>
+      <c r="N15" s="90"/>
+      <c r="R15" s="90"/>
+      <c r="S15" s="90"/>
+      <c r="T15" s="90"/>
+      <c r="U15" s="90"/>
+      <c r="V15" s="90"/>
+      <c r="W15" s="90"/>
+      <c r="X15" s="90"/>
+      <c r="Y15" s="90"/>
+      <c r="Z15" s="90"/>
+      <c r="AA15" s="90"/>
+      <c r="AB15" s="90"/>
+      <c r="AC15" s="90"/>
     </row>
     <row r="16" spans="1:32" ht="72">
-      <c r="A16" s="145"/>
-      <c r="B16" s="145"/>
-      <c r="C16" s="177"/>
+      <c r="A16" s="153"/>
+      <c r="B16" s="153"/>
+      <c r="C16" s="186"/>
       <c r="D16" s="30" t="s">
         <v>52</v>
       </c>
@@ -6952,30 +7025,30 @@
         <v>504</v>
       </c>
       <c r="H16" s="24"/>
-      <c r="I16" s="4" t="s">
+      <c r="I16" s="127" t="s">
         <v>275</v>
       </c>
       <c r="J16" s="50"/>
-      <c r="K16" s="91"/>
-      <c r="L16" s="91"/>
-      <c r="M16" s="91"/>
-      <c r="N16" s="91"/>
-      <c r="R16" s="91"/>
-      <c r="S16" s="91"/>
-      <c r="T16" s="91"/>
-      <c r="U16" s="91"/>
-      <c r="V16" s="91"/>
-      <c r="W16" s="91"/>
-      <c r="X16" s="91"/>
-      <c r="Y16" s="91"/>
-      <c r="Z16" s="91"/>
-      <c r="AA16" s="91"/>
-      <c r="AB16" s="91"/>
-      <c r="AC16" s="91"/>
+      <c r="K16" s="90"/>
+      <c r="L16" s="90"/>
+      <c r="M16" s="90"/>
+      <c r="N16" s="90"/>
+      <c r="R16" s="90"/>
+      <c r="S16" s="90"/>
+      <c r="T16" s="90"/>
+      <c r="U16" s="90"/>
+      <c r="V16" s="90"/>
+      <c r="W16" s="90"/>
+      <c r="X16" s="90"/>
+      <c r="Y16" s="90"/>
+      <c r="Z16" s="90"/>
+      <c r="AA16" s="90"/>
+      <c r="AB16" s="90"/>
+      <c r="AC16" s="90"/>
     </row>
     <row r="17" spans="1:29" ht="100.8">
-      <c r="A17" s="145"/>
-      <c r="B17" s="145"/>
+      <c r="A17" s="153"/>
+      <c r="B17" s="153"/>
       <c r="C17" s="4" t="s">
         <v>35</v>
       </c>
@@ -6992,29 +7065,29 @@
         <v>505</v>
       </c>
       <c r="H17" s="24"/>
-      <c r="I17" s="4" t="s">
+      <c r="I17" s="127" t="s">
         <v>275</v>
       </c>
       <c r="J17" s="50"/>
-      <c r="K17" s="91"/>
-      <c r="L17" s="91"/>
-      <c r="M17" s="91"/>
-      <c r="N17" s="91"/>
-      <c r="R17" s="91"/>
-      <c r="S17" s="91"/>
-      <c r="T17" s="91"/>
-      <c r="U17" s="91"/>
-      <c r="V17" s="91"/>
-      <c r="W17" s="91"/>
-      <c r="X17" s="91"/>
-      <c r="Y17" s="91"/>
-      <c r="Z17" s="91"/>
-      <c r="AA17" s="91"/>
-      <c r="AB17" s="91"/>
-      <c r="AC17" s="91"/>
+      <c r="K17" s="90"/>
+      <c r="L17" s="90"/>
+      <c r="M17" s="90"/>
+      <c r="N17" s="90"/>
+      <c r="R17" s="90"/>
+      <c r="S17" s="90"/>
+      <c r="T17" s="90"/>
+      <c r="U17" s="90"/>
+      <c r="V17" s="90"/>
+      <c r="W17" s="90"/>
+      <c r="X17" s="90"/>
+      <c r="Y17" s="90"/>
+      <c r="Z17" s="90"/>
+      <c r="AA17" s="90"/>
+      <c r="AB17" s="90"/>
+      <c r="AC17" s="90"/>
     </row>
     <row r="18" spans="1:29" ht="86.4">
-      <c r="A18" s="145"/>
+      <c r="A18" s="153"/>
       <c r="B18" s="4" t="s">
         <v>24</v>
       </c>
@@ -7034,29 +7107,29 @@
         <v>506</v>
       </c>
       <c r="H18" s="24"/>
-      <c r="I18" s="4" t="s">
-        <v>274</v>
+      <c r="I18" s="127" t="s">
+        <v>275</v>
       </c>
       <c r="J18" s="50"/>
-      <c r="K18" s="91"/>
-      <c r="L18" s="91"/>
-      <c r="M18" s="91"/>
-      <c r="N18" s="91"/>
-      <c r="R18" s="91"/>
-      <c r="S18" s="91"/>
-      <c r="T18" s="91"/>
-      <c r="U18" s="91"/>
-      <c r="V18" s="91"/>
-      <c r="W18" s="91"/>
-      <c r="X18" s="91"/>
-      <c r="Y18" s="91"/>
-      <c r="Z18" s="91"/>
-      <c r="AA18" s="91"/>
-      <c r="AB18" s="91"/>
-      <c r="AC18" s="91"/>
+      <c r="K18" s="90"/>
+      <c r="L18" s="90"/>
+      <c r="M18" s="90"/>
+      <c r="N18" s="90"/>
+      <c r="R18" s="90"/>
+      <c r="S18" s="90"/>
+      <c r="T18" s="90"/>
+      <c r="U18" s="90"/>
+      <c r="V18" s="90"/>
+      <c r="W18" s="90"/>
+      <c r="X18" s="90"/>
+      <c r="Y18" s="90"/>
+      <c r="Z18" s="90"/>
+      <c r="AA18" s="90"/>
+      <c r="AB18" s="90"/>
+      <c r="AC18" s="90"/>
     </row>
     <row r="19" spans="1:29" ht="115.2">
-      <c r="A19" s="145"/>
+      <c r="A19" s="153"/>
       <c r="B19" s="4" t="s">
         <v>38</v>
       </c>
@@ -7076,30 +7149,30 @@
         <v>507</v>
       </c>
       <c r="H19" s="24"/>
-      <c r="I19" s="4" t="s">
-        <v>274</v>
+      <c r="I19" s="127" t="s">
+        <v>275</v>
       </c>
       <c r="J19" s="50"/>
-      <c r="K19" s="91"/>
-      <c r="L19" s="91"/>
-      <c r="M19" s="91"/>
-      <c r="N19" s="91"/>
-      <c r="R19" s="91"/>
-      <c r="S19" s="91"/>
-      <c r="T19" s="91"/>
-      <c r="U19" s="91"/>
-      <c r="V19" s="91"/>
-      <c r="W19" s="91"/>
-      <c r="X19" s="91"/>
-      <c r="Y19" s="91"/>
-      <c r="Z19" s="91"/>
-      <c r="AA19" s="91"/>
-      <c r="AB19" s="91"/>
-      <c r="AC19" s="91"/>
+      <c r="K19" s="90"/>
+      <c r="L19" s="90"/>
+      <c r="M19" s="90"/>
+      <c r="N19" s="90"/>
+      <c r="R19" s="90"/>
+      <c r="S19" s="90"/>
+      <c r="T19" s="90"/>
+      <c r="U19" s="90"/>
+      <c r="V19" s="90"/>
+      <c r="W19" s="90"/>
+      <c r="X19" s="90"/>
+      <c r="Y19" s="90"/>
+      <c r="Z19" s="90"/>
+      <c r="AA19" s="90"/>
+      <c r="AB19" s="90"/>
+      <c r="AC19" s="90"/>
     </row>
     <row r="20" spans="1:29" ht="115.2">
-      <c r="A20" s="145"/>
-      <c r="B20" s="145" t="s">
+      <c r="A20" s="153"/>
+      <c r="B20" s="153" t="s">
         <v>46</v>
       </c>
       <c r="C20" s="4" t="s">
@@ -7118,30 +7191,30 @@
         <v>508</v>
       </c>
       <c r="H20" s="24"/>
-      <c r="I20" s="4" t="s">
+      <c r="I20" s="127" t="s">
         <v>275</v>
       </c>
       <c r="J20" s="50"/>
-      <c r="K20" s="91"/>
-      <c r="L20" s="91"/>
-      <c r="M20" s="91"/>
-      <c r="N20" s="91"/>
-      <c r="R20" s="91"/>
-      <c r="S20" s="91"/>
-      <c r="T20" s="91"/>
-      <c r="U20" s="91"/>
-      <c r="V20" s="91"/>
-      <c r="W20" s="91"/>
-      <c r="X20" s="91"/>
-      <c r="Y20" s="91"/>
-      <c r="Z20" s="91"/>
-      <c r="AA20" s="91"/>
-      <c r="AB20" s="91"/>
-      <c r="AC20" s="91"/>
+      <c r="K20" s="90"/>
+      <c r="L20" s="90"/>
+      <c r="M20" s="90"/>
+      <c r="N20" s="90"/>
+      <c r="R20" s="90"/>
+      <c r="S20" s="90"/>
+      <c r="T20" s="90"/>
+      <c r="U20" s="90"/>
+      <c r="V20" s="90"/>
+      <c r="W20" s="90"/>
+      <c r="X20" s="90"/>
+      <c r="Y20" s="90"/>
+      <c r="Z20" s="90"/>
+      <c r="AA20" s="90"/>
+      <c r="AB20" s="90"/>
+      <c r="AC20" s="90"/>
     </row>
     <row r="21" spans="1:29" ht="86.4">
-      <c r="A21" s="145"/>
-      <c r="B21" s="145"/>
+      <c r="A21" s="153"/>
+      <c r="B21" s="153"/>
       <c r="C21" s="25" t="s">
         <v>51</v>
       </c>
@@ -7158,30 +7231,30 @@
         <v>509</v>
       </c>
       <c r="H21" s="24"/>
-      <c r="I21" s="4" t="s">
+      <c r="I21" s="127" t="s">
         <v>275</v>
       </c>
       <c r="J21" s="50"/>
-      <c r="K21" s="91"/>
-      <c r="L21" s="91"/>
-      <c r="M21" s="91"/>
-      <c r="N21" s="91"/>
-      <c r="R21" s="91"/>
-      <c r="S21" s="91"/>
-      <c r="T21" s="91"/>
-      <c r="U21" s="91"/>
-      <c r="V21" s="91"/>
-      <c r="W21" s="91"/>
-      <c r="X21" s="91"/>
-      <c r="Y21" s="91"/>
-      <c r="Z21" s="91"/>
-      <c r="AA21" s="91"/>
-      <c r="AB21" s="91"/>
-      <c r="AC21" s="91"/>
+      <c r="K21" s="90"/>
+      <c r="L21" s="90"/>
+      <c r="M21" s="90"/>
+      <c r="N21" s="90"/>
+      <c r="R21" s="90"/>
+      <c r="S21" s="90"/>
+      <c r="T21" s="90"/>
+      <c r="U21" s="90"/>
+      <c r="V21" s="90"/>
+      <c r="W21" s="90"/>
+      <c r="X21" s="90"/>
+      <c r="Y21" s="90"/>
+      <c r="Z21" s="90"/>
+      <c r="AA21" s="90"/>
+      <c r="AB21" s="90"/>
+      <c r="AC21" s="90"/>
     </row>
     <row r="22" spans="1:29" ht="100.8">
-      <c r="A22" s="145"/>
-      <c r="B22" s="145"/>
+      <c r="A22" s="153"/>
+      <c r="B22" s="153"/>
       <c r="C22" s="25" t="s">
         <v>54</v>
       </c>
@@ -7198,30 +7271,30 @@
         <v>76</v>
       </c>
       <c r="H22" s="24"/>
-      <c r="I22" s="4" t="s">
-        <v>273</v>
+      <c r="I22" s="127" t="s">
+        <v>275</v>
       </c>
       <c r="J22" s="50"/>
-      <c r="K22" s="91"/>
-      <c r="L22" s="91"/>
-      <c r="M22" s="91"/>
-      <c r="N22" s="91"/>
-      <c r="R22" s="91"/>
-      <c r="S22" s="91"/>
-      <c r="T22" s="91"/>
-      <c r="U22" s="91"/>
-      <c r="V22" s="91"/>
-      <c r="W22" s="91"/>
-      <c r="X22" s="91"/>
-      <c r="Y22" s="91"/>
-      <c r="Z22" s="91"/>
-      <c r="AA22" s="91"/>
-      <c r="AB22" s="91"/>
-      <c r="AC22" s="91"/>
+      <c r="K22" s="90"/>
+      <c r="L22" s="90"/>
+      <c r="M22" s="90"/>
+      <c r="N22" s="90"/>
+      <c r="R22" s="90"/>
+      <c r="S22" s="90"/>
+      <c r="T22" s="90"/>
+      <c r="U22" s="90"/>
+      <c r="V22" s="90"/>
+      <c r="W22" s="90"/>
+      <c r="X22" s="90"/>
+      <c r="Y22" s="90"/>
+      <c r="Z22" s="90"/>
+      <c r="AA22" s="90"/>
+      <c r="AB22" s="90"/>
+      <c r="AC22" s="90"/>
     </row>
     <row r="23" spans="1:29" ht="115.2">
-      <c r="A23" s="145"/>
-      <c r="B23" s="145"/>
+      <c r="A23" s="153"/>
+      <c r="B23" s="153"/>
       <c r="C23" s="25" t="s">
         <v>56</v>
       </c>
@@ -7238,30 +7311,30 @@
         <v>510</v>
       </c>
       <c r="H23" s="24"/>
-      <c r="I23" s="4" t="s">
-        <v>273</v>
+      <c r="I23" s="127" t="s">
+        <v>275</v>
       </c>
       <c r="J23" s="50"/>
-      <c r="K23" s="91"/>
-      <c r="L23" s="91"/>
-      <c r="M23" s="91"/>
-      <c r="N23" s="91"/>
-      <c r="R23" s="91"/>
-      <c r="S23" s="91"/>
-      <c r="T23" s="91"/>
-      <c r="U23" s="91"/>
-      <c r="V23" s="91"/>
-      <c r="W23" s="91"/>
-      <c r="X23" s="91"/>
-      <c r="Y23" s="91"/>
-      <c r="Z23" s="91"/>
-      <c r="AA23" s="91"/>
-      <c r="AB23" s="91"/>
-      <c r="AC23" s="91"/>
+      <c r="K23" s="90"/>
+      <c r="L23" s="90"/>
+      <c r="M23" s="90"/>
+      <c r="N23" s="90"/>
+      <c r="R23" s="90"/>
+      <c r="S23" s="90"/>
+      <c r="T23" s="90"/>
+      <c r="U23" s="90"/>
+      <c r="V23" s="90"/>
+      <c r="W23" s="90"/>
+      <c r="X23" s="90"/>
+      <c r="Y23" s="90"/>
+      <c r="Z23" s="90"/>
+      <c r="AA23" s="90"/>
+      <c r="AB23" s="90"/>
+      <c r="AC23" s="90"/>
     </row>
     <row r="24" spans="1:29" ht="69">
-      <c r="A24" s="145"/>
-      <c r="B24" s="145"/>
+      <c r="A24" s="153"/>
+      <c r="B24" s="153"/>
       <c r="C24" s="4" t="s">
         <v>66</v>
       </c>
@@ -7278,30 +7351,30 @@
         <v>512</v>
       </c>
       <c r="H24" s="24"/>
-      <c r="I24" s="4" t="s">
-        <v>273</v>
+      <c r="I24" s="127" t="s">
+        <v>275</v>
       </c>
       <c r="J24" s="50"/>
-      <c r="K24" s="91"/>
-      <c r="L24" s="91"/>
-      <c r="M24" s="91"/>
-      <c r="N24" s="91"/>
-      <c r="R24" s="91"/>
-      <c r="S24" s="91"/>
-      <c r="T24" s="91"/>
-      <c r="U24" s="91"/>
-      <c r="V24" s="91"/>
-      <c r="W24" s="91"/>
-      <c r="X24" s="91"/>
-      <c r="Y24" s="91"/>
-      <c r="Z24" s="91"/>
-      <c r="AA24" s="91"/>
-      <c r="AB24" s="91"/>
-      <c r="AC24" s="91"/>
+      <c r="K24" s="90"/>
+      <c r="L24" s="90"/>
+      <c r="M24" s="90"/>
+      <c r="N24" s="90"/>
+      <c r="R24" s="90"/>
+      <c r="S24" s="90"/>
+      <c r="T24" s="90"/>
+      <c r="U24" s="90"/>
+      <c r="V24" s="90"/>
+      <c r="W24" s="90"/>
+      <c r="X24" s="90"/>
+      <c r="Y24" s="90"/>
+      <c r="Z24" s="90"/>
+      <c r="AA24" s="90"/>
+      <c r="AB24" s="90"/>
+      <c r="AC24" s="90"/>
     </row>
     <row r="25" spans="1:29" ht="86.4">
-      <c r="A25" s="145"/>
-      <c r="B25" s="145"/>
+      <c r="A25" s="153"/>
+      <c r="B25" s="153"/>
       <c r="C25" s="4" t="s">
         <v>69</v>
       </c>
@@ -7318,30 +7391,30 @@
         <v>511</v>
       </c>
       <c r="H25" s="24"/>
-      <c r="I25" s="4" t="s">
-        <v>273</v>
+      <c r="I25" s="127" t="s">
+        <v>275</v>
       </c>
       <c r="J25" s="50"/>
-      <c r="K25" s="91"/>
-      <c r="L25" s="91"/>
-      <c r="M25" s="91"/>
-      <c r="N25" s="91"/>
-      <c r="R25" s="91"/>
-      <c r="S25" s="91"/>
-      <c r="T25" s="91"/>
-      <c r="U25" s="91"/>
-      <c r="V25" s="91"/>
-      <c r="W25" s="91"/>
-      <c r="X25" s="91"/>
-      <c r="Y25" s="91"/>
-      <c r="Z25" s="91"/>
-      <c r="AA25" s="91"/>
-      <c r="AB25" s="91"/>
-      <c r="AC25" s="91"/>
+      <c r="K25" s="90"/>
+      <c r="L25" s="90"/>
+      <c r="M25" s="90"/>
+      <c r="N25" s="90"/>
+      <c r="R25" s="90"/>
+      <c r="S25" s="90"/>
+      <c r="T25" s="90"/>
+      <c r="U25" s="90"/>
+      <c r="V25" s="90"/>
+      <c r="W25" s="90"/>
+      <c r="X25" s="90"/>
+      <c r="Y25" s="90"/>
+      <c r="Z25" s="90"/>
+      <c r="AA25" s="90"/>
+      <c r="AB25" s="90"/>
+      <c r="AC25" s="90"/>
     </row>
     <row r="26" spans="1:29" ht="86.4">
-      <c r="A26" s="145"/>
-      <c r="B26" s="145"/>
+      <c r="A26" s="153"/>
+      <c r="B26" s="153"/>
       <c r="C26" s="4" t="s">
         <v>75</v>
       </c>
@@ -7358,31 +7431,31 @@
         <v>513</v>
       </c>
       <c r="H26" s="24"/>
-      <c r="I26" s="4" t="s">
-        <v>273</v>
+      <c r="I26" s="127" t="s">
+        <v>275</v>
       </c>
       <c r="J26" s="50"/>
-      <c r="K26" s="91"/>
-      <c r="L26" s="91"/>
-      <c r="M26" s="91"/>
-      <c r="N26" s="91"/>
-      <c r="R26" s="91"/>
-      <c r="S26" s="91"/>
-      <c r="T26" s="91"/>
-      <c r="U26" s="91"/>
-      <c r="V26" s="91"/>
-      <c r="W26" s="91"/>
-      <c r="X26" s="91"/>
-      <c r="Y26" s="91"/>
-      <c r="Z26" s="91"/>
-      <c r="AA26" s="91"/>
-      <c r="AB26" s="91"/>
-      <c r="AC26" s="91"/>
+      <c r="K26" s="90"/>
+      <c r="L26" s="90"/>
+      <c r="M26" s="90"/>
+      <c r="N26" s="90"/>
+      <c r="R26" s="90"/>
+      <c r="S26" s="90"/>
+      <c r="T26" s="90"/>
+      <c r="U26" s="90"/>
+      <c r="V26" s="90"/>
+      <c r="W26" s="90"/>
+      <c r="X26" s="90"/>
+      <c r="Y26" s="90"/>
+      <c r="Z26" s="90"/>
+      <c r="AA26" s="90"/>
+      <c r="AB26" s="90"/>
+      <c r="AC26" s="90"/>
     </row>
     <row r="27" spans="1:29" ht="86.4">
-      <c r="A27" s="145"/>
-      <c r="B27" s="145"/>
-      <c r="C27" s="145" t="s">
+      <c r="A27" s="153"/>
+      <c r="B27" s="153"/>
+      <c r="C27" s="153" t="s">
         <v>87</v>
       </c>
       <c r="D27" s="31" t="s">
@@ -7398,31 +7471,31 @@
         <v>514</v>
       </c>
       <c r="H27" s="24"/>
-      <c r="I27" s="4" t="s">
+      <c r="I27" s="127" t="s">
         <v>275</v>
       </c>
       <c r="J27" s="50"/>
-      <c r="K27" s="91"/>
-      <c r="L27" s="91"/>
-      <c r="M27" s="91"/>
-      <c r="N27" s="91"/>
-      <c r="R27" s="91"/>
-      <c r="S27" s="91"/>
-      <c r="T27" s="91"/>
-      <c r="U27" s="91"/>
-      <c r="V27" s="91"/>
-      <c r="W27" s="91"/>
-      <c r="X27" s="91"/>
-      <c r="Y27" s="91"/>
-      <c r="Z27" s="91"/>
-      <c r="AA27" s="91"/>
-      <c r="AB27" s="91"/>
-      <c r="AC27" s="91"/>
+      <c r="K27" s="90"/>
+      <c r="L27" s="90"/>
+      <c r="M27" s="90"/>
+      <c r="N27" s="90"/>
+      <c r="R27" s="90"/>
+      <c r="S27" s="90"/>
+      <c r="T27" s="90"/>
+      <c r="U27" s="90"/>
+      <c r="V27" s="90"/>
+      <c r="W27" s="90"/>
+      <c r="X27" s="90"/>
+      <c r="Y27" s="90"/>
+      <c r="Z27" s="90"/>
+      <c r="AA27" s="90"/>
+      <c r="AB27" s="90"/>
+      <c r="AC27" s="90"/>
     </row>
     <row r="28" spans="1:29" ht="86.4">
-      <c r="A28" s="145"/>
-      <c r="B28" s="145"/>
-      <c r="C28" s="145"/>
+      <c r="A28" s="153"/>
+      <c r="B28" s="153"/>
+      <c r="C28" s="153"/>
       <c r="D28" s="31" t="s">
         <v>127</v>
       </c>
@@ -7436,33 +7509,33 @@
         <v>515</v>
       </c>
       <c r="H28" s="24"/>
-      <c r="I28" s="124" t="s">
+      <c r="I28" s="123" t="s">
         <v>273</v>
       </c>
       <c r="J28" s="50"/>
-      <c r="K28" s="91"/>
-      <c r="L28" s="91"/>
-      <c r="M28" s="91"/>
-      <c r="N28" s="91"/>
-      <c r="R28" s="91"/>
-      <c r="S28" s="91"/>
-      <c r="T28" s="91"/>
-      <c r="U28" s="91"/>
-      <c r="V28" s="91"/>
-      <c r="W28" s="91"/>
-      <c r="X28" s="91"/>
-      <c r="Y28" s="91"/>
-      <c r="Z28" s="91"/>
-      <c r="AA28" s="91"/>
-      <c r="AB28" s="91"/>
-      <c r="AC28" s="91"/>
+      <c r="K28" s="90"/>
+      <c r="L28" s="90"/>
+      <c r="M28" s="90"/>
+      <c r="N28" s="90"/>
+      <c r="R28" s="90"/>
+      <c r="S28" s="90"/>
+      <c r="T28" s="90"/>
+      <c r="U28" s="90"/>
+      <c r="V28" s="90"/>
+      <c r="W28" s="90"/>
+      <c r="X28" s="90"/>
+      <c r="Y28" s="90"/>
+      <c r="Z28" s="90"/>
+      <c r="AA28" s="90"/>
+      <c r="AB28" s="90"/>
+      <c r="AC28" s="90"/>
     </row>
     <row r="29" spans="1:29" ht="86.4">
-      <c r="A29" s="145"/>
-      <c r="B29" s="145" t="s">
+      <c r="A29" s="153"/>
+      <c r="B29" s="153" t="s">
         <v>84</v>
       </c>
-      <c r="C29" s="145" t="s">
+      <c r="C29" s="153" t="s">
         <v>92</v>
       </c>
       <c r="D29" s="31" t="s">
@@ -7482,27 +7555,27 @@
         <v>275</v>
       </c>
       <c r="J29" s="50"/>
-      <c r="K29" s="91"/>
-      <c r="L29" s="91"/>
-      <c r="M29" s="91"/>
-      <c r="N29" s="91"/>
-      <c r="R29" s="91"/>
-      <c r="S29" s="91"/>
-      <c r="T29" s="91"/>
-      <c r="U29" s="91"/>
-      <c r="V29" s="91"/>
-      <c r="W29" s="91"/>
-      <c r="X29" s="91"/>
-      <c r="Y29" s="91"/>
-      <c r="Z29" s="91"/>
-      <c r="AA29" s="91"/>
-      <c r="AB29" s="91"/>
-      <c r="AC29" s="91"/>
+      <c r="K29" s="90"/>
+      <c r="L29" s="90"/>
+      <c r="M29" s="90"/>
+      <c r="N29" s="90"/>
+      <c r="R29" s="90"/>
+      <c r="S29" s="90"/>
+      <c r="T29" s="90"/>
+      <c r="U29" s="90"/>
+      <c r="V29" s="90"/>
+      <c r="W29" s="90"/>
+      <c r="X29" s="90"/>
+      <c r="Y29" s="90"/>
+      <c r="Z29" s="90"/>
+      <c r="AA29" s="90"/>
+      <c r="AB29" s="90"/>
+      <c r="AC29" s="90"/>
     </row>
     <row r="30" spans="1:29" ht="82.8">
-      <c r="A30" s="145"/>
-      <c r="B30" s="145"/>
-      <c r="C30" s="145"/>
+      <c r="A30" s="153"/>
+      <c r="B30" s="153"/>
+      <c r="C30" s="153"/>
       <c r="D30" s="31" t="s">
         <v>103</v>
       </c>
@@ -7520,24 +7593,24 @@
         <v>275</v>
       </c>
       <c r="J30" s="50"/>
-      <c r="K30" s="91"/>
-      <c r="L30" s="91"/>
-      <c r="R30" s="91"/>
-      <c r="S30" s="91"/>
-      <c r="T30" s="91"/>
-      <c r="U30" s="91"/>
-      <c r="V30" s="91"/>
-      <c r="W30" s="91"/>
-      <c r="X30" s="91"/>
-      <c r="Y30" s="91"/>
-      <c r="Z30" s="91"/>
-      <c r="AA30" s="91"/>
-      <c r="AB30" s="91"/>
-      <c r="AC30" s="91"/>
+      <c r="K30" s="90"/>
+      <c r="L30" s="90"/>
+      <c r="R30" s="90"/>
+      <c r="S30" s="90"/>
+      <c r="T30" s="90"/>
+      <c r="U30" s="90"/>
+      <c r="V30" s="90"/>
+      <c r="W30" s="90"/>
+      <c r="X30" s="90"/>
+      <c r="Y30" s="90"/>
+      <c r="Z30" s="90"/>
+      <c r="AA30" s="90"/>
+      <c r="AB30" s="90"/>
+      <c r="AC30" s="90"/>
     </row>
     <row r="31" spans="1:29" ht="69">
-      <c r="A31" s="145"/>
-      <c r="B31" s="145"/>
+      <c r="A31" s="153"/>
+      <c r="B31" s="153"/>
       <c r="C31" s="4"/>
       <c r="D31" s="31" t="s">
         <v>114</v>
@@ -7548,7 +7621,7 @@
       <c r="F31" s="30" t="s">
         <v>207</v>
       </c>
-      <c r="G31" s="149" t="s">
+      <c r="G31" s="157" t="s">
         <v>517</v>
       </c>
       <c r="H31" s="24"/>
@@ -7556,24 +7629,24 @@
         <v>275</v>
       </c>
       <c r="J31" s="50"/>
-      <c r="K31" s="91"/>
-      <c r="L31" s="91"/>
-      <c r="R31" s="91"/>
-      <c r="S31" s="91"/>
-      <c r="T31" s="91"/>
-      <c r="U31" s="91"/>
-      <c r="V31" s="91"/>
-      <c r="W31" s="91"/>
-      <c r="X31" s="91"/>
-      <c r="Y31" s="91"/>
-      <c r="Z31" s="91"/>
-      <c r="AA31" s="91"/>
-      <c r="AB31" s="91"/>
-      <c r="AC31" s="91"/>
+      <c r="K31" s="90"/>
+      <c r="L31" s="90"/>
+      <c r="R31" s="90"/>
+      <c r="S31" s="90"/>
+      <c r="T31" s="90"/>
+      <c r="U31" s="90"/>
+      <c r="V31" s="90"/>
+      <c r="W31" s="90"/>
+      <c r="X31" s="90"/>
+      <c r="Y31" s="90"/>
+      <c r="Z31" s="90"/>
+      <c r="AA31" s="90"/>
+      <c r="AB31" s="90"/>
+      <c r="AC31" s="90"/>
     </row>
     <row r="32" spans="1:29" ht="69">
-      <c r="A32" s="145"/>
-      <c r="B32" s="145" t="s">
+      <c r="A32" s="153"/>
+      <c r="B32" s="153" t="s">
         <v>86</v>
       </c>
       <c r="C32" s="4" t="s">
@@ -7588,7 +7661,7 @@
       <c r="F32" s="30" t="s">
         <v>208</v>
       </c>
-      <c r="G32" s="149"/>
+      <c r="G32" s="157"/>
       <c r="H32" s="24"/>
       <c r="I32" s="4" t="s">
         <v>275</v>
@@ -7596,8 +7669,8 @@
       <c r="J32" s="50"/>
     </row>
     <row r="33" spans="1:10" ht="55.2">
-      <c r="A33" s="145"/>
-      <c r="B33" s="145"/>
+      <c r="A33" s="153"/>
+      <c r="B33" s="153"/>
       <c r="C33" s="4" t="s">
         <v>98</v>
       </c>
@@ -7610,7 +7683,7 @@
       <c r="F33" s="30" t="s">
         <v>209</v>
       </c>
-      <c r="G33" s="149"/>
+      <c r="G33" s="157"/>
       <c r="H33" s="24"/>
       <c r="I33" s="4" t="s">
         <v>275</v>
@@ -7618,11 +7691,11 @@
       <c r="J33" s="50"/>
     </row>
     <row r="34" spans="1:10" ht="69">
-      <c r="A34" s="145"/>
-      <c r="B34" s="145" t="s">
+      <c r="A34" s="153"/>
+      <c r="B34" s="153" t="s">
         <v>91</v>
       </c>
-      <c r="C34" s="86"/>
+      <c r="C34" s="85"/>
       <c r="D34" s="31" t="s">
         <v>120</v>
       </c>
@@ -7642,9 +7715,9 @@
       <c r="J34" s="50"/>
     </row>
     <row r="35" spans="1:10" ht="69">
-      <c r="A35" s="145"/>
-      <c r="B35" s="145"/>
-      <c r="C35" s="145" t="s">
+      <c r="A35" s="153"/>
+      <c r="B35" s="153"/>
+      <c r="C35" s="153" t="s">
         <v>124</v>
       </c>
       <c r="D35" s="31" t="s">
@@ -7666,36 +7739,36 @@
       <c r="J35" s="50"/>
     </row>
     <row r="36" spans="1:10" ht="232.05" customHeight="1">
-      <c r="A36" s="145"/>
-      <c r="B36" s="145"/>
-      <c r="C36" s="145"/>
-      <c r="D36" s="180" t="s">
+      <c r="A36" s="153"/>
+      <c r="B36" s="153"/>
+      <c r="C36" s="153"/>
+      <c r="D36" s="185" t="s">
         <v>247</v>
       </c>
-      <c r="E36" s="145" t="s">
+      <c r="E36" s="153" t="s">
         <v>255</v>
       </c>
-      <c r="F36" s="145" t="s">
+      <c r="F36" s="153" t="s">
         <v>261</v>
       </c>
-      <c r="G36" s="145" t="s">
+      <c r="G36" s="153" t="s">
         <v>518</v>
       </c>
-      <c r="H36" s="145"/>
-      <c r="I36" s="145" t="s">
+      <c r="H36" s="153"/>
+      <c r="I36" s="153" t="s">
         <v>275</v>
       </c>
     </row>
     <row r="37" spans="1:10">
-      <c r="A37" s="145"/>
-      <c r="B37" s="145"/>
-      <c r="C37" s="145"/>
-      <c r="D37" s="180"/>
-      <c r="E37" s="145"/>
-      <c r="F37" s="145"/>
-      <c r="G37" s="145"/>
-      <c r="H37" s="145"/>
-      <c r="I37" s="145"/>
+      <c r="A37" s="153"/>
+      <c r="B37" s="153"/>
+      <c r="C37" s="153"/>
+      <c r="D37" s="185"/>
+      <c r="E37" s="153"/>
+      <c r="F37" s="153"/>
+      <c r="G37" s="153"/>
+      <c r="H37" s="153"/>
+      <c r="I37" s="153"/>
       <c r="J37" s="50"/>
     </row>
     <row r="38" spans="1:10">
@@ -7703,17 +7776,6 @@
     </row>
   </sheetData>
   <mergeCells count="24">
-    <mergeCell ref="G31:G33"/>
-    <mergeCell ref="B32:B33"/>
-    <mergeCell ref="M1:N1"/>
-    <mergeCell ref="B34:B37"/>
-    <mergeCell ref="C35:C37"/>
-    <mergeCell ref="I36:I37"/>
-    <mergeCell ref="D36:D37"/>
-    <mergeCell ref="E36:E37"/>
-    <mergeCell ref="F36:F37"/>
-    <mergeCell ref="G36:G37"/>
-    <mergeCell ref="H36:H37"/>
     <mergeCell ref="A2:A37"/>
     <mergeCell ref="B2:B5"/>
     <mergeCell ref="B6:B7"/>
@@ -7727,31 +7789,42 @@
     <mergeCell ref="C27:C28"/>
     <mergeCell ref="B29:B31"/>
     <mergeCell ref="C29:C30"/>
+    <mergeCell ref="G31:G33"/>
+    <mergeCell ref="B32:B33"/>
+    <mergeCell ref="M1:N1"/>
+    <mergeCell ref="B34:B37"/>
+    <mergeCell ref="C35:C37"/>
+    <mergeCell ref="I36:I37"/>
+    <mergeCell ref="D36:D37"/>
+    <mergeCell ref="E36:E37"/>
+    <mergeCell ref="F36:F37"/>
+    <mergeCell ref="G36:G37"/>
+    <mergeCell ref="H36:H37"/>
   </mergeCells>
   <conditionalFormatting sqref="A1:D1">
-    <cfRule type="expression" dxfId="35" priority="7">
+    <cfRule type="expression" dxfId="39" priority="7">
       <formula>$A1="header"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1:I1">
-    <cfRule type="expression" dxfId="34" priority="5">
+    <cfRule type="expression" dxfId="38" priority="5">
       <formula>$A1="header"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="33" priority="6">
+    <cfRule type="expression" dxfId="37" priority="6">
       <formula>$A1="blank"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I2:I36">
-    <cfRule type="cellIs" dxfId="32" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="36" priority="1" operator="equal">
       <formula>"N/A"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="31" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="35" priority="2" operator="equal">
       <formula>"N/A"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="30" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="34" priority="3" operator="equal">
       <formula>"No"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="29" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="33" priority="4" operator="equal">
       <formula>"Yes"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7815,11 +7888,11 @@
       <c r="H2" s="50"/>
       <c r="I2" s="50"/>
       <c r="K2" s="50"/>
-      <c r="L2" s="163" t="s">
+      <c r="L2" s="175" t="s">
         <v>279</v>
       </c>
-      <c r="M2" s="164"/>
-      <c r="N2" s="117" t="s">
+      <c r="M2" s="176"/>
+      <c r="N2" s="116" t="s">
         <v>600</v>
       </c>
       <c r="O2" s="58" t="s">
@@ -7863,44 +7936,44 @@
         <v>272</v>
       </c>
       <c r="K3" s="50"/>
-      <c r="L3" s="153">
+      <c r="L3" s="166">
         <f>COUNTA(H4:H25)</f>
         <v>21</v>
       </c>
-      <c r="M3" s="165"/>
-      <c r="N3" s="181">
+      <c r="M3" s="177"/>
+      <c r="N3" s="190">
         <f>L3-Q3</f>
         <v>20</v>
       </c>
-      <c r="O3" s="168">
+      <c r="O3" s="180">
         <f>COUNTIF(J4:J21,"Yes")</f>
         <v>16</v>
       </c>
-      <c r="P3" s="171">
+      <c r="P3" s="159">
         <f>COUNTIF(J4:J21,"No")</f>
         <v>0</v>
       </c>
-      <c r="Q3" s="174">
+      <c r="Q3" s="162">
         <f>COUNTIF(J4:J21,"N/A")</f>
         <v>1</v>
       </c>
-      <c r="R3" s="156">
+      <c r="R3" s="169">
         <f>O3/N3</f>
         <v>0.8</v>
       </c>
     </row>
     <row r="4" spans="1:18" ht="94.5" customHeight="1">
       <c r="A4" s="50"/>
-      <c r="B4" s="146" t="s">
+      <c r="B4" s="154" t="s">
         <v>85</v>
       </c>
-      <c r="C4" s="140" t="s">
+      <c r="C4" s="148" t="s">
         <v>86</v>
       </c>
-      <c r="D4" s="145" t="s">
+      <c r="D4" s="153" t="s">
         <v>87</v>
       </c>
-      <c r="E4" s="184" t="s">
+      <c r="E4" s="187" t="s">
         <v>278</v>
       </c>
       <c r="F4" s="12" t="s">
@@ -7909,54 +7982,54 @@
       <c r="G4" s="10" t="s">
         <v>193</v>
       </c>
-      <c r="H4" s="149" t="s">
+      <c r="H4" s="157" t="s">
         <v>321</v>
       </c>
       <c r="I4" s="24" t="s">
         <v>567</v>
       </c>
-      <c r="J4" s="145" t="s">
+      <c r="J4" s="153" t="s">
         <v>274</v>
       </c>
       <c r="K4" s="50"/>
-      <c r="L4" s="154"/>
-      <c r="M4" s="166"/>
-      <c r="N4" s="182"/>
-      <c r="O4" s="169"/>
-      <c r="P4" s="172"/>
-      <c r="Q4" s="175"/>
-      <c r="R4" s="157"/>
+      <c r="L4" s="167"/>
+      <c r="M4" s="178"/>
+      <c r="N4" s="191"/>
+      <c r="O4" s="181"/>
+      <c r="P4" s="160"/>
+      <c r="Q4" s="163"/>
+      <c r="R4" s="170"/>
     </row>
     <row r="5" spans="1:18" ht="81" customHeight="1" thickBot="1">
       <c r="A5" s="50"/>
-      <c r="B5" s="147"/>
-      <c r="C5" s="141"/>
-      <c r="D5" s="145"/>
-      <c r="E5" s="184"/>
+      <c r="B5" s="155"/>
+      <c r="C5" s="150"/>
+      <c r="D5" s="153"/>
+      <c r="E5" s="187"/>
       <c r="F5" s="12" t="s">
         <v>90</v>
       </c>
       <c r="G5" s="10" t="s">
         <v>194</v>
       </c>
-      <c r="H5" s="149"/>
+      <c r="H5" s="157"/>
       <c r="I5" s="24" t="s">
         <v>568</v>
       </c>
-      <c r="J5" s="145"/>
+      <c r="J5" s="153"/>
       <c r="K5" s="50"/>
-      <c r="L5" s="155"/>
-      <c r="M5" s="167"/>
-      <c r="N5" s="183"/>
-      <c r="O5" s="170"/>
-      <c r="P5" s="173"/>
-      <c r="Q5" s="176"/>
-      <c r="R5" s="158"/>
+      <c r="L5" s="168"/>
+      <c r="M5" s="179"/>
+      <c r="N5" s="192"/>
+      <c r="O5" s="182"/>
+      <c r="P5" s="161"/>
+      <c r="Q5" s="164"/>
+      <c r="R5" s="171"/>
     </row>
     <row r="6" spans="1:18" ht="111" customHeight="1" thickBot="1">
       <c r="A6" s="50"/>
-      <c r="B6" s="147"/>
-      <c r="C6" s="142"/>
+      <c r="B6" s="155"/>
+      <c r="C6" s="149"/>
       <c r="D6" s="2" t="s">
         <v>384</v>
       </c>
@@ -7988,20 +8061,20 @@
     </row>
     <row r="7" spans="1:18" ht="61.95" customHeight="1" thickBot="1">
       <c r="A7" s="50"/>
-      <c r="B7" s="147"/>
-      <c r="C7" s="145" t="s">
+      <c r="B7" s="155"/>
+      <c r="C7" s="153" t="s">
         <v>91</v>
       </c>
-      <c r="D7" s="145" t="s">
+      <c r="D7" s="153" t="s">
         <v>216</v>
       </c>
-      <c r="E7" s="184" t="s">
+      <c r="E7" s="187" t="s">
         <v>546</v>
       </c>
-      <c r="F7" s="185" t="s">
+      <c r="F7" s="188" t="s">
         <v>547</v>
       </c>
-      <c r="G7" s="186" t="s">
+      <c r="G7" s="189" t="s">
         <v>197</v>
       </c>
       <c r="H7" s="24" t="s">
@@ -8014,23 +8087,23 @@
         <v>275</v>
       </c>
       <c r="K7" s="50"/>
-      <c r="L7" s="92" t="s">
+      <c r="L7" s="91" t="s">
         <v>611</v>
       </c>
-      <c r="M7" s="126" t="s">
+      <c r="M7" s="125" t="s">
         <v>612</v>
       </c>
       <c r="N7" s="50"/>
-      <c r="O7" s="114"/>
+      <c r="O7" s="113"/>
     </row>
     <row r="8" spans="1:18" ht="53.55" customHeight="1">
       <c r="A8" s="50"/>
-      <c r="B8" s="147"/>
-      <c r="C8" s="145"/>
-      <c r="D8" s="145"/>
-      <c r="E8" s="184"/>
-      <c r="F8" s="185"/>
-      <c r="G8" s="186"/>
+      <c r="B8" s="155"/>
+      <c r="C8" s="153"/>
+      <c r="D8" s="153"/>
+      <c r="E8" s="187"/>
+      <c r="F8" s="188"/>
+      <c r="G8" s="189"/>
       <c r="H8" s="24" t="s">
         <v>320</v>
       </c>
@@ -8044,11 +8117,11 @@
       <c r="L8" s="50"/>
       <c r="M8" s="50"/>
       <c r="N8" s="50"/>
-      <c r="O8" s="115"/>
+      <c r="O8" s="114"/>
     </row>
     <row r="9" spans="1:18" ht="57.6">
       <c r="A9" s="50"/>
-      <c r="B9" s="147"/>
+      <c r="B9" s="155"/>
       <c r="C9" s="4" t="s">
         <v>306</v>
       </c>
@@ -8081,11 +8154,11 @@
     </row>
     <row r="10" spans="1:18" ht="58.05" customHeight="1">
       <c r="A10" s="50"/>
-      <c r="B10" s="147"/>
-      <c r="C10" s="177" t="s">
+      <c r="B10" s="155"/>
+      <c r="C10" s="186" t="s">
         <v>307</v>
       </c>
-      <c r="D10" s="140" t="s">
+      <c r="D10" s="148" t="s">
         <v>439</v>
       </c>
       <c r="E10" s="2" t="s">
@@ -8114,9 +8187,9 @@
     </row>
     <row r="11" spans="1:18" ht="43.2">
       <c r="A11" s="50"/>
-      <c r="B11" s="147"/>
-      <c r="C11" s="177"/>
-      <c r="D11" s="142"/>
+      <c r="B11" s="155"/>
+      <c r="C11" s="186"/>
+      <c r="D11" s="149"/>
       <c r="E11" s="2" t="s">
         <v>392</v>
       </c>
@@ -8143,11 +8216,11 @@
     </row>
     <row r="12" spans="1:18" ht="52.05" customHeight="1">
       <c r="A12" s="50"/>
-      <c r="B12" s="147"/>
-      <c r="C12" s="146" t="s">
+      <c r="B12" s="155"/>
+      <c r="C12" s="154" t="s">
         <v>308</v>
       </c>
-      <c r="D12" s="177" t="s">
+      <c r="D12" s="186" t="s">
         <v>440</v>
       </c>
       <c r="E12" s="2" t="s">
@@ -8175,9 +8248,9 @@
     </row>
     <row r="13" spans="1:18" ht="58.5" customHeight="1">
       <c r="A13" s="50"/>
-      <c r="B13" s="147"/>
-      <c r="C13" s="147"/>
-      <c r="D13" s="177"/>
+      <c r="B13" s="155"/>
+      <c r="C13" s="155"/>
+      <c r="D13" s="186"/>
       <c r="E13" s="2" t="s">
         <v>401</v>
       </c>
@@ -8203,8 +8276,8 @@
     </row>
     <row r="14" spans="1:18" ht="53.55" customHeight="1">
       <c r="A14" s="50"/>
-      <c r="B14" s="147"/>
-      <c r="C14" s="148"/>
+      <c r="B14" s="155"/>
+      <c r="C14" s="156"/>
       <c r="D14" s="3" t="s">
         <v>441</v>
       </c>
@@ -8228,11 +8301,11 @@
       </c>
     </row>
     <row r="15" spans="1:18" ht="66" customHeight="1">
-      <c r="B15" s="147"/>
-      <c r="C15" s="145" t="s">
+      <c r="B15" s="155"/>
+      <c r="C15" s="153" t="s">
         <v>315</v>
       </c>
-      <c r="D15" s="146" t="s">
+      <c r="D15" s="154" t="s">
         <v>442</v>
       </c>
       <c r="E15" s="24" t="s">
@@ -8255,9 +8328,9 @@
       </c>
     </row>
     <row r="16" spans="1:18" ht="43.2">
-      <c r="B16" s="147"/>
-      <c r="C16" s="145"/>
-      <c r="D16" s="148"/>
+      <c r="B16" s="155"/>
+      <c r="C16" s="153"/>
+      <c r="D16" s="156"/>
       <c r="E16" s="24" t="s">
         <v>407</v>
       </c>
@@ -8278,11 +8351,11 @@
       </c>
     </row>
     <row r="17" spans="2:10" ht="77.55" customHeight="1">
-      <c r="B17" s="147"/>
-      <c r="C17" s="140" t="s">
+      <c r="B17" s="155"/>
+      <c r="C17" s="148" t="s">
         <v>316</v>
       </c>
-      <c r="D17" s="146" t="s">
+      <c r="D17" s="154" t="s">
         <v>443</v>
       </c>
       <c r="E17" s="74" t="s">
@@ -8305,9 +8378,9 @@
       </c>
     </row>
     <row r="18" spans="2:10" ht="57.6">
-      <c r="B18" s="147"/>
-      <c r="C18" s="142"/>
-      <c r="D18" s="148"/>
+      <c r="B18" s="155"/>
+      <c r="C18" s="149"/>
+      <c r="D18" s="156"/>
       <c r="E18" s="72" t="s">
         <v>413</v>
       </c>
@@ -8328,8 +8401,8 @@
       </c>
     </row>
     <row r="19" spans="2:10" ht="42" customHeight="1">
-      <c r="B19" s="147"/>
-      <c r="C19" s="177" t="s">
+      <c r="B19" s="155"/>
+      <c r="C19" s="186" t="s">
         <v>323</v>
       </c>
       <c r="D19" s="3" t="s">
@@ -8355,8 +8428,8 @@
       </c>
     </row>
     <row r="20" spans="2:10" ht="39" customHeight="1">
-      <c r="B20" s="147"/>
-      <c r="C20" s="177"/>
+      <c r="B20" s="155"/>
+      <c r="C20" s="186"/>
       <c r="D20" s="3" t="s">
         <v>445</v>
       </c>
@@ -8380,11 +8453,11 @@
       </c>
     </row>
     <row r="21" spans="2:10" ht="43.2">
-      <c r="B21" s="147"/>
-      <c r="C21" s="145" t="s">
+      <c r="B21" s="155"/>
+      <c r="C21" s="153" t="s">
         <v>326</v>
       </c>
-      <c r="D21" s="146" t="s">
+      <c r="D21" s="154" t="s">
         <v>446</v>
       </c>
       <c r="E21" s="65" t="s">
@@ -8407,9 +8480,9 @@
       </c>
     </row>
     <row r="22" spans="2:10" ht="41.55" customHeight="1">
-      <c r="B22" s="147"/>
-      <c r="C22" s="145"/>
-      <c r="D22" s="148"/>
+      <c r="B22" s="155"/>
+      <c r="C22" s="153"/>
+      <c r="D22" s="156"/>
       <c r="E22" s="24" t="s">
         <v>427</v>
       </c>
@@ -8430,7 +8503,7 @@
       </c>
     </row>
     <row r="23" spans="2:10" ht="57.6">
-      <c r="B23" s="147"/>
+      <c r="B23" s="155"/>
       <c r="C23" s="4" t="s">
         <v>330</v>
       </c>
@@ -8457,8 +8530,8 @@
       </c>
     </row>
     <row r="24" spans="2:10" ht="43.2">
-      <c r="B24" s="147"/>
-      <c r="C24" s="177" t="s">
+      <c r="B24" s="155"/>
+      <c r="C24" s="186" t="s">
         <v>333</v>
       </c>
       <c r="D24" s="3" t="s">
@@ -8476,7 +8549,7 @@
       <c r="H24" s="2" t="s">
         <v>331</v>
       </c>
-      <c r="I24" s="85" t="s">
+      <c r="I24" s="84" t="s">
         <v>586</v>
       </c>
       <c r="J24" s="61" t="s">
@@ -8484,8 +8557,8 @@
       </c>
     </row>
     <row r="25" spans="2:10" ht="43.2">
-      <c r="B25" s="148"/>
-      <c r="C25" s="177"/>
+      <c r="B25" s="156"/>
+      <c r="C25" s="186"/>
       <c r="D25" s="3" t="s">
         <v>447</v>
       </c>
@@ -8513,6 +8586,20 @@
     </row>
   </sheetData>
   <mergeCells count="30">
+    <mergeCell ref="R3:R5"/>
+    <mergeCell ref="N3:N5"/>
+    <mergeCell ref="L2:M2"/>
+    <mergeCell ref="O3:O5"/>
+    <mergeCell ref="P3:P5"/>
+    <mergeCell ref="Q3:Q5"/>
+    <mergeCell ref="J4:J5"/>
+    <mergeCell ref="L3:M5"/>
+    <mergeCell ref="E4:E5"/>
+    <mergeCell ref="H4:H5"/>
+    <mergeCell ref="D7:D8"/>
+    <mergeCell ref="E7:E8"/>
+    <mergeCell ref="F7:F8"/>
+    <mergeCell ref="G7:G8"/>
     <mergeCell ref="B4:B25"/>
     <mergeCell ref="D10:D11"/>
     <mergeCell ref="D12:D13"/>
@@ -8529,45 +8616,31 @@
     <mergeCell ref="C17:C18"/>
     <mergeCell ref="C19:C20"/>
     <mergeCell ref="C7:C8"/>
-    <mergeCell ref="J4:J5"/>
-    <mergeCell ref="L3:M5"/>
-    <mergeCell ref="E4:E5"/>
-    <mergeCell ref="H4:H5"/>
-    <mergeCell ref="D7:D8"/>
-    <mergeCell ref="E7:E8"/>
-    <mergeCell ref="F7:F8"/>
-    <mergeCell ref="G7:G8"/>
-    <mergeCell ref="R3:R5"/>
-    <mergeCell ref="N3:N5"/>
-    <mergeCell ref="L2:M2"/>
-    <mergeCell ref="O3:O5"/>
-    <mergeCell ref="P3:P5"/>
-    <mergeCell ref="Q3:Q5"/>
   </mergeCells>
   <conditionalFormatting sqref="B3:E3">
-    <cfRule type="expression" dxfId="28" priority="11">
+    <cfRule type="expression" dxfId="32" priority="11">
       <formula>$A3="header"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:J3">
-    <cfRule type="expression" dxfId="27" priority="5">
+    <cfRule type="expression" dxfId="31" priority="5">
       <formula>$A3="header"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="26" priority="6">
+    <cfRule type="expression" dxfId="30" priority="6">
       <formula>$A3="blank"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J4 J6:J26">
-    <cfRule type="cellIs" dxfId="25" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="29" priority="1" operator="equal">
       <formula>"N/A"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="24" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="28" priority="2" operator="equal">
       <formula>"N/A"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="23" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="27" priority="3" operator="equal">
       <formula>"No"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="22" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="26" priority="4" operator="equal">
       <formula>"Yes"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8622,11 +8695,11 @@
       <c r="I2" s="50"/>
       <c r="J2" s="50"/>
       <c r="K2" s="50"/>
-      <c r="L2" s="163" t="s">
+      <c r="L2" s="175" t="s">
         <v>279</v>
       </c>
-      <c r="M2" s="164"/>
-      <c r="N2" s="117" t="s">
+      <c r="M2" s="176"/>
+      <c r="N2" s="116" t="s">
         <v>601</v>
       </c>
       <c r="O2" s="58" t="s">
@@ -8672,41 +8745,41 @@
         <v>272</v>
       </c>
       <c r="K3" s="50"/>
-      <c r="L3" s="153">
+      <c r="L3" s="166">
         <f>COUNTA(H4:H25)</f>
         <v>11</v>
       </c>
-      <c r="M3" s="165"/>
-      <c r="N3" s="181">
+      <c r="M3" s="177"/>
+      <c r="N3" s="190">
         <f>L3-Q3</f>
         <v>8</v>
       </c>
-      <c r="O3" s="168">
+      <c r="O3" s="180">
         <f>COUNTIF(J4:J25,"Yes")</f>
-        <v>4</v>
-      </c>
-      <c r="P3" s="171">
+        <v>7</v>
+      </c>
+      <c r="P3" s="159">
         <f>COUNTIF(J4:J25,"No")</f>
-        <v>4</v>
-      </c>
-      <c r="Q3" s="174">
+        <v>1</v>
+      </c>
+      <c r="Q3" s="162">
         <f>COUNTIF(J4:J25,"N/A")</f>
         <v>3</v>
       </c>
-      <c r="R3" s="156">
+      <c r="R3" s="169">
         <f>O3/N3</f>
-        <v>0.5</v>
+        <v>0.875</v>
       </c>
     </row>
     <row r="4" spans="1:20" ht="120" customHeight="1" thickBot="1">
       <c r="A4" s="50"/>
-      <c r="B4" s="145" t="s">
+      <c r="B4" s="153" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="145" t="s">
+      <c r="C4" s="153" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="190" t="s">
+      <c r="D4" s="196" t="s">
         <v>343</v>
       </c>
       <c r="E4" s="8" t="s">
@@ -8718,35 +8791,35 @@
       <c r="G4" s="30" t="s">
         <v>152</v>
       </c>
-      <c r="H4" s="190" t="s">
+      <c r="H4" s="196" t="s">
         <v>346</v>
       </c>
-      <c r="I4" s="187" t="s">
+      <c r="I4" s="197" t="s">
         <v>525</v>
       </c>
-      <c r="J4" s="145" t="s">
+      <c r="J4" s="153" t="s">
         <v>274</v>
       </c>
       <c r="K4" s="50"/>
-      <c r="L4" s="154"/>
-      <c r="M4" s="166"/>
-      <c r="N4" s="182"/>
-      <c r="O4" s="169"/>
-      <c r="P4" s="172"/>
-      <c r="Q4" s="175"/>
-      <c r="R4" s="157"/>
-      <c r="S4" s="92" t="s">
+      <c r="L4" s="167"/>
+      <c r="M4" s="178"/>
+      <c r="N4" s="191"/>
+      <c r="O4" s="181"/>
+      <c r="P4" s="160"/>
+      <c r="Q4" s="163"/>
+      <c r="R4" s="170"/>
+      <c r="S4" s="91" t="s">
         <v>611</v>
       </c>
-      <c r="T4" s="126" t="s">
+      <c r="T4" s="125" t="s">
         <v>613</v>
       </c>
     </row>
     <row r="5" spans="1:20" ht="169.05" customHeight="1" thickBot="1">
       <c r="A5" s="50"/>
-      <c r="B5" s="145"/>
-      <c r="C5" s="145"/>
-      <c r="D5" s="190"/>
+      <c r="B5" s="153"/>
+      <c r="C5" s="153"/>
+      <c r="D5" s="196"/>
       <c r="E5" s="8" t="s">
         <v>347</v>
       </c>
@@ -8756,23 +8829,23 @@
       <c r="G5" s="30" t="s">
         <v>154</v>
       </c>
-      <c r="H5" s="190"/>
-      <c r="I5" s="188"/>
-      <c r="J5" s="145"/>
+      <c r="H5" s="196"/>
+      <c r="I5" s="198"/>
+      <c r="J5" s="153"/>
       <c r="K5" s="50"/>
-      <c r="L5" s="155"/>
-      <c r="M5" s="167"/>
-      <c r="N5" s="183"/>
-      <c r="O5" s="170"/>
-      <c r="P5" s="173"/>
-      <c r="Q5" s="176"/>
-      <c r="R5" s="158"/>
+      <c r="L5" s="168"/>
+      <c r="M5" s="179"/>
+      <c r="N5" s="192"/>
+      <c r="O5" s="182"/>
+      <c r="P5" s="161"/>
+      <c r="Q5" s="164"/>
+      <c r="R5" s="171"/>
     </row>
     <row r="6" spans="1:20" ht="141" customHeight="1">
       <c r="A6" s="50"/>
-      <c r="B6" s="145"/>
-      <c r="C6" s="145"/>
-      <c r="D6" s="190"/>
+      <c r="B6" s="153"/>
+      <c r="C6" s="153"/>
+      <c r="D6" s="196"/>
       <c r="E6" s="8" t="s">
         <v>349</v>
       </c>
@@ -8782,13 +8855,13 @@
       <c r="G6" s="30" t="s">
         <v>153</v>
       </c>
-      <c r="H6" s="190" t="s">
+      <c r="H6" s="196" t="s">
         <v>351</v>
       </c>
-      <c r="I6" s="187" t="s">
+      <c r="I6" s="197" t="s">
         <v>526</v>
       </c>
-      <c r="J6" s="145" t="s">
+      <c r="J6" s="153" t="s">
         <v>275</v>
       </c>
       <c r="K6" s="50"/>
@@ -8799,9 +8872,9 @@
     </row>
     <row r="7" spans="1:20" ht="151.94999999999999" customHeight="1">
       <c r="A7" s="50"/>
-      <c r="B7" s="145"/>
-      <c r="C7" s="145"/>
-      <c r="D7" s="190"/>
+      <c r="B7" s="153"/>
+      <c r="C7" s="153"/>
+      <c r="D7" s="196"/>
       <c r="E7" s="27" t="s">
         <v>352</v>
       </c>
@@ -8811,20 +8884,20 @@
       <c r="G7" s="30" t="s">
         <v>155</v>
       </c>
-      <c r="H7" s="190"/>
-      <c r="I7" s="188"/>
-      <c r="J7" s="145"/>
+      <c r="H7" s="196"/>
+      <c r="I7" s="198"/>
+      <c r="J7" s="153"/>
       <c r="K7" s="50"/>
       <c r="L7" s="50"/>
       <c r="M7" s="50"/>
       <c r="N7" s="50"/>
-      <c r="O7" s="114"/>
+      <c r="O7" s="113"/>
     </row>
     <row r="8" spans="1:20" ht="109.5" customHeight="1">
       <c r="A8" s="50"/>
-      <c r="B8" s="145"/>
-      <c r="C8" s="145"/>
-      <c r="D8" s="149" t="s">
+      <c r="B8" s="153"/>
+      <c r="C8" s="153"/>
+      <c r="D8" s="157" t="s">
         <v>5</v>
       </c>
       <c r="E8" s="27" t="s">
@@ -8836,23 +8909,23 @@
       <c r="G8" s="30" t="s">
         <v>156</v>
       </c>
-      <c r="H8" s="149" t="s">
+      <c r="H8" s="157" t="s">
         <v>269</v>
       </c>
-      <c r="I8" s="140" t="s">
+      <c r="I8" s="148" t="s">
         <v>527</v>
       </c>
-      <c r="J8" s="145" t="s">
+      <c r="J8" s="153" t="s">
         <v>274</v>
       </c>
       <c r="K8" s="50"/>
-      <c r="O8" s="115"/>
+      <c r="O8" s="114"/>
     </row>
     <row r="9" spans="1:20" ht="136.05000000000001" customHeight="1">
       <c r="A9" s="50"/>
-      <c r="B9" s="145"/>
-      <c r="C9" s="145"/>
-      <c r="D9" s="149"/>
+      <c r="B9" s="153"/>
+      <c r="C9" s="153"/>
+      <c r="D9" s="157"/>
       <c r="E9" s="27" t="s">
         <v>356</v>
       </c>
@@ -8862,18 +8935,18 @@
       <c r="G9" s="30" t="s">
         <v>157</v>
       </c>
-      <c r="H9" s="149"/>
-      <c r="I9" s="142"/>
-      <c r="J9" s="145"/>
+      <c r="H9" s="157"/>
+      <c r="I9" s="149"/>
+      <c r="J9" s="153"/>
       <c r="K9" s="50"/>
     </row>
     <row r="10" spans="1:20" ht="132.44999999999999" customHeight="1">
       <c r="A10" s="50"/>
-      <c r="B10" s="145"/>
-      <c r="C10" s="145" t="s">
+      <c r="B10" s="153"/>
+      <c r="C10" s="153" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="149" t="s">
+      <c r="D10" s="157" t="s">
         <v>358</v>
       </c>
       <c r="E10" s="27" t="s">
@@ -8885,22 +8958,22 @@
       <c r="G10" s="30" t="s">
         <v>160</v>
       </c>
-      <c r="H10" s="190" t="s">
+      <c r="H10" s="196" t="s">
         <v>528</v>
       </c>
-      <c r="I10" s="187" t="s">
+      <c r="I10" s="197" t="s">
         <v>529</v>
       </c>
-      <c r="J10" s="145" t="s">
-        <v>273</v>
+      <c r="J10" s="153" t="s">
+        <v>275</v>
       </c>
       <c r="K10" s="50"/>
     </row>
     <row r="11" spans="1:20" ht="138.44999999999999" customHeight="1">
       <c r="A11" s="50"/>
-      <c r="B11" s="145"/>
-      <c r="C11" s="145"/>
-      <c r="D11" s="149"/>
+      <c r="B11" s="153"/>
+      <c r="C11" s="153"/>
+      <c r="D11" s="157"/>
       <c r="E11" s="31" t="s">
         <v>361</v>
       </c>
@@ -8910,16 +8983,16 @@
       <c r="G11" s="30" t="s">
         <v>163</v>
       </c>
-      <c r="H11" s="190"/>
-      <c r="I11" s="188"/>
-      <c r="J11" s="145"/>
+      <c r="H11" s="196"/>
+      <c r="I11" s="198"/>
+      <c r="J11" s="153"/>
       <c r="K11" s="50"/>
     </row>
     <row r="12" spans="1:20" ht="121.5" customHeight="1">
       <c r="A12" s="50"/>
-      <c r="B12" s="145"/>
-      <c r="C12" s="145"/>
-      <c r="D12" s="149" t="s">
+      <c r="B12" s="153"/>
+      <c r="C12" s="153"/>
+      <c r="D12" s="157" t="s">
         <v>307</v>
       </c>
       <c r="E12" s="31" t="s">
@@ -8931,22 +9004,22 @@
       <c r="G12" s="30" t="s">
         <v>162</v>
       </c>
-      <c r="H12" s="190" t="s">
+      <c r="H12" s="196" t="s">
         <v>342</v>
       </c>
-      <c r="I12" s="187" t="s">
+      <c r="I12" s="197" t="s">
         <v>530</v>
       </c>
-      <c r="J12" s="145" t="s">
+      <c r="J12" s="153" t="s">
         <v>274</v>
       </c>
       <c r="K12" s="50"/>
     </row>
     <row r="13" spans="1:20" ht="154.5" customHeight="1">
       <c r="A13" s="50"/>
-      <c r="B13" s="145"/>
-      <c r="C13" s="145"/>
-      <c r="D13" s="149"/>
+      <c r="B13" s="153"/>
+      <c r="C13" s="153"/>
+      <c r="D13" s="157"/>
       <c r="E13" s="31" t="s">
         <v>364</v>
       </c>
@@ -8956,15 +9029,15 @@
       <c r="G13" s="30" t="s">
         <v>164</v>
       </c>
-      <c r="H13" s="190"/>
-      <c r="I13" s="192"/>
-      <c r="J13" s="145"/>
+      <c r="H13" s="196"/>
+      <c r="I13" s="199"/>
+      <c r="J13" s="153"/>
       <c r="K13" s="50"/>
     </row>
     <row r="14" spans="1:20" ht="144.44999999999999" customHeight="1">
       <c r="A14" s="50"/>
-      <c r="B14" s="145"/>
-      <c r="C14" s="145"/>
+      <c r="B14" s="153"/>
+      <c r="C14" s="153"/>
       <c r="D14" s="24" t="s">
         <v>18</v>
       </c>
@@ -8977,25 +9050,25 @@
       <c r="G14" s="30" t="s">
         <v>170</v>
       </c>
-      <c r="H14" s="190"/>
-      <c r="I14" s="188"/>
-      <c r="J14" s="145"/>
+      <c r="H14" s="196"/>
+      <c r="I14" s="198"/>
+      <c r="J14" s="153"/>
       <c r="K14" s="50"/>
     </row>
     <row r="15" spans="1:20" ht="52.95" customHeight="1">
       <c r="A15" s="50"/>
-      <c r="B15" s="145"/>
-      <c r="C15" s="145"/>
-      <c r="D15" s="145" t="s">
+      <c r="B15" s="153"/>
+      <c r="C15" s="153"/>
+      <c r="D15" s="153" t="s">
         <v>17</v>
       </c>
       <c r="E15" s="193" t="s">
         <v>369</v>
       </c>
-      <c r="F15" s="191" t="s">
+      <c r="F15" s="194" t="s">
         <v>370</v>
       </c>
-      <c r="G15" s="194" t="s">
+      <c r="G15" s="195" t="s">
         <v>169</v>
       </c>
       <c r="H15" s="24" t="s">
@@ -9011,12 +9084,12 @@
     </row>
     <row r="16" spans="1:20" ht="91.05" customHeight="1">
       <c r="A16" s="50"/>
-      <c r="B16" s="145"/>
-      <c r="C16" s="145"/>
-      <c r="D16" s="145"/>
+      <c r="B16" s="153"/>
+      <c r="C16" s="153"/>
+      <c r="D16" s="153"/>
       <c r="E16" s="193"/>
-      <c r="F16" s="191"/>
-      <c r="G16" s="194"/>
+      <c r="F16" s="194"/>
+      <c r="G16" s="195"/>
       <c r="H16" s="70" t="s">
         <v>532</v>
       </c>
@@ -9030,8 +9103,8 @@
     </row>
     <row r="17" spans="1:15" ht="124.05" customHeight="1">
       <c r="A17" s="50"/>
-      <c r="B17" s="145"/>
-      <c r="C17" s="145"/>
+      <c r="B17" s="153"/>
+      <c r="C17" s="153"/>
       <c r="D17" s="60" t="s">
         <v>368</v>
       </c>
@@ -9044,21 +9117,21 @@
       <c r="G17" s="30" t="s">
         <v>175</v>
       </c>
-      <c r="H17" s="190" t="s">
+      <c r="H17" s="196" t="s">
         <v>371</v>
       </c>
-      <c r="I17" s="187" t="s">
+      <c r="I17" s="197" t="s">
         <v>534</v>
       </c>
-      <c r="J17" s="145" t="s">
+      <c r="J17" s="153" t="s">
         <v>273</v>
       </c>
       <c r="K17" s="50"/>
     </row>
     <row r="18" spans="1:15" ht="123" customHeight="1">
       <c r="A18" s="50"/>
-      <c r="B18" s="145"/>
-      <c r="C18" s="145"/>
+      <c r="B18" s="153"/>
+      <c r="C18" s="153"/>
       <c r="D18" s="24" t="s">
         <v>19</v>
       </c>
@@ -9071,16 +9144,16 @@
       <c r="G18" s="30" t="s">
         <v>171</v>
       </c>
-      <c r="H18" s="190"/>
-      <c r="I18" s="188"/>
-      <c r="J18" s="145"/>
+      <c r="H18" s="196"/>
+      <c r="I18" s="198"/>
+      <c r="J18" s="153"/>
       <c r="K18" s="50"/>
     </row>
     <row r="19" spans="1:15" ht="118.05" customHeight="1">
       <c r="A19" s="50"/>
-      <c r="B19" s="145"/>
-      <c r="C19" s="145"/>
-      <c r="D19" s="149" t="s">
+      <c r="B19" s="153"/>
+      <c r="C19" s="153"/>
+      <c r="D19" s="157" t="s">
         <v>25</v>
       </c>
       <c r="E19" s="31" t="s">
@@ -9092,13 +9165,13 @@
       <c r="G19" s="30" t="s">
         <v>168</v>
       </c>
-      <c r="H19" s="189" t="s">
+      <c r="H19" s="200" t="s">
         <v>376</v>
       </c>
-      <c r="I19" s="187" t="s">
+      <c r="I19" s="197" t="s">
         <v>535</v>
       </c>
-      <c r="J19" s="145" t="s">
+      <c r="J19" s="153" t="s">
         <v>275</v>
       </c>
       <c r="K19" s="50"/>
@@ -9107,9 +9180,9 @@
     </row>
     <row r="20" spans="1:15" ht="123" customHeight="1">
       <c r="A20" s="50"/>
-      <c r="B20" s="145"/>
-      <c r="C20" s="145"/>
-      <c r="D20" s="149"/>
+      <c r="B20" s="153"/>
+      <c r="C20" s="153"/>
+      <c r="D20" s="157"/>
       <c r="E20" s="31" t="s">
         <v>30</v>
       </c>
@@ -9119,9 +9192,9 @@
       <c r="G20" s="30" t="s">
         <v>176</v>
       </c>
-      <c r="H20" s="189"/>
-      <c r="I20" s="192"/>
-      <c r="J20" s="145"/>
+      <c r="H20" s="200"/>
+      <c r="I20" s="199"/>
+      <c r="J20" s="153"/>
       <c r="K20" s="51"/>
       <c r="L20" s="45"/>
       <c r="M20" s="45"/>
@@ -9130,9 +9203,9 @@
     </row>
     <row r="21" spans="1:15" ht="106.05" customHeight="1">
       <c r="A21" s="50"/>
-      <c r="B21" s="145"/>
-      <c r="C21" s="145"/>
-      <c r="D21" s="149"/>
+      <c r="B21" s="153"/>
+      <c r="C21" s="153"/>
+      <c r="D21" s="157"/>
       <c r="E21" s="31" t="s">
         <v>26</v>
       </c>
@@ -9142,59 +9215,59 @@
       <c r="G21" s="30" t="s">
         <v>174</v>
       </c>
-      <c r="H21" s="189"/>
-      <c r="I21" s="188"/>
-      <c r="J21" s="145"/>
+      <c r="H21" s="200"/>
+      <c r="I21" s="198"/>
+      <c r="J21" s="153"/>
       <c r="K21" s="50"/>
     </row>
     <row r="22" spans="1:15" ht="78" customHeight="1">
       <c r="A22" s="50"/>
-      <c r="B22" s="145"/>
-      <c r="C22" s="145" t="s">
+      <c r="B22" s="153"/>
+      <c r="C22" s="153" t="s">
         <v>24</v>
       </c>
-      <c r="D22" s="145" t="s">
+      <c r="D22" s="153" t="s">
         <v>32</v>
       </c>
       <c r="E22" s="193" t="s">
         <v>33</v>
       </c>
-      <c r="F22" s="191" t="s">
+      <c r="F22" s="194" t="s">
         <v>34</v>
       </c>
       <c r="G22" s="30" t="s">
         <v>177</v>
       </c>
-      <c r="H22" s="190" t="s">
+      <c r="H22" s="196" t="s">
         <v>341</v>
       </c>
-      <c r="I22" s="187" t="s">
+      <c r="I22" s="197" t="s">
         <v>536</v>
       </c>
-      <c r="J22" s="145" t="s">
-        <v>273</v>
+      <c r="J22" s="153" t="s">
+        <v>275</v>
       </c>
       <c r="K22" s="50"/>
     </row>
     <row r="23" spans="1:15" ht="72">
       <c r="A23" s="50"/>
-      <c r="B23" s="145"/>
-      <c r="C23" s="145"/>
-      <c r="D23" s="145"/>
+      <c r="B23" s="153"/>
+      <c r="C23" s="153"/>
+      <c r="D23" s="153"/>
       <c r="E23" s="193"/>
-      <c r="F23" s="191"/>
+      <c r="F23" s="194"/>
       <c r="G23" s="30" t="s">
         <v>158</v>
       </c>
-      <c r="H23" s="190"/>
-      <c r="I23" s="192"/>
-      <c r="J23" s="145"/>
+      <c r="H23" s="196"/>
+      <c r="I23" s="199"/>
+      <c r="J23" s="153"/>
       <c r="K23" s="50"/>
     </row>
     <row r="24" spans="1:15" ht="72">
       <c r="A24" s="50"/>
-      <c r="B24" s="145"/>
-      <c r="C24" s="145"/>
+      <c r="B24" s="153"/>
+      <c r="C24" s="153"/>
       <c r="D24" s="24" t="s">
         <v>12</v>
       </c>
@@ -9207,15 +9280,15 @@
       <c r="G24" s="30" t="s">
         <v>166</v>
       </c>
-      <c r="H24" s="190"/>
-      <c r="I24" s="188"/>
-      <c r="J24" s="145"/>
+      <c r="H24" s="196"/>
+      <c r="I24" s="198"/>
+      <c r="J24" s="153"/>
       <c r="K24" s="50"/>
     </row>
     <row r="25" spans="1:15" ht="100.8">
       <c r="A25" s="50"/>
-      <c r="B25" s="145"/>
-      <c r="C25" s="145"/>
+      <c r="B25" s="153"/>
+      <c r="C25" s="153"/>
       <c r="D25" s="2" t="s">
         <v>17</v>
       </c>
@@ -9234,8 +9307,8 @@
       <c r="I25" s="2" t="s">
         <v>537</v>
       </c>
-      <c r="J25" s="4" t="s">
-        <v>273</v>
+      <c r="J25" s="127" t="s">
+        <v>275</v>
       </c>
       <c r="K25" s="50"/>
     </row>
@@ -9254,6 +9327,37 @@
     </row>
   </sheetData>
   <mergeCells count="47">
+    <mergeCell ref="O3:O5"/>
+    <mergeCell ref="N3:N5"/>
+    <mergeCell ref="R3:R5"/>
+    <mergeCell ref="I8:I9"/>
+    <mergeCell ref="I10:I11"/>
+    <mergeCell ref="C4:C9"/>
+    <mergeCell ref="H19:H21"/>
+    <mergeCell ref="H22:H24"/>
+    <mergeCell ref="D19:D21"/>
+    <mergeCell ref="F22:F23"/>
+    <mergeCell ref="C10:C21"/>
+    <mergeCell ref="D4:D7"/>
+    <mergeCell ref="D8:D9"/>
+    <mergeCell ref="J19:J21"/>
+    <mergeCell ref="J22:J24"/>
+    <mergeCell ref="D10:D11"/>
+    <mergeCell ref="H10:H11"/>
+    <mergeCell ref="D12:D13"/>
+    <mergeCell ref="H12:H14"/>
+    <mergeCell ref="I12:I14"/>
+    <mergeCell ref="I22:I24"/>
+    <mergeCell ref="I19:I21"/>
+    <mergeCell ref="I17:I18"/>
+    <mergeCell ref="L2:M2"/>
+    <mergeCell ref="L3:M5"/>
+    <mergeCell ref="H6:H7"/>
+    <mergeCell ref="H4:H5"/>
+    <mergeCell ref="J4:J5"/>
+    <mergeCell ref="J6:J7"/>
+    <mergeCell ref="I4:I5"/>
+    <mergeCell ref="I6:I7"/>
     <mergeCell ref="B4:B25"/>
     <mergeCell ref="C22:C25"/>
     <mergeCell ref="P3:P5"/>
@@ -9270,92 +9374,61 @@
     <mergeCell ref="J10:J11"/>
     <mergeCell ref="J12:J14"/>
     <mergeCell ref="J17:J18"/>
-    <mergeCell ref="L2:M2"/>
-    <mergeCell ref="L3:M5"/>
-    <mergeCell ref="H6:H7"/>
-    <mergeCell ref="H4:H5"/>
-    <mergeCell ref="J4:J5"/>
-    <mergeCell ref="J6:J7"/>
-    <mergeCell ref="I4:I5"/>
-    <mergeCell ref="I6:I7"/>
-    <mergeCell ref="J19:J21"/>
-    <mergeCell ref="J22:J24"/>
-    <mergeCell ref="D10:D11"/>
-    <mergeCell ref="H10:H11"/>
-    <mergeCell ref="D12:D13"/>
-    <mergeCell ref="H12:H14"/>
-    <mergeCell ref="I12:I14"/>
-    <mergeCell ref="I22:I24"/>
-    <mergeCell ref="I19:I21"/>
-    <mergeCell ref="I17:I18"/>
-    <mergeCell ref="C4:C9"/>
-    <mergeCell ref="H19:H21"/>
-    <mergeCell ref="H22:H24"/>
-    <mergeCell ref="D19:D21"/>
-    <mergeCell ref="F22:F23"/>
-    <mergeCell ref="C10:C21"/>
-    <mergeCell ref="D4:D7"/>
-    <mergeCell ref="D8:D9"/>
-    <mergeCell ref="O3:O5"/>
-    <mergeCell ref="N3:N5"/>
-    <mergeCell ref="R3:R5"/>
-    <mergeCell ref="I8:I9"/>
-    <mergeCell ref="I10:I11"/>
   </mergeCells>
   <conditionalFormatting sqref="B3:D3 E3:E4">
-    <cfRule type="expression" dxfId="21" priority="11">
+    <cfRule type="expression" dxfId="25" priority="11">
       <formula>$A3="header"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:J3">
-    <cfRule type="expression" dxfId="20" priority="5">
+    <cfRule type="expression" dxfId="24" priority="5">
       <formula>$A3="header"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="19" priority="6">
+    <cfRule type="expression" dxfId="23" priority="6">
       <formula>$A3="blank"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E5">
-    <cfRule type="expression" dxfId="18" priority="18">
+    <cfRule type="expression" dxfId="22" priority="18">
       <formula>$A6="header"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="17" priority="19">
+    <cfRule type="expression" dxfId="21" priority="19">
       <formula>$A6="header"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="16" priority="20">
+    <cfRule type="expression" dxfId="20" priority="20">
       <formula>$A6="blank"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E6">
-    <cfRule type="expression" dxfId="15" priority="13">
+    <cfRule type="expression" dxfId="19" priority="13">
       <formula>$A5="header"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="14" priority="16">
+    <cfRule type="expression" dxfId="18" priority="16">
       <formula>$A5="header"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="13" priority="17">
+    <cfRule type="expression" dxfId="17" priority="17">
       <formula>$A5="blank"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:F4">
-    <cfRule type="expression" dxfId="12" priority="9">
+    <cfRule type="expression" dxfId="16" priority="9">
       <formula>$A4="header"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="11" priority="10">
+    <cfRule type="expression" dxfId="15" priority="10">
       <formula>$A4="blank"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J4 J6 J8 J10 J12 J15:J17 J19 J22 J25">
-    <cfRule type="cellIs" dxfId="10" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">
       <formula>"N/A"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="9" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="2" operator="equal">
       <formula>"N/A"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="8" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="3" operator="equal">
       <formula>"No"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="7" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="4" operator="equal">
       <formula>"Yes"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9413,11 +9486,11 @@
       <c r="K2" s="50"/>
       <c r="L2" s="50"/>
       <c r="M2" s="50"/>
-      <c r="N2" s="163" t="s">
+      <c r="N2" s="175" t="s">
         <v>279</v>
       </c>
-      <c r="O2" s="164"/>
-      <c r="P2" s="117" t="s">
+      <c r="O2" s="176"/>
+      <c r="P2" s="116" t="s">
         <v>601</v>
       </c>
       <c r="Q2" s="58" t="s">
@@ -9465,41 +9538,41 @@
       <c r="K3" s="6"/>
       <c r="L3" s="50"/>
       <c r="M3" s="50"/>
-      <c r="N3" s="153">
+      <c r="N3" s="166">
         <f>COUNTA(H4:H13)</f>
         <v>4</v>
       </c>
-      <c r="O3" s="165"/>
-      <c r="P3" s="181">
+      <c r="O3" s="177"/>
+      <c r="P3" s="190">
         <f>N3-S3</f>
         <v>3</v>
       </c>
-      <c r="Q3" s="168">
+      <c r="Q3" s="180">
         <f>COUNTIF(J4:J10,"Yes")</f>
         <v>2</v>
       </c>
-      <c r="R3" s="171">
+      <c r="R3" s="159">
         <f>COUNTIF(J4:J10,"No")</f>
         <v>0</v>
       </c>
-      <c r="S3" s="174">
+      <c r="S3" s="162">
         <f>COUNTIF(J4:J10,"N/A")</f>
         <v>1</v>
       </c>
-      <c r="T3" s="168">
+      <c r="T3" s="180">
         <f>Q3/P3</f>
         <v>0.66666666666666663</v>
       </c>
     </row>
     <row r="4" spans="1:20" ht="78" customHeight="1">
       <c r="A4" s="50"/>
-      <c r="B4" s="145" t="s">
+      <c r="B4" s="153" t="s">
         <v>132</v>
       </c>
-      <c r="C4" s="145" t="s">
+      <c r="C4" s="153" t="s">
         <v>215</v>
       </c>
-      <c r="D4" s="145" t="s">
+      <c r="D4" s="153" t="s">
         <v>102</v>
       </c>
       <c r="E4" s="12" t="s">
@@ -9511,31 +9584,31 @@
       <c r="G4" s="10" t="s">
         <v>200</v>
       </c>
-      <c r="H4" s="149" t="s">
+      <c r="H4" s="157" t="s">
         <v>268</v>
       </c>
       <c r="I4" s="24" t="s">
         <v>544</v>
       </c>
-      <c r="J4" s="145" t="s">
+      <c r="J4" s="153" t="s">
         <v>275</v>
       </c>
       <c r="K4" s="50"/>
       <c r="L4" s="50"/>
       <c r="M4" s="50"/>
-      <c r="N4" s="154"/>
-      <c r="O4" s="166"/>
-      <c r="P4" s="182"/>
-      <c r="Q4" s="169"/>
-      <c r="R4" s="172"/>
-      <c r="S4" s="175"/>
-      <c r="T4" s="169"/>
+      <c r="N4" s="167"/>
+      <c r="O4" s="178"/>
+      <c r="P4" s="191"/>
+      <c r="Q4" s="181"/>
+      <c r="R4" s="160"/>
+      <c r="S4" s="163"/>
+      <c r="T4" s="181"/>
     </row>
     <row r="5" spans="1:20" ht="82.95" customHeight="1" thickBot="1">
       <c r="A5" s="50"/>
-      <c r="B5" s="145"/>
-      <c r="C5" s="145"/>
-      <c r="D5" s="145"/>
+      <c r="B5" s="153"/>
+      <c r="C5" s="153"/>
+      <c r="D5" s="153"/>
       <c r="E5" s="12" t="s">
         <v>107</v>
       </c>
@@ -9545,27 +9618,27 @@
       <c r="G5" s="10" t="s">
         <v>201</v>
       </c>
-      <c r="H5" s="149"/>
+      <c r="H5" s="157"/>
       <c r="I5" s="24" t="s">
         <v>545</v>
       </c>
-      <c r="J5" s="145"/>
+      <c r="J5" s="153"/>
       <c r="K5" s="50"/>
       <c r="L5" s="50"/>
       <c r="M5" s="50"/>
-      <c r="N5" s="155"/>
-      <c r="O5" s="167"/>
-      <c r="P5" s="183"/>
-      <c r="Q5" s="170"/>
-      <c r="R5" s="173"/>
-      <c r="S5" s="176"/>
-      <c r="T5" s="170"/>
+      <c r="N5" s="201"/>
+      <c r="O5" s="179"/>
+      <c r="P5" s="192"/>
+      <c r="Q5" s="182"/>
+      <c r="R5" s="161"/>
+      <c r="S5" s="164"/>
+      <c r="T5" s="182"/>
     </row>
     <row r="6" spans="1:20" ht="88.5" customHeight="1" thickBot="1">
       <c r="A6" s="50"/>
-      <c r="B6" s="145"/>
-      <c r="C6" s="145"/>
-      <c r="D6" s="145" t="s">
+      <c r="B6" s="153"/>
+      <c r="C6" s="153"/>
+      <c r="D6" s="153" t="s">
         <v>106</v>
       </c>
       <c r="E6" s="12" t="s">
@@ -9577,31 +9650,31 @@
       <c r="G6" s="10" t="s">
         <v>202</v>
       </c>
-      <c r="H6" s="143" t="s">
+      <c r="H6" s="151" t="s">
         <v>267</v>
       </c>
       <c r="I6" s="24" t="s">
         <v>538</v>
       </c>
-      <c r="J6" s="145" t="s">
+      <c r="J6" s="153" t="s">
         <v>275</v>
       </c>
       <c r="K6" s="50"/>
       <c r="L6" s="50"/>
       <c r="M6" s="50"/>
-      <c r="N6" s="92" t="s">
+      <c r="N6" s="203" t="s">
         <v>611</v>
       </c>
-      <c r="O6" s="126" t="s">
+      <c r="O6" s="202" t="s">
         <v>612</v>
       </c>
       <c r="P6" s="57"/>
     </row>
     <row r="7" spans="1:20" ht="76.5" customHeight="1">
       <c r="A7" s="50"/>
-      <c r="B7" s="145"/>
-      <c r="C7" s="145"/>
-      <c r="D7" s="145"/>
+      <c r="B7" s="153"/>
+      <c r="C7" s="153"/>
+      <c r="D7" s="153"/>
       <c r="E7" s="12" t="s">
         <v>109</v>
       </c>
@@ -9611,24 +9684,24 @@
       <c r="G7" s="10" t="s">
         <v>203</v>
       </c>
-      <c r="H7" s="144"/>
+      <c r="H7" s="152"/>
       <c r="I7" s="24" t="s">
         <v>539</v>
       </c>
-      <c r="J7" s="145"/>
+      <c r="J7" s="153"/>
       <c r="K7" s="50"/>
       <c r="L7" s="50"/>
       <c r="M7" s="50"/>
       <c r="N7" s="50"/>
       <c r="O7" s="50"/>
       <c r="P7" s="50"/>
-      <c r="Q7" s="114"/>
+      <c r="Q7" s="113"/>
     </row>
     <row r="8" spans="1:20" ht="98.55" customHeight="1">
       <c r="A8" s="50"/>
-      <c r="B8" s="145"/>
-      <c r="C8" s="145"/>
-      <c r="D8" s="145" t="s">
+      <c r="B8" s="153"/>
+      <c r="C8" s="153"/>
+      <c r="D8" s="153" t="s">
         <v>110</v>
       </c>
       <c r="E8" s="12" t="s">
@@ -9640,25 +9713,25 @@
       <c r="G8" s="10" t="s">
         <v>204</v>
       </c>
-      <c r="H8" s="149" t="s">
+      <c r="H8" s="157" t="s">
         <v>266</v>
       </c>
       <c r="I8" s="24" t="s">
         <v>540</v>
       </c>
-      <c r="J8" s="140" t="s">
+      <c r="J8" s="148" t="s">
         <v>274</v>
       </c>
       <c r="K8" s="50"/>
       <c r="L8" s="50"/>
       <c r="M8" s="50"/>
-      <c r="Q8" s="118"/>
+      <c r="Q8" s="117"/>
     </row>
     <row r="9" spans="1:20" ht="75.45" customHeight="1">
       <c r="A9" s="50"/>
-      <c r="B9" s="145"/>
-      <c r="C9" s="145"/>
-      <c r="D9" s="145"/>
+      <c r="B9" s="153"/>
+      <c r="C9" s="153"/>
+      <c r="D9" s="153"/>
       <c r="E9" s="12" t="s">
         <v>112</v>
       </c>
@@ -9668,48 +9741,48 @@
       <c r="G9" s="10" t="s">
         <v>205</v>
       </c>
-      <c r="H9" s="149"/>
+      <c r="H9" s="157"/>
       <c r="I9" s="24" t="s">
         <v>541</v>
       </c>
-      <c r="J9" s="141"/>
+      <c r="J9" s="150"/>
       <c r="K9" s="50"/>
       <c r="L9" s="50"/>
       <c r="M9" s="50"/>
-      <c r="Q9" s="80"/>
+      <c r="Q9" s="79"/>
     </row>
     <row r="10" spans="1:20" ht="109.95" customHeight="1">
       <c r="A10" s="50"/>
-      <c r="B10" s="145"/>
-      <c r="C10" s="145"/>
-      <c r="D10" s="145"/>
-      <c r="E10" s="185" t="s">
+      <c r="B10" s="153"/>
+      <c r="C10" s="153"/>
+      <c r="D10" s="153"/>
+      <c r="E10" s="188" t="s">
         <v>113</v>
       </c>
-      <c r="F10" s="185" t="s">
+      <c r="F10" s="188" t="s">
         <v>227</v>
       </c>
-      <c r="G10" s="186" t="s">
+      <c r="G10" s="189" t="s">
         <v>206</v>
       </c>
-      <c r="H10" s="149"/>
+      <c r="H10" s="157"/>
       <c r="I10" s="24" t="s">
         <v>542</v>
       </c>
-      <c r="J10" s="142"/>
+      <c r="J10" s="149"/>
       <c r="K10" s="50"/>
       <c r="L10" s="50"/>
       <c r="M10" s="50"/>
-      <c r="Q10" s="80"/>
+      <c r="Q10" s="79"/>
     </row>
     <row r="11" spans="1:20" ht="63" customHeight="1">
       <c r="A11" s="50"/>
-      <c r="B11" s="145"/>
-      <c r="C11" s="145"/>
-      <c r="D11" s="145"/>
-      <c r="E11" s="185"/>
-      <c r="F11" s="185"/>
-      <c r="G11" s="186"/>
+      <c r="B11" s="153"/>
+      <c r="C11" s="153"/>
+      <c r="D11" s="153"/>
+      <c r="E11" s="188"/>
+      <c r="F11" s="188"/>
+      <c r="G11" s="189"/>
       <c r="H11" s="2" t="s">
         <v>280</v>
       </c>
@@ -9731,18 +9804,6 @@
     </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="G10:G11"/>
-    <mergeCell ref="F10:F11"/>
-    <mergeCell ref="P3:P5"/>
-    <mergeCell ref="N2:O2"/>
-    <mergeCell ref="N3:O5"/>
-    <mergeCell ref="J4:J5"/>
-    <mergeCell ref="B4:B11"/>
-    <mergeCell ref="D6:D7"/>
-    <mergeCell ref="E10:E11"/>
-    <mergeCell ref="D8:D11"/>
-    <mergeCell ref="C4:C11"/>
-    <mergeCell ref="D4:D5"/>
     <mergeCell ref="T3:T5"/>
     <mergeCell ref="H8:H10"/>
     <mergeCell ref="H4:H5"/>
@@ -9752,31 +9813,43 @@
     <mergeCell ref="J8:J10"/>
     <mergeCell ref="Q3:Q5"/>
     <mergeCell ref="R3:R5"/>
+    <mergeCell ref="B4:B11"/>
+    <mergeCell ref="D6:D7"/>
+    <mergeCell ref="E10:E11"/>
+    <mergeCell ref="D8:D11"/>
+    <mergeCell ref="C4:C11"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="G10:G11"/>
+    <mergeCell ref="F10:F11"/>
+    <mergeCell ref="P3:P5"/>
+    <mergeCell ref="N2:O2"/>
+    <mergeCell ref="N3:O5"/>
+    <mergeCell ref="J4:J5"/>
   </mergeCells>
   <conditionalFormatting sqref="B3:E3">
-    <cfRule type="expression" dxfId="6" priority="9">
+    <cfRule type="expression" dxfId="14" priority="9">
       <formula>$A3="header"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:K3">
-    <cfRule type="expression" dxfId="5" priority="5">
+    <cfRule type="expression" dxfId="13" priority="5">
       <formula>$A3="header"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="4" priority="6">
+    <cfRule type="expression" dxfId="12" priority="6">
       <formula>$A3="blank"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J4 J6 J8 J11">
-    <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="11" priority="1" operator="equal">
       <formula>"N/A"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="10" priority="2" operator="equal">
       <formula>"N/A"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="9" priority="3" operator="equal">
       <formula>"No"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="8" priority="4" operator="equal">
       <formula>"Yes"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9807,258 +9880,258 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
-      <c r="A1" s="120" t="s">
+      <c r="A1" s="119" t="s">
         <v>148</v>
       </c>
-      <c r="B1" s="120" t="s">
+      <c r="B1" s="119" t="s">
         <v>608</v>
       </c>
-      <c r="C1" s="120" t="s">
+      <c r="C1" s="119" t="s">
         <v>609</v>
       </c>
-      <c r="D1" s="120" t="s">
+      <c r="D1" s="119" t="s">
         <v>275</v>
       </c>
-      <c r="E1" s="120" t="s">
+      <c r="E1" s="119" t="s">
         <v>273</v>
       </c>
-      <c r="F1" s="120" t="s">
+      <c r="F1" s="119" t="s">
         <v>274</v>
       </c>
-      <c r="G1" s="120" t="s">
+      <c r="G1" s="119" t="s">
         <v>610</v>
       </c>
-      <c r="H1" s="120" t="s">
+      <c r="H1" s="119" t="s">
         <v>602</v>
       </c>
-      <c r="I1" s="120" t="s">
+      <c r="I1" s="119" t="s">
         <v>611</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="14.55" customHeight="1">
-      <c r="A2" s="120" t="s">
+      <c r="A2" s="119" t="s">
         <v>595</v>
       </c>
-      <c r="B2" s="111">
+      <c r="B2" s="110">
         <f>'Questionnaire Domain Forensics'!$N$3</f>
         <v>4</v>
       </c>
-      <c r="C2" s="111">
+      <c r="C2" s="110">
         <f>'Questionnaire Domain Forensics'!$P$3</f>
         <v>3</v>
       </c>
-      <c r="D2" s="111">
+      <c r="D2" s="110">
         <f>'Questionnaire Domain Forensics'!$Q$3</f>
         <v>2</v>
       </c>
-      <c r="E2" s="111">
+      <c r="E2" s="110">
         <f>'Questionnaire Domain Forensics'!$R$3</f>
         <v>0</v>
       </c>
-      <c r="F2" s="111">
+      <c r="F2" s="110">
         <f>'Questionnaire Domain Forensics'!$S$3</f>
         <v>1</v>
       </c>
-      <c r="G2" s="122">
+      <c r="G2" s="121">
         <f>'Questionnaire Domain Forensics'!$T$3</f>
         <v>0.66666666666666663</v>
       </c>
-      <c r="H2" s="125">
+      <c r="H2" s="124">
         <f>PONDERATION!$L$20</f>
         <v>6</v>
       </c>
-      <c r="I2" s="127" t="str">
+      <c r="I2" s="126" t="str">
         <f>'Questionnaire Domain Forensics'!$O$6</f>
         <v>Oumayma</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="14.55" customHeight="1">
-      <c r="A3" s="120" t="s">
+      <c r="A3" s="119" t="s">
         <v>596</v>
       </c>
-      <c r="B3" s="111">
+      <c r="B3" s="110">
         <f>'Question Continuité d’activité'!$L$3</f>
         <v>11</v>
       </c>
-      <c r="C3" s="111">
+      <c r="C3" s="110">
         <f>'Question Continuité d’activité'!$N$3</f>
         <v>8</v>
       </c>
-      <c r="D3" s="111">
+      <c r="D3" s="110">
         <f>'Question Continuité d’activité'!$O$3</f>
-        <v>4</v>
-      </c>
-      <c r="E3" s="111">
+        <v>7</v>
+      </c>
+      <c r="E3" s="110">
         <f>'Question Continuité d’activité'!$P$3</f>
-        <v>4</v>
-      </c>
-      <c r="F3" s="111">
+        <v>1</v>
+      </c>
+      <c r="F3" s="110">
         <f>'Question Continuité d’activité'!$Q$3</f>
         <v>3</v>
       </c>
-      <c r="G3" s="122">
+      <c r="G3" s="121">
         <f>'Question Continuité d’activité'!$R$3</f>
-        <v>0.5</v>
-      </c>
-      <c r="H3" s="125">
+        <v>0.875</v>
+      </c>
+      <c r="H3" s="124">
         <f>PONDERATION!$L$19</f>
         <v>23</v>
       </c>
-      <c r="I3" s="127" t="str">
+      <c r="I3" s="126" t="str">
         <f>'Question Continuité d’activité'!$T$4</f>
         <v>Dhia</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="14.55" customHeight="1">
-      <c r="A4" s="120" t="s">
+      <c r="A4" s="119" t="s">
         <v>597</v>
       </c>
-      <c r="B4" s="111">
+      <c r="B4" s="110">
         <f>'Questionnaire Gestion de crise'!$L$3</f>
         <v>21</v>
       </c>
-      <c r="C4" s="111">
+      <c r="C4" s="110">
         <f>'Questionnaire Gestion de crise'!$N$3</f>
         <v>20</v>
       </c>
-      <c r="D4" s="111">
+      <c r="D4" s="110">
         <f>'Questionnaire Gestion de crise'!$O$3</f>
         <v>16</v>
       </c>
-      <c r="E4" s="111">
+      <c r="E4" s="110">
         <f>'Questionnaire Gestion de crise'!$P$3</f>
         <v>0</v>
       </c>
-      <c r="F4" s="111">
+      <c r="F4" s="110">
         <f>'Questionnaire Gestion de crise'!$Q$3</f>
         <v>1</v>
       </c>
-      <c r="G4" s="122">
+      <c r="G4" s="121">
         <f>'Questionnaire Gestion de crise'!$R$3</f>
         <v>0.8</v>
       </c>
-      <c r="H4" s="125">
+      <c r="H4" s="124">
         <f>PONDERATION!$L$18</f>
         <v>20</v>
       </c>
-      <c r="I4" s="127" t="str">
+      <c r="I4" s="126" t="str">
         <f>'Questionnaire Gestion de crise'!$M$7</f>
         <v>Oumayma</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="14.55" customHeight="1">
-      <c r="A5" s="120" t="s">
+      <c r="A5" s="119" t="s">
         <v>598</v>
       </c>
-      <c r="B5" s="123">
+      <c r="B5" s="122">
         <f>'Questionnaire Gestion Incidents'!$P$2</f>
         <v>17</v>
       </c>
-      <c r="C5" s="111">
+      <c r="C5" s="110">
         <f>'Questionnaire Gestion Incidents'!$R$2</f>
         <v>16</v>
       </c>
-      <c r="D5" s="123">
+      <c r="D5" s="122">
         <f>'Questionnaire Gestion Incidents'!$N$2</f>
         <v>14</v>
       </c>
-      <c r="E5" s="123">
+      <c r="E5" s="122">
         <f>'Questionnaire Gestion Incidents'!$N$3</f>
         <v>2</v>
       </c>
-      <c r="F5" s="123">
+      <c r="F5" s="122">
         <f>'Questionnaire Gestion Incidents'!$N$4</f>
         <v>1</v>
       </c>
-      <c r="G5" s="122">
+      <c r="G5" s="121">
         <f>'Questionnaire Gestion Incidents'!$L$2</f>
         <v>0.875</v>
       </c>
-      <c r="H5" s="125">
+      <c r="H5" s="124">
         <f>PONDERATION!$L$17</f>
         <v>18.5</v>
       </c>
-      <c r="I5" s="127" t="str">
+      <c r="I5" s="126" t="str">
         <f>'Questionnaire Gestion Incidents'!$N$5</f>
         <v>Oumayma</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="14.55" customHeight="1">
-      <c r="A6" s="120" t="s">
+      <c r="A6" s="119" t="s">
         <v>599</v>
       </c>
-      <c r="B6" s="111">
+      <c r="B6" s="110">
         <f>'Questionnaire Confirmitee'!$L$3</f>
         <v>4</v>
       </c>
-      <c r="C6" s="111">
+      <c r="C6" s="110">
         <f>'Questionnaire Confirmitee'!$Q$3</f>
         <v>3</v>
       </c>
-      <c r="D6" s="111">
+      <c r="D6" s="110">
         <f>'Questionnaire Confirmitee'!$N$3</f>
         <v>2</v>
       </c>
-      <c r="E6" s="111">
+      <c r="E6" s="110">
         <f>'Questionnaire Confirmitee'!$O$3</f>
         <v>1</v>
       </c>
-      <c r="F6" s="111">
+      <c r="F6" s="110">
         <f>'Questionnaire Confirmitee'!$P$3</f>
         <v>1</v>
       </c>
-      <c r="G6" s="122">
+      <c r="G6" s="121">
         <f>'Questionnaire Confirmitee'!$R$3</f>
         <v>0.66666666666666663</v>
       </c>
-      <c r="H6" s="125">
+      <c r="H6" s="124">
         <f>PONDERATION!$L$21</f>
         <v>6</v>
       </c>
-      <c r="I6" s="127" t="str">
+      <c r="I6" s="126" t="str">
         <f>'Questionnaire Confirmitee'!$M$7</f>
         <v>Oumayma</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="14.55" customHeight="1">
-      <c r="A7" s="195" t="s">
+      <c r="A7" s="128" t="s">
         <v>594</v>
       </c>
-      <c r="B7" s="196">
+      <c r="B7" s="129">
         <f>'Questionnaire Gouvernance '!$Q$2</f>
         <v>35</v>
       </c>
-      <c r="C7" s="196">
+      <c r="C7" s="129">
         <f>'Questionnaire Gouvernance '!$S$2</f>
-        <v>32</v>
-      </c>
-      <c r="D7" s="196">
+        <v>35</v>
+      </c>
+      <c r="D7" s="129">
         <f>'Questionnaire Gouvernance '!$O$2</f>
-        <v>20</v>
-      </c>
-      <c r="E7" s="196">
+        <v>34</v>
+      </c>
+      <c r="E7" s="129">
         <f>'Questionnaire Gouvernance '!$O$3</f>
-        <v>12</v>
-      </c>
-      <c r="F7" s="196">
+        <v>1</v>
+      </c>
+      <c r="F7" s="129">
         <f>'Questionnaire Gouvernance '!$O$4</f>
-        <v>3</v>
-      </c>
-      <c r="G7" s="197">
+        <v>0</v>
+      </c>
+      <c r="G7" s="130">
         <f>'Questionnaire Gouvernance '!$L$2</f>
-        <v>0.625</v>
-      </c>
-      <c r="H7" s="198">
+        <v>0.97142857142857142</v>
+      </c>
+      <c r="H7" s="131">
         <f>PONDERATION!$L$16</f>
         <v>26.5</v>
       </c>
-      <c r="I7" s="127" t="str">
+      <c r="I7" s="126" t="str">
         <f>'Questionnaire Gouvernance '!$U$2</f>
         <v>Dhia</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="15" customHeight="1">
-      <c r="A8" s="199" t="s">
+      <c r="A8" s="132" t="s">
         <v>272</v>
       </c>
       <c r="B8" s="18">
@@ -10067,23 +10140,23 @@
       </c>
       <c r="C8" s="18">
         <f>SUM(C2:C7)</f>
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="D8" s="18">
         <f t="shared" ref="D8:F8" si="0">SUM(D2:D7)</f>
-        <v>58</v>
+        <v>75</v>
       </c>
       <c r="E8" s="18">
         <f t="shared" si="0"/>
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="F8" s="18">
         <f t="shared" si="0"/>
-        <v>10</v>
-      </c>
-      <c r="G8" s="200">
+        <v>7</v>
+      </c>
+      <c r="G8" s="133">
         <f>G2*H2+G3*H3+G4*H4+G5*H5+G6*H6+G7*H7</f>
-        <v>68.25</v>
+        <v>86.055357142857147</v>
       </c>
       <c r="H8" s="18">
         <f>SUM(H2:H7)</f>
@@ -10099,127 +10172,127 @@
       <c r="F10" s="47"/>
     </row>
     <row r="11" spans="1:9" ht="21">
-      <c r="A11" s="113" t="s">
+      <c r="A11" s="112" t="s">
         <v>603</v>
       </c>
-      <c r="B11" s="113" t="s">
+      <c r="B11" s="112" t="s">
         <v>607</v>
       </c>
-      <c r="C11" s="113" t="s">
+      <c r="C11" s="112" t="s">
         <v>604</v>
       </c>
-      <c r="D11" s="113" t="s">
+      <c r="D11" s="112" t="s">
         <v>605</v>
       </c>
-      <c r="E11" s="113" t="s">
+      <c r="E11" s="112" t="s">
         <v>606</v>
       </c>
-      <c r="F11" s="119"/>
+      <c r="F11" s="118"/>
     </row>
     <row r="12" spans="1:9">
-      <c r="A12" s="121">
+      <c r="A12" s="120">
         <v>1</v>
       </c>
       <c r="B12" s="42" t="s">
         <v>378</v>
       </c>
-      <c r="C12" s="112">
+      <c r="C12" s="111">
         <v>0</v>
       </c>
-      <c r="D12" s="112">
+      <c r="D12" s="111">
         <v>16</v>
       </c>
-      <c r="E12" s="112">
+      <c r="E12" s="111">
         <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:9">
-      <c r="A13" s="121">
+      <c r="A13" s="120">
         <v>2</v>
       </c>
       <c r="B13" s="42" t="s">
         <v>379</v>
       </c>
-      <c r="C13" s="112">
+      <c r="C13" s="111">
         <v>17</v>
       </c>
-      <c r="D13" s="112">
+      <c r="D13" s="111">
         <v>33</v>
       </c>
-      <c r="E13" s="112">
+      <c r="E13" s="111">
         <v>2</v>
       </c>
     </row>
     <row r="14" spans="1:9">
-      <c r="A14" s="121">
+      <c r="A14" s="120">
         <v>3</v>
       </c>
       <c r="B14" s="42" t="s">
         <v>380</v>
       </c>
-      <c r="C14" s="112">
+      <c r="C14" s="111">
         <v>34</v>
       </c>
-      <c r="D14" s="112">
+      <c r="D14" s="111">
         <v>51</v>
       </c>
-      <c r="E14" s="112">
+      <c r="E14" s="111">
         <v>3</v>
       </c>
     </row>
     <row r="15" spans="1:9">
-      <c r="A15" s="121">
+      <c r="A15" s="120">
         <v>4</v>
       </c>
       <c r="B15" s="42" t="s">
         <v>381</v>
       </c>
-      <c r="C15" s="112">
+      <c r="C15" s="111">
         <v>52</v>
       </c>
-      <c r="D15" s="112">
+      <c r="D15" s="111">
         <v>68</v>
       </c>
-      <c r="E15" s="112">
+      <c r="E15" s="111">
         <v>4</v>
       </c>
     </row>
     <row r="16" spans="1:9">
-      <c r="A16" s="121">
+      <c r="A16" s="120">
         <v>5</v>
       </c>
       <c r="B16" s="42" t="s">
         <v>382</v>
       </c>
-      <c r="C16" s="112">
+      <c r="C16" s="111">
         <v>69</v>
       </c>
-      <c r="D16" s="112">
+      <c r="D16" s="111">
         <v>85</v>
       </c>
-      <c r="E16" s="112">
+      <c r="E16" s="111">
         <v>5</v>
       </c>
     </row>
     <row r="17" spans="1:5">
-      <c r="A17" s="121">
+      <c r="A17" s="120">
         <v>6</v>
       </c>
       <c r="B17" s="42" t="s">
         <v>383</v>
       </c>
-      <c r="C17" s="112">
+      <c r="C17" s="111">
         <v>86</v>
       </c>
-      <c r="D17" s="112">
+      <c r="D17" s="111">
         <v>100</v>
       </c>
-      <c r="E17" s="112">
+      <c r="E17" s="111">
         <v>6</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" copies="2" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" copies="2" r:id="rId1"/>
 </worksheet>
 </file>